--- a/public/docs/datas/pokes.xlsx
+++ b/public/docs/datas/pokes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="24060" activeTab="1"/>
+    <workbookView windowWidth="26420" windowHeight="10260" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="pokes" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10133" uniqueCount="6055">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10133" uniqueCount="6056">
   <si>
     <t>no</t>
   </si>
@@ -16511,6 +16511,9 @@
   </si>
   <si>
     <t>0445-mega.png</t>
+  </si>
+  <si>
+    <t>超进化Z</t>
   </si>
   <si>
     <t>0445-mega-z.png</t>
@@ -52772,7 +52775,7 @@
         <v>34</v>
       </c>
       <c r="K2" s="4">
-        <f>SUM(L2:Q2)</f>
+        <f t="shared" ref="K2:K33" si="0">SUM(L2:Q2)</f>
         <v>625</v>
       </c>
       <c r="L2" s="6">
@@ -52824,7 +52827,7 @@
         <v>34</v>
       </c>
       <c r="K3" s="4">
-        <f>SUM(L3:Q3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L3" s="5"/>
@@ -52860,7 +52863,7 @@
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
       <c r="K4" s="4">
-        <f>SUM(L4:Q4)</f>
+        <f t="shared" si="0"/>
         <v>634</v>
       </c>
       <c r="L4" s="6">
@@ -52908,7 +52911,7 @@
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="4">
-        <f>SUM(L5:Q5)</f>
+        <f t="shared" si="0"/>
         <v>634</v>
       </c>
       <c r="L5" s="6">
@@ -52956,7 +52959,7 @@
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="4">
-        <f>SUM(L6:Q6)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L6" s="6"/>
@@ -52990,7 +52993,7 @@
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
       <c r="K7" s="4">
-        <f>SUM(L7:Q7)</f>
+        <f t="shared" si="0"/>
         <v>630</v>
       </c>
       <c r="L7" s="6">
@@ -53036,7 +53039,7 @@
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
       <c r="K8" s="4">
-        <f>SUM(L8:Q8)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L8" s="6"/>
@@ -53072,7 +53075,7 @@
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
       <c r="K9" s="4">
-        <f>SUM(L9:Q9)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L9" s="6"/>
@@ -53108,7 +53111,7 @@
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
       <c r="K10" s="4">
-        <f>SUM(L10:Q10)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L10" s="6"/>
@@ -53144,7 +53147,7 @@
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
       <c r="K11" s="4">
-        <f>SUM(L11:Q11)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L11" s="6"/>
@@ -53180,7 +53183,7 @@
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
       <c r="K12" s="4">
-        <f>SUM(L12:Q12)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L12" s="6"/>
@@ -53216,7 +53219,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
       <c r="K13" s="4">
-        <f>SUM(L13:Q13)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L13" s="6"/>
@@ -53250,7 +53253,7 @@
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
       <c r="K14" s="4">
-        <f>SUM(L14:Q14)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L14" s="6"/>
@@ -53286,7 +53289,7 @@
       <c r="I15" s="5"/>
       <c r="J15" s="5"/>
       <c r="K15" s="4">
-        <f>SUM(L15:Q15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L15" s="6"/>
@@ -53320,7 +53323,7 @@
       <c r="I16" s="5"/>
       <c r="J16" s="5"/>
       <c r="K16" s="4">
-        <f>SUM(L16:Q16)</f>
+        <f t="shared" si="0"/>
         <v>585</v>
       </c>
       <c r="L16" s="6">
@@ -53366,7 +53369,7 @@
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
       <c r="K17" s="4">
-        <f>SUM(L17:Q17)</f>
+        <f t="shared" si="0"/>
         <v>585</v>
       </c>
       <c r="L17" s="6">
@@ -53414,7 +53417,7 @@
       <c r="I18" s="5"/>
       <c r="J18" s="5"/>
       <c r="K18" s="4">
-        <f>SUM(L18:Q18)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L18" s="6"/>
@@ -53450,7 +53453,7 @@
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
       <c r="K19" s="4">
-        <f>SUM(L19:Q19)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L19" s="6"/>
@@ -53486,7 +53489,7 @@
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
       <c r="K20" s="4">
-        <f>SUM(L20:Q20)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L20" s="6"/>
@@ -53520,7 +53523,7 @@
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
       <c r="K21" s="4">
-        <f>SUM(L21:Q21)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L21" s="6"/>
@@ -53556,7 +53559,7 @@
       <c r="I22" s="5"/>
       <c r="J22" s="5"/>
       <c r="K22" s="4">
-        <f>SUM(L22:Q22)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L22" s="6"/>
@@ -53592,7 +53595,7 @@
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
       <c r="K23" s="4">
-        <f>SUM(L23:Q23)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L23" s="6"/>
@@ -53628,7 +53631,7 @@
       <c r="I24" s="5"/>
       <c r="J24" s="5"/>
       <c r="K24" s="4">
-        <f>SUM(L24:Q24)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L24" s="6"/>
@@ -53662,7 +53665,7 @@
       <c r="I25" s="5"/>
       <c r="J25" s="5"/>
       <c r="K25" s="4">
-        <f>SUM(L25:Q25)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L25" s="6"/>
@@ -53696,7 +53699,7 @@
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
       <c r="K26" s="4">
-        <f>SUM(L26:Q26)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L26" s="6"/>
@@ -53730,7 +53733,7 @@
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
       <c r="K27" s="4">
-        <f>SUM(L27:Q27)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L27" s="6"/>
@@ -53766,7 +53769,7 @@
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
       <c r="K28" s="4">
-        <f>SUM(L28:Q28)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L28" s="6"/>
@@ -53802,7 +53805,7 @@
       <c r="I29" s="5"/>
       <c r="J29" s="5"/>
       <c r="K29" s="4">
-        <f>SUM(L29:Q29)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L29" s="6"/>
@@ -53836,7 +53839,7 @@
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
       <c r="K30" s="4">
-        <f>SUM(L30:Q30)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L30" s="6"/>
@@ -53870,7 +53873,7 @@
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
       <c r="K31" s="4">
-        <f>SUM(L31:Q31)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L31" s="6"/>
@@ -53906,7 +53909,7 @@
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
       <c r="K32" s="4">
-        <f>SUM(L32:Q32)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L32" s="6"/>
@@ -53942,7 +53945,7 @@
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
       <c r="K33" s="4">
-        <f>SUM(L33:Q33)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L33" s="6"/>
@@ -53978,7 +53981,7 @@
       <c r="I34" s="5"/>
       <c r="J34" s="5"/>
       <c r="K34" s="4">
-        <f t="shared" ref="K33:K70" si="0">SUM(L34:Q34)</f>
+        <f t="shared" ref="K33:K70" si="1">SUM(L34:Q34)</f>
         <v>0</v>
       </c>
       <c r="L34" s="6"/>
@@ -54014,7 +54017,7 @@
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
       <c r="K35" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L35" s="6"/>
@@ -54048,7 +54051,7 @@
       <c r="I36" s="5"/>
       <c r="J36" s="5"/>
       <c r="K36" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L36" s="6"/>
@@ -54084,7 +54087,7 @@
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
       <c r="K37" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L37" s="6"/>
@@ -54118,7 +54121,7 @@
       <c r="I38" s="5"/>
       <c r="J38" s="5"/>
       <c r="K38" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L38" s="6"/>
@@ -54154,7 +54157,7 @@
       <c r="I39" s="5"/>
       <c r="J39" s="5"/>
       <c r="K39" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L39" s="6"/>
@@ -54190,7 +54193,7 @@
       <c r="I40" s="5"/>
       <c r="J40" s="5"/>
       <c r="K40" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L40" s="6"/>
@@ -54224,7 +54227,7 @@
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
       <c r="K41" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L41" s="6"/>
@@ -54260,7 +54263,7 @@
       <c r="I42" s="5"/>
       <c r="J42" s="5"/>
       <c r="K42" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L42" s="6"/>
@@ -54296,7 +54299,7 @@
       <c r="I43" s="5"/>
       <c r="J43" s="5"/>
       <c r="K43" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L43" s="6"/>
@@ -54332,7 +54335,7 @@
       <c r="I44" s="5"/>
       <c r="J44" s="5"/>
       <c r="K44" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L44" s="6"/>
@@ -54368,7 +54371,7 @@
       <c r="I45" s="5"/>
       <c r="J45" s="5"/>
       <c r="K45" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L45" s="6"/>
@@ -54402,7 +54405,7 @@
       <c r="I46" s="5"/>
       <c r="J46" s="5"/>
       <c r="K46" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L46" s="6"/>
@@ -54438,7 +54441,7 @@
       <c r="I47" s="5"/>
       <c r="J47" s="5"/>
       <c r="K47" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L47" s="6"/>
@@ -54474,7 +54477,7 @@
       <c r="I48" s="5"/>
       <c r="J48" s="5"/>
       <c r="K48" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L48" s="6"/>
@@ -54510,7 +54513,7 @@
       <c r="I49" s="5"/>
       <c r="J49" s="5"/>
       <c r="K49" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L49" s="6"/>
@@ -54546,7 +54549,7 @@
       <c r="I50" s="5"/>
       <c r="J50" s="5"/>
       <c r="K50" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L50" s="6"/>
@@ -54582,7 +54585,7 @@
       <c r="I51" s="5"/>
       <c r="J51" s="5"/>
       <c r="K51" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L51" s="6"/>
@@ -54616,7 +54619,7 @@
       <c r="I52" s="5"/>
       <c r="J52" s="5"/>
       <c r="K52" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L52" s="6"/>
@@ -54685,7 +54688,7 @@
       <c r="I54" s="5"/>
       <c r="J54" s="5"/>
       <c r="K54" s="4">
-        <f>SUM(L54:Q54)</f>
+        <f t="shared" ref="K54:K113" si="2">SUM(L54:Q54)</f>
         <v>0</v>
       </c>
       <c r="L54" s="6"/>
@@ -54721,7 +54724,7 @@
       <c r="I55" s="5"/>
       <c r="J55" s="5"/>
       <c r="K55" s="4">
-        <f>SUM(L55:Q55)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L55" s="6"/>
@@ -54755,7 +54758,7 @@
       <c r="I56" s="5"/>
       <c r="J56" s="5"/>
       <c r="K56" s="4">
-        <f>SUM(L56:Q56)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L56" s="6"/>
@@ -54791,7 +54794,7 @@
       <c r="I57" s="5"/>
       <c r="J57" s="5"/>
       <c r="K57" s="4">
-        <f>SUM(L57:Q57)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L57" s="6"/>
@@ -54827,7 +54830,7 @@
       <c r="I58" s="5"/>
       <c r="J58" s="5"/>
       <c r="K58" s="4">
-        <f>SUM(L58:Q58)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L58" s="6"/>
@@ -54863,7 +54866,7 @@
       <c r="I59" s="5"/>
       <c r="J59" s="5"/>
       <c r="K59" s="4">
-        <f>SUM(L59:Q59)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L59" s="6"/>
@@ -54899,7 +54902,7 @@
       <c r="I60" s="5"/>
       <c r="J60" s="5"/>
       <c r="K60" s="4">
-        <f>SUM(L60:Q60)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L60" s="6"/>
@@ -54933,7 +54936,7 @@
       <c r="I61" s="5"/>
       <c r="J61" s="5"/>
       <c r="K61" s="4">
-        <f>SUM(L61:Q61)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L61" s="6"/>
@@ -54969,7 +54972,7 @@
       <c r="I62" s="5"/>
       <c r="J62" s="5"/>
       <c r="K62" s="4">
-        <f>SUM(L62:Q62)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L62" s="6"/>
@@ -55003,7 +55006,7 @@
       <c r="I63" s="5"/>
       <c r="J63" s="5"/>
       <c r="K63" s="4">
-        <f>SUM(L63:Q63)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L63" s="6"/>
@@ -55039,7 +55042,7 @@
       <c r="I64" s="5"/>
       <c r="J64" s="5"/>
       <c r="K64" s="4">
-        <f>SUM(L64:Q64)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L64" s="6"/>
@@ -55075,7 +55078,7 @@
       <c r="I65" s="5"/>
       <c r="J65" s="5"/>
       <c r="K65" s="4">
-        <f>SUM(L65:Q65)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L65" s="6"/>
@@ -55111,7 +55114,7 @@
       <c r="I66" s="5"/>
       <c r="J66" s="5"/>
       <c r="K66" s="4">
-        <f>SUM(L66:Q66)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L66" s="6"/>
@@ -55147,7 +55150,7 @@
       <c r="I67" s="5"/>
       <c r="J67" s="5"/>
       <c r="K67" s="4">
-        <f>SUM(L67:Q67)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L67" s="6"/>
@@ -55183,7 +55186,7 @@
       <c r="I68" s="5"/>
       <c r="J68" s="5"/>
       <c r="K68" s="4">
-        <f>SUM(L68:Q68)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L68" s="6"/>
@@ -55217,7 +55220,7 @@
       <c r="I69" s="5"/>
       <c r="J69" s="5"/>
       <c r="K69" s="4">
-        <f>SUM(L69:Q69)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L69" s="6"/>
@@ -55253,7 +55256,7 @@
       <c r="I70" s="5"/>
       <c r="J70" s="5"/>
       <c r="K70" s="4">
-        <f>SUM(L70:Q70)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L70" s="6"/>
@@ -55289,7 +55292,7 @@
       <c r="I71" s="5"/>
       <c r="J71" s="5"/>
       <c r="K71" s="4">
-        <f>SUM(L71:Q71)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L71" s="6"/>
@@ -55325,7 +55328,7 @@
       <c r="I72" s="5"/>
       <c r="J72" s="5"/>
       <c r="K72" s="4">
-        <f>SUM(L72:Q72)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L72" s="6"/>
@@ -55361,7 +55364,7 @@
       <c r="I73" s="5"/>
       <c r="J73" s="5"/>
       <c r="K73" s="4">
-        <f>SUM(L73:Q73)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L73" s="6"/>
@@ -55397,7 +55400,7 @@
       <c r="I74" s="5"/>
       <c r="J74" s="5"/>
       <c r="K74" s="4">
-        <f>SUM(L74:Q74)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L74" s="6"/>
@@ -55433,7 +55436,7 @@
       <c r="I75" s="5"/>
       <c r="J75" s="5"/>
       <c r="K75" s="4">
-        <f>SUM(L75:Q75)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L75" s="6"/>
@@ -55469,7 +55472,7 @@
       <c r="I76" s="5"/>
       <c r="J76" s="5"/>
       <c r="K76" s="4">
-        <f>SUM(L76:Q76)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L76" s="6"/>
@@ -55505,7 +55508,7 @@
       <c r="I77" s="5"/>
       <c r="J77" s="5"/>
       <c r="K77" s="4">
-        <f>SUM(L77:Q77)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L77" s="6"/>
@@ -55541,7 +55544,7 @@
       <c r="I78" s="5"/>
       <c r="J78" s="5"/>
       <c r="K78" s="4">
-        <f>SUM(L78:Q78)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L78" s="6"/>
@@ -55577,7 +55580,7 @@
       <c r="I79" s="5"/>
       <c r="J79" s="5"/>
       <c r="K79" s="4">
-        <f>SUM(L79:Q79)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L79" s="6"/>
@@ -55613,7 +55616,7 @@
       <c r="I80" s="5"/>
       <c r="J80" s="5"/>
       <c r="K80" s="4">
-        <f>SUM(L80:Q80)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L80" s="6"/>
@@ -55647,7 +55650,7 @@
       <c r="I81" s="5"/>
       <c r="J81" s="5"/>
       <c r="K81" s="4">
-        <f>SUM(L81:Q81)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L81" s="6"/>
@@ -55683,7 +55686,7 @@
       <c r="I82" s="5"/>
       <c r="J82" s="5"/>
       <c r="K82" s="4">
-        <f>SUM(L82:Q82)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L82" s="6"/>
@@ -55719,7 +55722,7 @@
       <c r="I83" s="5"/>
       <c r="J83" s="5"/>
       <c r="K83" s="4">
-        <f>SUM(L83:Q83)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L83" s="6"/>
@@ -55755,7 +55758,7 @@
       <c r="I84" s="5"/>
       <c r="J84" s="5"/>
       <c r="K84" s="4">
-        <f>SUM(L84:Q84)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L84" s="6"/>
@@ -55791,7 +55794,7 @@
       <c r="I85" s="5"/>
       <c r="J85" s="5"/>
       <c r="K85" s="4">
-        <f>SUM(L85:Q85)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L85" s="6"/>
@@ -55827,7 +55830,7 @@
       <c r="I86" s="5"/>
       <c r="J86" s="5"/>
       <c r="K86" s="4">
-        <f>SUM(L86:Q86)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L86" s="6"/>
@@ -55863,7 +55866,7 @@
       <c r="I87" s="5"/>
       <c r="J87" s="5"/>
       <c r="K87" s="4">
-        <f>SUM(L87:Q87)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L87" s="6"/>
@@ -55899,7 +55902,7 @@
       <c r="I88" s="5"/>
       <c r="J88" s="5"/>
       <c r="K88" s="4">
-        <f>SUM(L88:Q88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L88" s="6"/>
@@ -55935,7 +55938,7 @@
       <c r="I89" s="5"/>
       <c r="J89" s="5"/>
       <c r="K89" s="4">
-        <f>SUM(L89:Q89)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L89" s="6"/>
@@ -55971,7 +55974,7 @@
       <c r="I90" s="5"/>
       <c r="J90" s="5"/>
       <c r="K90" s="4">
-        <f>SUM(L90:Q90)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L90" s="6"/>
@@ -56007,7 +56010,7 @@
       <c r="I91" s="5"/>
       <c r="J91" s="5"/>
       <c r="K91" s="4">
-        <f>SUM(L91:Q91)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L91" s="6"/>
@@ -56043,7 +56046,7 @@
       <c r="I92" s="5"/>
       <c r="J92" s="5"/>
       <c r="K92" s="4">
-        <f>SUM(L92:Q92)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L92" s="6"/>
@@ -56077,7 +56080,7 @@
       <c r="I93" s="5"/>
       <c r="J93" s="5"/>
       <c r="K93" s="4">
-        <f>SUM(L93:Q93)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L93" s="6"/>
@@ -56113,7 +56116,7 @@
       <c r="I94" s="5"/>
       <c r="J94" s="5"/>
       <c r="K94" s="4">
-        <f>SUM(L94:Q94)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L94" s="6"/>
@@ -56147,7 +56150,7 @@
       <c r="I95" s="5"/>
       <c r="J95" s="5"/>
       <c r="K95" s="4">
-        <f>SUM(L95:Q95)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L95" s="6"/>
@@ -56183,7 +56186,7 @@
       <c r="I96" s="5"/>
       <c r="J96" s="5"/>
       <c r="K96" s="4">
-        <f>SUM(L96:Q96)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L96" s="6"/>
@@ -56219,7 +56222,7 @@
       <c r="I97" s="5"/>
       <c r="J97" s="5"/>
       <c r="K97" s="4">
-        <f>SUM(L97:Q97)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L97" s="6"/>
@@ -56255,7 +56258,7 @@
       <c r="I98" s="5"/>
       <c r="J98" s="5"/>
       <c r="K98" s="4">
-        <f>SUM(L98:Q98)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L98" s="6"/>
@@ -56289,7 +56292,7 @@
       <c r="I99" s="5"/>
       <c r="J99" s="5"/>
       <c r="K99" s="4">
-        <f>SUM(L99:Q99)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L99" s="6"/>
@@ -56325,7 +56328,7 @@
       <c r="I100" s="5"/>
       <c r="J100" s="5"/>
       <c r="K100" s="4">
-        <f>SUM(L100:Q100)</f>
+        <f t="shared" si="2"/>
         <v>555</v>
       </c>
       <c r="L100" s="6">
@@ -56371,7 +56374,7 @@
       <c r="I101" s="5"/>
       <c r="J101" s="5"/>
       <c r="K101" s="4">
-        <f>SUM(L101:Q101)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L101" s="6"/>
@@ -56407,7 +56410,7 @@
       <c r="I102" s="5"/>
       <c r="J102" s="5"/>
       <c r="K102" s="4">
-        <f>SUM(L102:Q102)</f>
+        <f t="shared" si="2"/>
         <v>565</v>
       </c>
       <c r="L102" s="6">
@@ -56453,7 +56456,7 @@
       <c r="I103" s="5"/>
       <c r="J103" s="5"/>
       <c r="K103" s="4">
-        <f>SUM(L103:Q103)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L103" s="6"/>
@@ -56489,7 +56492,7 @@
       <c r="I104" s="5"/>
       <c r="J104" s="5"/>
       <c r="K104" s="4">
-        <f>SUM(L104:Q104)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L104" s="6"/>
@@ -56525,7 +56528,7 @@
       <c r="I105" s="5"/>
       <c r="J105" s="5"/>
       <c r="K105" s="4">
-        <f>SUM(L105:Q105)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L105" s="6"/>
@@ -56561,7 +56564,7 @@
       <c r="I106" s="5"/>
       <c r="J106" s="5"/>
       <c r="K106" s="4">
-        <f>SUM(L106:Q106)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L106" s="6"/>
@@ -56597,7 +56600,7 @@
       <c r="I107" s="5"/>
       <c r="J107" s="5"/>
       <c r="K107" s="4">
-        <f>SUM(L107:Q107)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L107" s="6"/>
@@ -56629,7 +56632,7 @@
       <c r="I108" s="5"/>
       <c r="J108" s="5"/>
       <c r="K108" s="4">
-        <f>SUM(L108:Q108)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L108" s="6"/>
@@ -56663,7 +56666,7 @@
       <c r="I109" s="5"/>
       <c r="J109" s="5"/>
       <c r="K109" s="4">
-        <f>SUM(L109:Q109)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L109" s="6"/>
@@ -56699,7 +56702,7 @@
       <c r="I110" s="5"/>
       <c r="J110" s="5"/>
       <c r="K110" s="4">
-        <f>SUM(L110:Q110)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L110" s="6"/>
@@ -56731,7 +56734,7 @@
       <c r="I111" s="5"/>
       <c r="J111" s="5"/>
       <c r="K111" s="4">
-        <f>SUM(L111:Q111)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L111" s="6"/>
@@ -56763,7 +56766,7 @@
       <c r="I112" s="5"/>
       <c r="J112" s="5"/>
       <c r="K112" s="4">
-        <f>SUM(L112:Q112)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L112" s="6"/>
@@ -56795,7 +56798,7 @@
       <c r="I113" s="5"/>
       <c r="J113" s="5"/>
       <c r="K113" s="4">
-        <f>SUM(L113:Q113)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L113" s="6"/>
@@ -57157,7 +57160,7 @@
         <v>2358</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>5340</v>
+        <v>5492</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>5340</v>
@@ -57170,7 +57173,7 @@
       </c>
       <c r="F124" s="4"/>
       <c r="G124" s="5" t="s">
-        <v>5492</v>
+        <v>5493</v>
       </c>
       <c r="H124" s="5"/>
       <c r="I124" s="5"/>
@@ -57218,13 +57221,13 @@
         <v>504</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>5493</v>
+        <v>5494</v>
       </c>
       <c r="H125" s="5"/>
       <c r="I125" s="5"/>
       <c r="J125" s="5"/>
       <c r="K125" s="4">
-        <f>SUM(L125:Q125)</f>
+        <f t="shared" ref="K125:K136" si="3">SUM(L125:Q125)</f>
         <v>625</v>
       </c>
       <c r="L125" s="6">
@@ -57251,7 +57254,7 @@
         <v>2374</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>5340</v>
+        <v>5492</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>5340</v>
@@ -57266,13 +57269,13 @@
         <v>504</v>
       </c>
       <c r="G126" s="5" t="s">
-        <v>5494</v>
+        <v>5495</v>
       </c>
       <c r="H126" s="5"/>
       <c r="I126" s="5"/>
       <c r="J126" s="5"/>
       <c r="K126" s="4">
-        <f>SUM(L126:Q126)</f>
+        <f t="shared" si="3"/>
         <v>625</v>
       </c>
       <c r="L126" s="6">
@@ -57314,13 +57317,13 @@
         <v>535</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>5495</v>
+        <v>5496</v>
       </c>
       <c r="H127" s="5"/>
       <c r="I127" s="5"/>
       <c r="J127" s="5"/>
       <c r="K127" s="4">
-        <f>SUM(L127:Q127)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L127" s="6"/>
@@ -57350,13 +57353,13 @@
         <v>360</v>
       </c>
       <c r="G128" s="5" t="s">
-        <v>5496</v>
+        <v>5497</v>
       </c>
       <c r="H128" s="5"/>
       <c r="I128" s="5"/>
       <c r="J128" s="5"/>
       <c r="K128" s="4">
-        <f>SUM(L128:Q128)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L128" s="6"/>
@@ -57386,13 +57389,13 @@
         <v>561</v>
       </c>
       <c r="G129" s="5" t="s">
-        <v>5497</v>
+        <v>5498</v>
       </c>
       <c r="H129" s="5"/>
       <c r="I129" s="5"/>
       <c r="J129" s="5"/>
       <c r="K129" s="4">
-        <f>SUM(L129:Q129)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L129" s="6"/>
@@ -57407,7 +57410,7 @@
         <v>2535</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>5498</v>
+        <v>5499</v>
       </c>
       <c r="C130" s="4"/>
       <c r="D130" s="4" t="s">
@@ -57420,13 +57423,13 @@
         <v>535</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>5499</v>
+        <v>5500</v>
       </c>
       <c r="H130" s="5"/>
       <c r="I130" s="5"/>
       <c r="J130" s="5"/>
       <c r="K130" s="4">
-        <f>SUM(L130:Q130)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L130" s="6"/>
@@ -57441,7 +57444,7 @@
         <v>2535</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>5500</v>
+        <v>5501</v>
       </c>
       <c r="C131" s="4"/>
       <c r="D131" s="4" t="s">
@@ -57454,13 +57457,13 @@
         <v>76</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>5501</v>
+        <v>5502</v>
       </c>
       <c r="H131" s="5"/>
       <c r="I131" s="5"/>
       <c r="J131" s="5"/>
       <c r="K131" s="4">
-        <f>SUM(L131:Q131)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L131" s="6"/>
@@ -57475,7 +57478,7 @@
         <v>2535</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>5502</v>
+        <v>5503</v>
       </c>
       <c r="C132" s="4"/>
       <c r="D132" s="4" t="s">
@@ -57488,13 +57491,13 @@
         <v>55</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>5503</v>
+        <v>5504</v>
       </c>
       <c r="H132" s="5"/>
       <c r="I132" s="5"/>
       <c r="J132" s="5"/>
       <c r="K132" s="4">
-        <f>SUM(L132:Q132)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L132" s="6"/>
@@ -57509,7 +57512,7 @@
         <v>2535</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>5504</v>
+        <v>5505</v>
       </c>
       <c r="C133" s="4"/>
       <c r="D133" s="4" t="s">
@@ -57522,13 +57525,13 @@
         <v>69</v>
       </c>
       <c r="G133" s="5" t="s">
-        <v>5505</v>
+        <v>5506</v>
       </c>
       <c r="H133" s="5"/>
       <c r="I133" s="5"/>
       <c r="J133" s="5"/>
       <c r="K133" s="4">
-        <f>SUM(L133:Q133)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L133" s="6"/>
@@ -57543,7 +57546,7 @@
         <v>2535</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>5506</v>
+        <v>5507</v>
       </c>
       <c r="C134" s="4"/>
       <c r="D134" s="4" t="s">
@@ -57556,13 +57559,13 @@
         <v>30</v>
       </c>
       <c r="G134" s="5" t="s">
-        <v>5507</v>
+        <v>5508</v>
       </c>
       <c r="H134" s="5"/>
       <c r="I134" s="5"/>
       <c r="J134" s="5"/>
       <c r="K134" s="4">
-        <f>SUM(L134:Q134)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L134" s="6"/>
@@ -57577,7 +57580,7 @@
         <v>2556</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>5508</v>
+        <v>5509</v>
       </c>
       <c r="C135" s="4"/>
       <c r="D135" s="4" t="s">
@@ -57590,13 +57593,13 @@
         <v>841</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>5509</v>
+        <v>5510</v>
       </c>
       <c r="H135" s="5"/>
       <c r="I135" s="5"/>
       <c r="J135" s="5"/>
       <c r="K135" s="4">
-        <f>SUM(L135:Q135)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L135" s="6"/>
@@ -57611,7 +57614,7 @@
         <v>2561</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>5508</v>
+        <v>5509</v>
       </c>
       <c r="C136" s="4"/>
       <c r="D136" s="4" t="s">
@@ -57624,13 +57627,13 @@
         <v>841</v>
       </c>
       <c r="G136" s="5" t="s">
-        <v>5510</v>
+        <v>5511</v>
       </c>
       <c r="H136" s="5"/>
       <c r="I136" s="5"/>
       <c r="J136" s="5"/>
       <c r="K136" s="4">
-        <f>SUM(L136:Q136)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L136" s="6"/>
@@ -57660,7 +57663,7 @@
         <v>504</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>5511</v>
+        <v>5512</v>
       </c>
       <c r="H137" s="5"/>
       <c r="I137" s="5"/>
@@ -57678,7 +57681,7 @@
         <v>2576</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>5508</v>
+        <v>5509</v>
       </c>
       <c r="C138" s="4"/>
       <c r="D138" s="4" t="s">
@@ -57691,7 +57694,7 @@
         <v>841</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>5512</v>
+        <v>5513</v>
       </c>
       <c r="H138" s="5"/>
       <c r="I138" s="5"/>
@@ -57725,7 +57728,7 @@
       </c>
       <c r="F139" s="4"/>
       <c r="G139" s="5" t="s">
-        <v>5513</v>
+        <v>5514</v>
       </c>
       <c r="H139" s="5"/>
       <c r="I139" s="5"/>
@@ -57746,7 +57749,7 @@
         <v>2602</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>5514</v>
+        <v>5515</v>
       </c>
       <c r="C140" s="4"/>
       <c r="D140" s="4" t="s">
@@ -57759,7 +57762,7 @@
         <v>69</v>
       </c>
       <c r="G140" s="5" t="s">
-        <v>5515</v>
+        <v>5516</v>
       </c>
       <c r="H140" s="5"/>
       <c r="I140" s="5"/>
@@ -57795,7 +57798,7 @@
         <v>360</v>
       </c>
       <c r="G141" s="5" t="s">
-        <v>5516</v>
+        <v>5517</v>
       </c>
       <c r="H141" s="5"/>
       <c r="I141" s="5"/>
@@ -57831,7 +57834,7 @@
         <v>1101</v>
       </c>
       <c r="G142" s="5" t="s">
-        <v>5517</v>
+        <v>5518</v>
       </c>
       <c r="H142" s="5"/>
       <c r="I142" s="5"/>
@@ -57852,7 +57855,7 @@
         <v>2752</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>5518</v>
+        <v>5519</v>
       </c>
       <c r="C143" s="4"/>
       <c r="D143" s="4" t="s">
@@ -57865,13 +57868,13 @@
         <v>69</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>5519</v>
+        <v>5520</v>
       </c>
       <c r="H143" s="5"/>
       <c r="I143" s="5"/>
       <c r="J143" s="5"/>
       <c r="K143" s="4">
-        <f t="shared" ref="K143:K167" si="1">SUM(L143:Q143)</f>
+        <f t="shared" ref="K143:K169" si="4">SUM(L143:Q143)</f>
         <v>0</v>
       </c>
       <c r="L143" s="6"/>
@@ -57901,13 +57904,13 @@
         <v>504</v>
       </c>
       <c r="G144" s="5" t="s">
-        <v>5520</v>
+        <v>5521</v>
       </c>
       <c r="H144" s="5"/>
       <c r="I144" s="5"/>
       <c r="J144" s="5"/>
       <c r="K144" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L144" s="6"/>
@@ -57937,13 +57940,13 @@
         <v>248</v>
       </c>
       <c r="G145" s="5" t="s">
-        <v>5521</v>
+        <v>5522</v>
       </c>
       <c r="H145" s="5"/>
       <c r="I145" s="5"/>
       <c r="J145" s="5"/>
       <c r="K145" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L145" s="6"/>
@@ -57973,13 +57976,13 @@
         <v>31</v>
       </c>
       <c r="G146" s="5" t="s">
-        <v>5522</v>
+        <v>5523</v>
       </c>
       <c r="H146" s="5"/>
       <c r="I146" s="5"/>
       <c r="J146" s="5"/>
       <c r="K146" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L146" s="6"/>
@@ -58009,13 +58012,13 @@
         <v>360</v>
       </c>
       <c r="G147" s="5" t="s">
-        <v>5523</v>
+        <v>5524</v>
       </c>
       <c r="H147" s="5"/>
       <c r="I147" s="5"/>
       <c r="J147" s="5"/>
       <c r="K147" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L147" s="6"/>
@@ -58030,7 +58033,7 @@
         <v>2898</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>5524</v>
+        <v>5525</v>
       </c>
       <c r="C148" s="4"/>
       <c r="D148" s="4" t="s">
@@ -58041,13 +58044,13 @@
       </c>
       <c r="F148" s="4"/>
       <c r="G148" s="5" t="s">
-        <v>5525</v>
+        <v>5526</v>
       </c>
       <c r="H148" s="5"/>
       <c r="I148" s="5"/>
       <c r="J148" s="5"/>
       <c r="K148" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L148" s="6"/>
@@ -58062,7 +58065,7 @@
         <v>2898</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>5526</v>
+        <v>5527</v>
       </c>
       <c r="C149" s="4"/>
       <c r="D149" s="4" t="s">
@@ -58073,13 +58076,13 @@
       </c>
       <c r="F149" s="4"/>
       <c r="G149" s="5" t="s">
-        <v>5527</v>
+        <v>5528</v>
       </c>
       <c r="H149" s="5"/>
       <c r="I149" s="5"/>
       <c r="J149" s="5"/>
       <c r="K149" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L149" s="6"/>
@@ -58107,13 +58110,13 @@
       </c>
       <c r="F150" s="4"/>
       <c r="G150" s="5" t="s">
-        <v>5528</v>
+        <v>5529</v>
       </c>
       <c r="H150" s="5"/>
       <c r="I150" s="5"/>
       <c r="J150" s="5"/>
       <c r="K150" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L150" s="6"/>
@@ -58128,7 +58131,7 @@
         <v>2924</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>5529</v>
+        <v>5530</v>
       </c>
       <c r="C151" s="4"/>
       <c r="D151" s="4" t="s">
@@ -58141,13 +58144,13 @@
         <v>397</v>
       </c>
       <c r="G151" s="5" t="s">
-        <v>5530</v>
+        <v>5531</v>
       </c>
       <c r="H151" s="5"/>
       <c r="I151" s="5"/>
       <c r="J151" s="5"/>
       <c r="K151" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L151" s="6"/>
@@ -58175,13 +58178,13 @@
       </c>
       <c r="F152" s="4"/>
       <c r="G152" s="5" t="s">
-        <v>5531</v>
+        <v>5532</v>
       </c>
       <c r="H152" s="5"/>
       <c r="I152" s="5"/>
       <c r="J152" s="5"/>
       <c r="K152" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L152" s="6"/>
@@ -58196,7 +58199,7 @@
         <v>2924</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>5529</v>
+        <v>5530</v>
       </c>
       <c r="C153" s="4"/>
       <c r="D153" s="4" t="s">
@@ -58209,13 +58212,13 @@
         <v>55</v>
       </c>
       <c r="G153" s="5" t="s">
-        <v>5532</v>
+        <v>5533</v>
       </c>
       <c r="H153" s="5"/>
       <c r="I153" s="5"/>
       <c r="J153" s="5"/>
       <c r="K153" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L153" s="6"/>
@@ -58245,13 +58248,13 @@
         <v>360</v>
       </c>
       <c r="G154" s="5" t="s">
-        <v>5533</v>
+        <v>5534</v>
       </c>
       <c r="H154" s="5"/>
       <c r="I154" s="5"/>
       <c r="J154" s="5"/>
       <c r="K154" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L154" s="6"/>
@@ -58281,13 +58284,13 @@
         <v>561</v>
       </c>
       <c r="G155" s="5" t="s">
-        <v>5534</v>
+        <v>5535</v>
       </c>
       <c r="H155" s="5"/>
       <c r="I155" s="5"/>
       <c r="J155" s="5"/>
       <c r="K155" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L155" s="6"/>
@@ -58315,13 +58318,13 @@
       </c>
       <c r="F156" s="4"/>
       <c r="G156" s="5" t="s">
-        <v>5535</v>
+        <v>5536</v>
       </c>
       <c r="H156" s="5"/>
       <c r="I156" s="5"/>
       <c r="J156" s="5"/>
       <c r="K156" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L156" s="6"/>
@@ -58351,13 +58354,13 @@
         <v>561</v>
       </c>
       <c r="G157" s="5" t="s">
-        <v>5536</v>
+        <v>5537</v>
       </c>
       <c r="H157" s="5"/>
       <c r="I157" s="5"/>
       <c r="J157" s="5"/>
       <c r="K157" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L157" s="6"/>
@@ -58387,13 +58390,13 @@
         <v>561</v>
       </c>
       <c r="G158" s="5" t="s">
-        <v>5537</v>
+        <v>5538</v>
       </c>
       <c r="H158" s="5"/>
       <c r="I158" s="5"/>
       <c r="J158" s="5"/>
       <c r="K158" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L158" s="6"/>
@@ -58408,7 +58411,7 @@
         <v>3075</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>5538</v>
+        <v>5539</v>
       </c>
       <c r="C159" s="4"/>
       <c r="D159" s="4" t="s">
@@ -58421,13 +58424,13 @@
         <v>30</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>5539</v>
+        <v>5540</v>
       </c>
       <c r="H159" s="5"/>
       <c r="I159" s="5"/>
       <c r="J159" s="5"/>
       <c r="K159" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L159" s="6"/>
@@ -58442,7 +58445,7 @@
         <v>3075</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>5540</v>
+        <v>5541</v>
       </c>
       <c r="C160" s="4"/>
       <c r="D160" s="4" t="s">
@@ -58455,13 +58458,13 @@
         <v>30</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>5541</v>
+        <v>5542</v>
       </c>
       <c r="H160" s="5"/>
       <c r="I160" s="5"/>
       <c r="J160" s="5"/>
       <c r="K160" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L160" s="6"/>
@@ -58476,7 +58479,7 @@
         <v>3075</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>5542</v>
+        <v>5543</v>
       </c>
       <c r="C161" s="4"/>
       <c r="D161" s="4" t="s">
@@ -58489,13 +58492,13 @@
         <v>30</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>5543</v>
+        <v>5544</v>
       </c>
       <c r="H161" s="5"/>
       <c r="I161" s="5"/>
       <c r="J161" s="5"/>
       <c r="K161" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L161" s="6"/>
@@ -58510,7 +58513,7 @@
         <v>3081</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>5538</v>
+        <v>5539</v>
       </c>
       <c r="C162" s="4"/>
       <c r="D162" s="4" t="s">
@@ -58523,13 +58526,13 @@
         <v>30</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>5544</v>
+        <v>5545</v>
       </c>
       <c r="H162" s="5"/>
       <c r="I162" s="5"/>
       <c r="J162" s="5"/>
       <c r="K162" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L162" s="6"/>
@@ -58544,7 +58547,7 @@
         <v>3081</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>5540</v>
+        <v>5541</v>
       </c>
       <c r="C163" s="4"/>
       <c r="D163" s="4" t="s">
@@ -58557,13 +58560,13 @@
         <v>30</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>5545</v>
+        <v>5546</v>
       </c>
       <c r="H163" s="5"/>
       <c r="I163" s="5"/>
       <c r="J163" s="5"/>
       <c r="K163" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L163" s="6"/>
@@ -58578,7 +58581,7 @@
         <v>3081</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>5542</v>
+        <v>5543</v>
       </c>
       <c r="C164" s="4"/>
       <c r="D164" s="4" t="s">
@@ -58591,13 +58594,13 @@
         <v>30</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>5546</v>
+        <v>5547</v>
       </c>
       <c r="H164" s="5"/>
       <c r="I164" s="5"/>
       <c r="J164" s="5"/>
       <c r="K164" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L164" s="6"/>
@@ -58612,7 +58615,7 @@
         <v>3112</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>5518</v>
+        <v>5519</v>
       </c>
       <c r="C165" s="4"/>
       <c r="D165" s="4" t="s">
@@ -58625,13 +58628,13 @@
         <v>561</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>5547</v>
+        <v>5548</v>
       </c>
       <c r="H165" s="5"/>
       <c r="I165" s="5"/>
       <c r="J165" s="5"/>
       <c r="K165" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L165" s="6"/>
@@ -58646,7 +58649,7 @@
         <v>3117</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>5518</v>
+        <v>5519</v>
       </c>
       <c r="C166" s="4"/>
       <c r="D166" s="4" t="s">
@@ -58659,13 +58662,13 @@
         <v>561</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>5548</v>
+        <v>5549</v>
       </c>
       <c r="H166" s="5"/>
       <c r="I166" s="5"/>
       <c r="J166" s="5"/>
       <c r="K166" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L166" s="6"/>
@@ -58693,13 +58696,13 @@
       </c>
       <c r="F167" s="4"/>
       <c r="G167" s="5" t="s">
-        <v>5549</v>
+        <v>5550</v>
       </c>
       <c r="H167" s="5"/>
       <c r="I167" s="5"/>
       <c r="J167" s="5"/>
       <c r="K167" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L167" s="6"/>
@@ -58729,13 +58732,13 @@
         <v>55</v>
       </c>
       <c r="G168" s="5" t="s">
-        <v>5550</v>
+        <v>5551</v>
       </c>
       <c r="H168" s="5"/>
       <c r="I168" s="5"/>
       <c r="J168" s="5"/>
       <c r="K168" s="4">
-        <f>SUM(L168:Q168)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L168" s="6"/>
@@ -58765,13 +58768,13 @@
         <v>504</v>
       </c>
       <c r="G169" s="5" t="s">
-        <v>5551</v>
+        <v>5552</v>
       </c>
       <c r="H169" s="5"/>
       <c r="I169" s="5"/>
       <c r="J169" s="5"/>
       <c r="K169" s="4">
-        <f>SUM(L169:Q169)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L169" s="6"/>
@@ -58801,7 +58804,7 @@
         <v>561</v>
       </c>
       <c r="G170" s="5" t="s">
-        <v>5552</v>
+        <v>5553</v>
       </c>
       <c r="H170" s="5"/>
       <c r="I170" s="5"/>
@@ -58834,13 +58837,13 @@
         <v>69</v>
       </c>
       <c r="G171" s="5" t="s">
-        <v>5553</v>
+        <v>5554</v>
       </c>
       <c r="H171" s="5"/>
       <c r="I171" s="5"/>
       <c r="J171" s="5"/>
       <c r="K171" s="4">
-        <f>SUM(L171:Q171)</f>
+        <f t="shared" ref="K171:K182" si="5">SUM(L171:Q171)</f>
         <v>0</v>
       </c>
       <c r="L171" s="6"/>
@@ -58855,7 +58858,7 @@
         <v>3357</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>5554</v>
+        <v>5555</v>
       </c>
       <c r="C172" s="4"/>
       <c r="D172" s="4" t="s">
@@ -58866,13 +58869,13 @@
       </c>
       <c r="F172" s="4"/>
       <c r="G172" s="5" t="s">
-        <v>5555</v>
+        <v>5556</v>
       </c>
       <c r="H172" s="5"/>
       <c r="I172" s="5"/>
       <c r="J172" s="5"/>
       <c r="K172" s="4">
-        <f>SUM(L172:Q172)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L172" s="6"/>
@@ -58887,7 +58890,7 @@
         <v>3363</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>5554</v>
+        <v>5555</v>
       </c>
       <c r="C173" s="4"/>
       <c r="D173" s="4" t="s">
@@ -58900,13 +58903,13 @@
         <v>69</v>
       </c>
       <c r="G173" s="5" t="s">
-        <v>5556</v>
+        <v>5557</v>
       </c>
       <c r="H173" s="5"/>
       <c r="I173" s="5"/>
       <c r="J173" s="5"/>
       <c r="K173" s="4">
-        <f>SUM(L173:Q173)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L173" s="6"/>
@@ -58921,7 +58924,7 @@
         <v>3378</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>5554</v>
+        <v>5555</v>
       </c>
       <c r="C174" s="4"/>
       <c r="D174" s="4" t="s">
@@ -58934,13 +58937,13 @@
         <v>69</v>
       </c>
       <c r="G174" s="5" t="s">
-        <v>5557</v>
+        <v>5558</v>
       </c>
       <c r="H174" s="5"/>
       <c r="I174" s="5"/>
       <c r="J174" s="5"/>
       <c r="K174" s="4">
-        <f>SUM(L174:Q174)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L174" s="6"/>
@@ -58955,7 +58958,7 @@
         <v>3383</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>5558</v>
+        <v>5559</v>
       </c>
       <c r="C175" s="4"/>
       <c r="D175" s="4" t="s">
@@ -58968,13 +58971,13 @@
         <v>535</v>
       </c>
       <c r="G175" s="5" t="s">
-        <v>5559</v>
+        <v>5560</v>
       </c>
       <c r="H175" s="5"/>
       <c r="I175" s="5"/>
       <c r="J175" s="5"/>
       <c r="K175" s="4">
-        <f>SUM(L175:Q175)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L175" s="6"/>
@@ -58989,7 +58992,7 @@
         <v>3383</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>5560</v>
+        <v>5561</v>
       </c>
       <c r="C176" s="4"/>
       <c r="D176" s="4" t="s">
@@ -59002,13 +59005,13 @@
         <v>535</v>
       </c>
       <c r="G176" s="5" t="s">
-        <v>5561</v>
+        <v>5562</v>
       </c>
       <c r="H176" s="5"/>
       <c r="I176" s="5"/>
       <c r="J176" s="5"/>
       <c r="K176" s="4">
-        <f>SUM(L176:Q176)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L176" s="6"/>
@@ -59023,7 +59026,7 @@
         <v>3388</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>5562</v>
+        <v>5563</v>
       </c>
       <c r="C177" s="4"/>
       <c r="D177" s="4" t="s">
@@ -59036,13 +59039,13 @@
         <v>360</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>5563</v>
+        <v>5564</v>
       </c>
       <c r="H177" s="5"/>
       <c r="I177" s="5"/>
       <c r="J177" s="5"/>
       <c r="K177" s="4">
-        <f>SUM(L177:Q177)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L177" s="6"/>
@@ -59057,7 +59060,7 @@
         <v>3394</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>5564</v>
+        <v>5565</v>
       </c>
       <c r="C178" s="4"/>
       <c r="D178" s="4" t="s">
@@ -59070,13 +59073,13 @@
         <v>360</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>5565</v>
+        <v>5566</v>
       </c>
       <c r="H178" s="5"/>
       <c r="I178" s="5"/>
       <c r="J178" s="5"/>
       <c r="K178" s="4">
-        <f>SUM(L178:Q178)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L178" s="6"/>
@@ -59106,13 +59109,13 @@
         <v>360</v>
       </c>
       <c r="G179" s="5" t="s">
-        <v>5566</v>
+        <v>5567</v>
       </c>
       <c r="H179" s="5"/>
       <c r="I179" s="5"/>
       <c r="J179" s="5"/>
       <c r="K179" s="4">
-        <f>SUM(L179:Q179)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L179" s="6"/>
@@ -59142,13 +59145,13 @@
         <v>397</v>
       </c>
       <c r="G180" s="5" t="s">
-        <v>5567</v>
+        <v>5568</v>
       </c>
       <c r="H180" s="5"/>
       <c r="I180" s="5"/>
       <c r="J180" s="5"/>
       <c r="K180" s="4">
-        <f>SUM(L180:Q180)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L180" s="6"/>
@@ -59178,13 +59181,13 @@
         <v>1101</v>
       </c>
       <c r="G181" s="5" t="s">
-        <v>5568</v>
+        <v>5569</v>
       </c>
       <c r="H181" s="5"/>
       <c r="I181" s="5"/>
       <c r="J181" s="5"/>
       <c r="K181" s="4">
-        <f>SUM(L181:Q181)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L181" s="6"/>
@@ -59199,7 +59202,7 @@
         <v>3452</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>5569</v>
+        <v>5570</v>
       </c>
       <c r="C182" s="4"/>
       <c r="D182" s="4" t="s">
@@ -59212,13 +59215,13 @@
         <v>1101</v>
       </c>
       <c r="G182" s="5" t="s">
-        <v>5570</v>
+        <v>5571</v>
       </c>
       <c r="H182" s="5"/>
       <c r="I182" s="5"/>
       <c r="J182" s="5"/>
       <c r="K182" s="4">
-        <f>SUM(L182:Q182)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L182" s="6"/>
@@ -59233,7 +59236,7 @@
         <v>3514</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>5518</v>
+        <v>5519</v>
       </c>
       <c r="C183" s="4"/>
       <c r="D183" s="4" t="s">
@@ -59246,13 +59249,13 @@
         <v>135</v>
       </c>
       <c r="G183" s="5" t="s">
-        <v>5571</v>
+        <v>5572</v>
       </c>
       <c r="H183" s="5"/>
       <c r="I183" s="5"/>
       <c r="J183" s="5"/>
       <c r="K183" s="4">
-        <f t="shared" ref="K183:K221" si="2">SUM(L183:Q183)</f>
+        <f t="shared" ref="K183:K221" si="6">SUM(L183:Q183)</f>
         <v>0</v>
       </c>
       <c r="L183" s="6"/>
@@ -59282,13 +59285,13 @@
         <v>135</v>
       </c>
       <c r="G184" s="5" t="s">
-        <v>5572</v>
+        <v>5573</v>
       </c>
       <c r="H184" s="5"/>
       <c r="I184" s="5"/>
       <c r="J184" s="5"/>
       <c r="K184" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L184" s="6"/>
@@ -59316,13 +59319,13 @@
       </c>
       <c r="F185" s="4"/>
       <c r="G185" s="5" t="s">
-        <v>5573</v>
+        <v>5574</v>
       </c>
       <c r="H185" s="5"/>
       <c r="I185" s="5"/>
       <c r="J185" s="5"/>
       <c r="K185" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L185" s="6"/>
@@ -59337,7 +59340,7 @@
         <v>3569</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>5518</v>
+        <v>5519</v>
       </c>
       <c r="C186" s="4"/>
       <c r="D186" s="4" t="s">
@@ -59348,13 +59351,13 @@
       </c>
       <c r="F186" s="4"/>
       <c r="G186" s="5" t="s">
-        <v>5574</v>
+        <v>5575</v>
       </c>
       <c r="H186" s="5"/>
       <c r="I186" s="5"/>
       <c r="J186" s="5"/>
       <c r="K186" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L186" s="6"/>
@@ -59382,13 +59385,13 @@
       </c>
       <c r="F187" s="4"/>
       <c r="G187" s="5" t="s">
-        <v>5575</v>
+        <v>5576</v>
       </c>
       <c r="H187" s="5"/>
       <c r="I187" s="5"/>
       <c r="J187" s="5"/>
       <c r="K187" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L187" s="6"/>
@@ -59403,7 +59406,7 @@
         <v>3584</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>5576</v>
+        <v>5577</v>
       </c>
       <c r="C188" s="4"/>
       <c r="D188" s="4" t="s">
@@ -59416,13 +59419,13 @@
         <v>561</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>5577</v>
+        <v>5578</v>
       </c>
       <c r="H188" s="5"/>
       <c r="I188" s="5"/>
       <c r="J188" s="5"/>
       <c r="K188" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L188" s="6"/>
@@ -59452,13 +59455,13 @@
         <v>397</v>
       </c>
       <c r="G189" s="5" t="s">
-        <v>5578</v>
+        <v>5579</v>
       </c>
       <c r="H189" s="5"/>
       <c r="I189" s="5"/>
       <c r="J189" s="5"/>
       <c r="K189" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L189" s="6"/>
@@ -59488,13 +59491,13 @@
         <v>360</v>
       </c>
       <c r="G190" s="5" t="s">
-        <v>5579</v>
+        <v>5580</v>
       </c>
       <c r="H190" s="5"/>
       <c r="I190" s="5"/>
       <c r="J190" s="5"/>
       <c r="K190" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L190" s="6"/>
@@ -59524,13 +59527,13 @@
         <v>841</v>
       </c>
       <c r="G191" s="5" t="s">
-        <v>5580</v>
+        <v>5581</v>
       </c>
       <c r="H191" s="5"/>
       <c r="I191" s="5"/>
       <c r="J191" s="5"/>
       <c r="K191" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L191" s="6"/>
@@ -59560,13 +59563,13 @@
         <v>69</v>
       </c>
       <c r="G192" s="5" t="s">
-        <v>5581</v>
+        <v>5582</v>
       </c>
       <c r="H192" s="5"/>
       <c r="I192" s="5"/>
       <c r="J192" s="5"/>
       <c r="K192" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L192" s="6"/>
@@ -59596,13 +59599,13 @@
         <v>841</v>
       </c>
       <c r="G193" s="5" t="s">
-        <v>5582</v>
+        <v>5583</v>
       </c>
       <c r="H193" s="5"/>
       <c r="I193" s="5"/>
       <c r="J193" s="5"/>
       <c r="K193" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L193" s="6"/>
@@ -59632,13 +59635,13 @@
         <v>841</v>
       </c>
       <c r="G194" s="5" t="s">
-        <v>5583</v>
+        <v>5584</v>
       </c>
       <c r="H194" s="5"/>
       <c r="I194" s="5"/>
       <c r="J194" s="5"/>
       <c r="K194" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L194" s="6"/>
@@ -59668,13 +59671,13 @@
         <v>463</v>
       </c>
       <c r="G195" s="5" t="s">
-        <v>5584</v>
+        <v>5585</v>
       </c>
       <c r="H195" s="5"/>
       <c r="I195" s="5"/>
       <c r="J195" s="5"/>
       <c r="K195" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L195" s="6"/>
@@ -59689,7 +59692,7 @@
         <v>3778</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>5585</v>
+        <v>5586</v>
       </c>
       <c r="C196" s="4"/>
       <c r="D196" s="4" t="s">
@@ -59702,13 +59705,13 @@
         <v>207</v>
       </c>
       <c r="G196" s="5" t="s">
-        <v>5586</v>
+        <v>5587</v>
       </c>
       <c r="H196" s="5"/>
       <c r="I196" s="5"/>
       <c r="J196" s="5"/>
       <c r="K196" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L196" s="6"/>
@@ -59723,7 +59726,7 @@
         <v>3778</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>5587</v>
+        <v>5588</v>
       </c>
       <c r="C197" s="4"/>
       <c r="D197" s="4" t="s">
@@ -59736,13 +59739,13 @@
         <v>207</v>
       </c>
       <c r="G197" s="5" t="s">
-        <v>5588</v>
+        <v>5589</v>
       </c>
       <c r="H197" s="5"/>
       <c r="I197" s="5"/>
       <c r="J197" s="5"/>
       <c r="K197" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L197" s="6"/>
@@ -59772,13 +59775,13 @@
         <v>207</v>
       </c>
       <c r="G198" s="5" t="s">
-        <v>5589</v>
+        <v>5590</v>
       </c>
       <c r="H198" s="5"/>
       <c r="I198" s="5"/>
       <c r="J198" s="5"/>
       <c r="K198" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L198" s="6"/>
@@ -59800,13 +59803,13 @@
       <c r="E199" s="4"/>
       <c r="F199" s="4"/>
       <c r="G199" s="5" t="s">
-        <v>5590</v>
+        <v>5591</v>
       </c>
       <c r="H199" s="5"/>
       <c r="I199" s="5"/>
       <c r="J199" s="5"/>
       <c r="K199" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L199" s="6"/>
@@ -59836,13 +59839,13 @@
         <v>248</v>
       </c>
       <c r="G200" s="5" t="s">
-        <v>5591</v>
+        <v>5592</v>
       </c>
       <c r="H200" s="5"/>
       <c r="I200" s="5"/>
       <c r="J200" s="5"/>
       <c r="K200" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L200" s="6"/>
@@ -59857,7 +59860,7 @@
         <v>3789</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>5592</v>
+        <v>5593</v>
       </c>
       <c r="C201" s="4"/>
       <c r="D201" s="4" t="s">
@@ -59870,13 +59873,13 @@
         <v>1101</v>
       </c>
       <c r="G201" s="5" t="s">
-        <v>5593</v>
+        <v>5594</v>
       </c>
       <c r="H201" s="5"/>
       <c r="I201" s="5"/>
       <c r="J201" s="5"/>
       <c r="K201" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L201" s="6"/>
@@ -59906,13 +59909,13 @@
         <v>360</v>
       </c>
       <c r="G202" s="5" t="s">
-        <v>5594</v>
+        <v>5595</v>
       </c>
       <c r="H202" s="5"/>
       <c r="I202" s="5"/>
       <c r="J202" s="5"/>
       <c r="K202" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L202" s="6"/>
@@ -59942,13 +59945,13 @@
         <v>535</v>
       </c>
       <c r="G203" s="5" t="s">
-        <v>5595</v>
+        <v>5596</v>
       </c>
       <c r="H203" s="5"/>
       <c r="I203" s="5"/>
       <c r="J203" s="5"/>
       <c r="K203" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L203" s="6"/>
@@ -59963,7 +59966,7 @@
         <v>3895</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>5596</v>
+        <v>5597</v>
       </c>
       <c r="C204" s="4"/>
       <c r="D204" s="4"/>
@@ -59974,13 +59977,13 @@
         <v>69</v>
       </c>
       <c r="G204" s="5" t="s">
-        <v>5597</v>
+        <v>5598</v>
       </c>
       <c r="H204" s="5"/>
       <c r="I204" s="5"/>
       <c r="J204" s="5"/>
       <c r="K204" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L204" s="6"/>
@@ -59995,7 +59998,7 @@
         <v>3895</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>5598</v>
+        <v>5599</v>
       </c>
       <c r="C205" s="4"/>
       <c r="D205" s="4"/>
@@ -60006,13 +60009,13 @@
         <v>69</v>
       </c>
       <c r="G205" s="5" t="s">
-        <v>5599</v>
+        <v>5600</v>
       </c>
       <c r="H205" s="5"/>
       <c r="I205" s="5"/>
       <c r="J205" s="5"/>
       <c r="K205" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L205" s="6"/>
@@ -60027,7 +60030,7 @@
         <v>3895</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>5600</v>
+        <v>5601</v>
       </c>
       <c r="C206" s="4"/>
       <c r="D206" s="4"/>
@@ -60038,13 +60041,13 @@
         <v>69</v>
       </c>
       <c r="G206" s="5" t="s">
-        <v>5601</v>
+        <v>5602</v>
       </c>
       <c r="H206" s="5"/>
       <c r="I206" s="5"/>
       <c r="J206" s="5"/>
       <c r="K206" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L206" s="6"/>
@@ -60059,7 +60062,7 @@
         <v>3916</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>5602</v>
+        <v>5603</v>
       </c>
       <c r="C207" s="4"/>
       <c r="D207" s="4"/>
@@ -60068,13 +60071,13 @@
       </c>
       <c r="F207" s="4"/>
       <c r="G207" s="5" t="s">
-        <v>5603</v>
+        <v>5604</v>
       </c>
       <c r="H207" s="5"/>
       <c r="I207" s="5"/>
       <c r="J207" s="5"/>
       <c r="K207" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L207" s="6"/>
@@ -60089,7 +60092,7 @@
         <v>3916</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>5604</v>
+        <v>5605</v>
       </c>
       <c r="C208" s="4"/>
       <c r="D208" s="4"/>
@@ -60098,13 +60101,13 @@
       </c>
       <c r="F208" s="4"/>
       <c r="G208" s="5" t="s">
-        <v>5605</v>
+        <v>5606</v>
       </c>
       <c r="H208" s="5"/>
       <c r="I208" s="5"/>
       <c r="J208" s="5"/>
       <c r="K208" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L208" s="6"/>
@@ -60119,7 +60122,7 @@
         <v>3922</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>5606</v>
+        <v>5607</v>
       </c>
       <c r="C209" s="4"/>
       <c r="D209" s="4"/>
@@ -60128,13 +60131,13 @@
       </c>
       <c r="F209" s="4"/>
       <c r="G209" s="5" t="s">
-        <v>5607</v>
+        <v>5608</v>
       </c>
       <c r="H209" s="5"/>
       <c r="I209" s="5"/>
       <c r="J209" s="5"/>
       <c r="K209" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L209" s="6"/>
@@ -60164,13 +60167,13 @@
         <v>504</v>
       </c>
       <c r="G210" s="5" t="s">
-        <v>5608</v>
+        <v>5609</v>
       </c>
       <c r="H210" s="5"/>
       <c r="I210" s="5"/>
       <c r="J210" s="5"/>
       <c r="K210" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L210" s="6"/>
@@ -60185,7 +60188,7 @@
         <v>4063</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>5609</v>
+        <v>5610</v>
       </c>
       <c r="C211" s="4"/>
       <c r="D211" s="4" t="s">
@@ -60198,13 +60201,13 @@
         <v>69</v>
       </c>
       <c r="G211" s="5" t="s">
-        <v>5610</v>
+        <v>5611</v>
       </c>
       <c r="H211" s="5"/>
       <c r="I211" s="5"/>
       <c r="J211" s="5"/>
       <c r="K211" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L211" s="6"/>
@@ -60234,13 +60237,13 @@
         <v>841</v>
       </c>
       <c r="G212" s="5" t="s">
-        <v>5611</v>
+        <v>5612</v>
       </c>
       <c r="H212" s="5"/>
       <c r="I212" s="5"/>
       <c r="J212" s="5"/>
       <c r="K212" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L212" s="6"/>
@@ -60255,7 +60258,7 @@
         <v>4195</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>5612</v>
+        <v>5613</v>
       </c>
       <c r="C213" s="4"/>
       <c r="D213" s="4" t="s">
@@ -60268,13 +60271,13 @@
         <v>504</v>
       </c>
       <c r="G213" s="5" t="s">
-        <v>5613</v>
+        <v>5614</v>
       </c>
       <c r="H213" s="5"/>
       <c r="I213" s="5"/>
       <c r="J213" s="5"/>
       <c r="K213" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L213" s="6"/>
@@ -60289,7 +60292,7 @@
         <v>4195</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>5614</v>
+        <v>5615</v>
       </c>
       <c r="C214" s="4"/>
       <c r="D214" s="4" t="s">
@@ -60302,13 +60305,13 @@
         <v>561</v>
       </c>
       <c r="G214" s="5" t="s">
-        <v>5615</v>
+        <v>5616</v>
       </c>
       <c r="H214" s="5"/>
       <c r="I214" s="5"/>
       <c r="J214" s="5"/>
       <c r="K214" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L214" s="6"/>
@@ -60323,7 +60326,7 @@
         <v>4195</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>5616</v>
+        <v>5617</v>
       </c>
       <c r="C215" s="4"/>
       <c r="D215" s="4" t="s">
@@ -60336,13 +60339,13 @@
         <v>841</v>
       </c>
       <c r="G215" s="5" t="s">
-        <v>5617</v>
+        <v>5618</v>
       </c>
       <c r="H215" s="5"/>
       <c r="I215" s="5"/>
       <c r="J215" s="5"/>
       <c r="K215" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L215" s="6"/>
@@ -60372,13 +60375,13 @@
         <v>248</v>
       </c>
       <c r="G216" s="5" t="s">
-        <v>5618</v>
+        <v>5619</v>
       </c>
       <c r="H216" s="5"/>
       <c r="I216" s="5"/>
       <c r="J216" s="5"/>
       <c r="K216" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L216" s="6"/>
@@ -60406,13 +60409,13 @@
       </c>
       <c r="F217" s="4"/>
       <c r="G217" s="5" t="s">
-        <v>5619</v>
+        <v>5620</v>
       </c>
       <c r="H217" s="5"/>
       <c r="I217" s="5"/>
       <c r="J217" s="5"/>
       <c r="K217" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L217" s="6"/>
@@ -60440,13 +60443,13 @@
       </c>
       <c r="F218" s="4"/>
       <c r="G218" s="5" t="s">
-        <v>5620</v>
+        <v>5621</v>
       </c>
       <c r="H218" s="5"/>
       <c r="I218" s="5"/>
       <c r="J218" s="5"/>
       <c r="K218" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L218" s="6"/>
@@ -60474,13 +60477,13 @@
       </c>
       <c r="F219" s="4"/>
       <c r="G219" s="5" t="s">
-        <v>5621</v>
+        <v>5622</v>
       </c>
       <c r="H219" s="5"/>
       <c r="I219" s="5"/>
       <c r="J219" s="5"/>
       <c r="K219" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L219" s="6"/>
@@ -60508,13 +60511,13 @@
       </c>
       <c r="F220" s="4"/>
       <c r="G220" s="5" t="s">
-        <v>5622</v>
+        <v>5623</v>
       </c>
       <c r="H220" s="5"/>
       <c r="I220" s="5"/>
       <c r="J220" s="5"/>
       <c r="K220" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L220" s="6"/>
@@ -60542,13 +60545,13 @@
       </c>
       <c r="F221" s="4"/>
       <c r="G221" s="5" t="s">
-        <v>5623</v>
+        <v>5624</v>
       </c>
       <c r="H221" s="5"/>
       <c r="I221" s="5"/>
       <c r="J221" s="5"/>
       <c r="K221" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L221" s="6"/>
@@ -60578,13 +60581,13 @@
         <v>504</v>
       </c>
       <c r="G222" s="5" t="s">
-        <v>5624</v>
+        <v>5625</v>
       </c>
       <c r="H222" s="5"/>
       <c r="I222" s="5"/>
       <c r="J222" s="5"/>
       <c r="K222" s="4">
-        <f t="shared" ref="K218:K234" si="3">SUM(L222:Q222)</f>
+        <f t="shared" ref="K218:K234" si="7">SUM(L222:Q222)</f>
         <v>0</v>
       </c>
       <c r="L222" s="6"/>
@@ -60614,13 +60617,13 @@
         <v>397</v>
       </c>
       <c r="G223" s="5" t="s">
-        <v>5625</v>
+        <v>5626</v>
       </c>
       <c r="H223" s="5"/>
       <c r="I223" s="5"/>
       <c r="J223" s="5"/>
       <c r="K223" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L223" s="6"/>
@@ -60650,13 +60653,13 @@
         <v>463</v>
       </c>
       <c r="G224" s="5" t="s">
-        <v>5626</v>
+        <v>5627</v>
       </c>
       <c r="H224" s="5"/>
       <c r="I224" s="5"/>
       <c r="J224" s="5"/>
       <c r="K224" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L224" s="6"/>
@@ -60686,13 +60689,13 @@
         <v>55</v>
       </c>
       <c r="G225" s="5" t="s">
-        <v>5627</v>
+        <v>5628</v>
       </c>
       <c r="H225" s="5"/>
       <c r="I225" s="5"/>
       <c r="J225" s="5"/>
       <c r="K225" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L225" s="6"/>
@@ -60722,13 +60725,13 @@
         <v>841</v>
       </c>
       <c r="G226" s="5" t="s">
-        <v>5628</v>
+        <v>5629</v>
       </c>
       <c r="H226" s="5"/>
       <c r="I226" s="5"/>
       <c r="J226" s="5"/>
       <c r="K226" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L226" s="6"/>
@@ -60758,13 +60761,13 @@
         <v>841</v>
       </c>
       <c r="G227" s="5" t="s">
-        <v>5629</v>
+        <v>5630</v>
       </c>
       <c r="H227" s="5"/>
       <c r="I227" s="5"/>
       <c r="J227" s="5"/>
       <c r="K227" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L227" s="6"/>
@@ -60792,13 +60795,13 @@
       </c>
       <c r="F228" s="4"/>
       <c r="G228" s="5" t="s">
-        <v>5630</v>
+        <v>5631</v>
       </c>
       <c r="H228" s="5"/>
       <c r="I228" s="5"/>
       <c r="J228" s="5"/>
       <c r="K228" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L228" s="6"/>
@@ -60813,7 +60816,7 @@
         <v>4440</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>5631</v>
+        <v>5632</v>
       </c>
       <c r="C229" s="4"/>
       <c r="D229" s="4" t="s">
@@ -60826,13 +60829,13 @@
         <v>31</v>
       </c>
       <c r="G229" s="5" t="s">
-        <v>5632</v>
+        <v>5633</v>
       </c>
       <c r="H229" s="5"/>
       <c r="I229" s="5"/>
       <c r="J229" s="5"/>
       <c r="K229" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L229" s="6"/>
@@ -60862,13 +60865,13 @@
         <v>31</v>
       </c>
       <c r="G230" s="5" t="s">
-        <v>5633</v>
+        <v>5634</v>
       </c>
       <c r="H230" s="5"/>
       <c r="I230" s="5"/>
       <c r="J230" s="5"/>
       <c r="K230" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L230" s="6"/>
@@ -60898,13 +60901,13 @@
         <v>96</v>
       </c>
       <c r="G231" s="5" t="s">
-        <v>5634</v>
+        <v>5635</v>
       </c>
       <c r="H231" s="5"/>
       <c r="I231" s="5"/>
       <c r="J231" s="5"/>
       <c r="K231" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L231" s="6"/>
@@ -60934,13 +60937,13 @@
         <v>248</v>
       </c>
       <c r="G232" s="5" t="s">
-        <v>5635</v>
+        <v>5636</v>
       </c>
       <c r="H232" s="5"/>
       <c r="I232" s="5"/>
       <c r="J232" s="5"/>
       <c r="K232" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L232" s="6"/>
@@ -60970,13 +60973,13 @@
         <v>248</v>
       </c>
       <c r="G233" s="5" t="s">
-        <v>5636</v>
+        <v>5637</v>
       </c>
       <c r="H233" s="5"/>
       <c r="I233" s="5"/>
       <c r="J233" s="5"/>
       <c r="K233" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L233" s="6"/>
@@ -61004,13 +61007,13 @@
       </c>
       <c r="F234" s="4"/>
       <c r="G234" s="5" t="s">
-        <v>5637</v>
+        <v>5638</v>
       </c>
       <c r="H234" s="5"/>
       <c r="I234" s="5"/>
       <c r="J234" s="5"/>
       <c r="K234" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L234" s="6"/>
@@ -61038,7 +61041,7 @@
       </c>
       <c r="F235" s="4"/>
       <c r="G235" s="5" t="s">
-        <v>5638</v>
+        <v>5639</v>
       </c>
       <c r="H235" s="5"/>
       <c r="I235" s="5"/>
@@ -61056,7 +61059,7 @@
         <v>4571</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>5639</v>
+        <v>5640</v>
       </c>
       <c r="C236" s="4"/>
       <c r="D236" s="4" t="s">
@@ -61067,13 +61070,13 @@
       </c>
       <c r="F236" s="4"/>
       <c r="G236" s="5" t="s">
-        <v>5640</v>
+        <v>5641</v>
       </c>
       <c r="H236" s="5"/>
       <c r="I236" s="5"/>
       <c r="J236" s="5"/>
       <c r="K236" s="4">
-        <f t="shared" ref="K236:K266" si="4">SUM(L236:Q236)</f>
+        <f t="shared" ref="K236:K266" si="8">SUM(L236:Q236)</f>
         <v>0</v>
       </c>
       <c r="L236" s="6"/>
@@ -61088,7 +61091,7 @@
         <v>4577</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>5518</v>
+        <v>5519</v>
       </c>
       <c r="C237" s="4"/>
       <c r="D237" s="4" t="s">
@@ -61101,13 +61104,13 @@
         <v>135</v>
       </c>
       <c r="G237" s="5" t="s">
-        <v>5641</v>
+        <v>5642</v>
       </c>
       <c r="H237" s="5"/>
       <c r="I237" s="5"/>
       <c r="J237" s="5"/>
       <c r="K237" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L237" s="6"/>
@@ -61122,7 +61125,7 @@
         <v>4582</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>5642</v>
+        <v>5643</v>
       </c>
       <c r="C238" s="4"/>
       <c r="D238" s="4" t="s">
@@ -61135,13 +61138,13 @@
         <v>1101</v>
       </c>
       <c r="G238" s="5" t="s">
-        <v>5643</v>
+        <v>5644</v>
       </c>
       <c r="H238" s="5"/>
       <c r="I238" s="5"/>
       <c r="J238" s="5"/>
       <c r="K238" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L238" s="6"/>
@@ -61169,13 +61172,13 @@
       </c>
       <c r="F239" s="4"/>
       <c r="G239" s="5" t="s">
-        <v>5644</v>
+        <v>5645</v>
       </c>
       <c r="H239" s="5"/>
       <c r="I239" s="5"/>
       <c r="J239" s="5"/>
       <c r="K239" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L239" s="6"/>
@@ -61205,13 +61208,13 @@
         <v>841</v>
       </c>
       <c r="G240" s="5" t="s">
-        <v>5645</v>
+        <v>5646</v>
       </c>
       <c r="H240" s="5"/>
       <c r="I240" s="5"/>
       <c r="J240" s="5"/>
       <c r="K240" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L240" s="6"/>
@@ -61226,7 +61229,7 @@
         <v>4638</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>5646</v>
+        <v>5647</v>
       </c>
       <c r="C241" s="4"/>
       <c r="D241" s="4" t="s">
@@ -61239,13 +61242,13 @@
         <v>504</v>
       </c>
       <c r="G241" s="5" t="s">
-        <v>5647</v>
+        <v>5648</v>
       </c>
       <c r="H241" s="5"/>
       <c r="I241" s="5"/>
       <c r="J241" s="5"/>
       <c r="K241" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L241" s="6"/>
@@ -61260,7 +61263,7 @@
         <v>4644</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>5648</v>
+        <v>5649</v>
       </c>
       <c r="C242" s="4"/>
       <c r="D242" s="4" t="s">
@@ -61273,13 +61276,13 @@
         <v>504</v>
       </c>
       <c r="G242" s="5" t="s">
-        <v>5649</v>
+        <v>5650</v>
       </c>
       <c r="H242" s="5"/>
       <c r="I242" s="5"/>
       <c r="J242" s="5"/>
       <c r="K242" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L242" s="6"/>
@@ -61309,13 +61312,13 @@
         <v>841</v>
       </c>
       <c r="G243" s="5" t="s">
-        <v>5650</v>
+        <v>5651</v>
       </c>
       <c r="H243" s="5"/>
       <c r="I243" s="5"/>
       <c r="J243" s="5"/>
       <c r="K243" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L243" s="6"/>
@@ -61330,7 +61333,7 @@
         <v>4659</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>5651</v>
+        <v>5652</v>
       </c>
       <c r="C244" s="4"/>
       <c r="D244" s="4" t="s">
@@ -61343,13 +61346,13 @@
         <v>76</v>
       </c>
       <c r="G244" s="5" t="s">
-        <v>5652</v>
+        <v>5653</v>
       </c>
       <c r="H244" s="5"/>
       <c r="I244" s="5"/>
       <c r="J244" s="5"/>
       <c r="K244" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L244" s="6"/>
@@ -61379,13 +61382,13 @@
         <v>1101</v>
       </c>
       <c r="G245" s="5" t="s">
-        <v>5653</v>
+        <v>5654</v>
       </c>
       <c r="H245" s="5"/>
       <c r="I245" s="5"/>
       <c r="J245" s="5"/>
       <c r="K245" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L245" s="6"/>
@@ -61415,13 +61418,13 @@
         <v>76</v>
       </c>
       <c r="G246" s="5" t="s">
-        <v>5654</v>
+        <v>5655</v>
       </c>
       <c r="H246" s="5"/>
       <c r="I246" s="5"/>
       <c r="J246" s="5"/>
       <c r="K246" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L246" s="6"/>
@@ -61436,7 +61439,7 @@
         <v>4690</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>5655</v>
+        <v>5656</v>
       </c>
       <c r="C247" s="4"/>
       <c r="D247" s="4" t="s">
@@ -61449,13 +61452,13 @@
         <v>535</v>
       </c>
       <c r="G247" s="5" t="s">
-        <v>5656</v>
+        <v>5657</v>
       </c>
       <c r="H247" s="5"/>
       <c r="I247" s="5"/>
       <c r="J247" s="5"/>
       <c r="K247" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L247" s="6"/>
@@ -61470,7 +61473,7 @@
         <v>4690</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>5657</v>
+        <v>5658</v>
       </c>
       <c r="C248" s="4"/>
       <c r="D248" s="4" t="s">
@@ -61483,13 +61486,13 @@
         <v>561</v>
       </c>
       <c r="G248" s="5" t="s">
-        <v>5658</v>
+        <v>5659</v>
       </c>
       <c r="H248" s="5"/>
       <c r="I248" s="5"/>
       <c r="J248" s="5"/>
       <c r="K248" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L248" s="6"/>
@@ -61504,7 +61507,7 @@
         <v>4705</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>5659</v>
+        <v>5660</v>
       </c>
       <c r="C249" s="4"/>
       <c r="D249" s="4" t="s">
@@ -61517,13 +61520,13 @@
         <v>135</v>
       </c>
       <c r="G249" s="5" t="s">
-        <v>5660</v>
+        <v>5661</v>
       </c>
       <c r="H249" s="5"/>
       <c r="I249" s="5"/>
       <c r="J249" s="5"/>
       <c r="K249" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L249" s="6"/>
@@ -61538,7 +61541,7 @@
         <v>4710</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>5518</v>
+        <v>5519</v>
       </c>
       <c r="C250" s="4"/>
       <c r="D250" s="4" t="s">
@@ -61551,13 +61554,13 @@
         <v>561</v>
       </c>
       <c r="G250" s="5" t="s">
-        <v>5661</v>
+        <v>5662</v>
       </c>
       <c r="H250" s="5"/>
       <c r="I250" s="5"/>
       <c r="J250" s="5"/>
       <c r="K250" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L250" s="6"/>
@@ -61572,7 +61575,7 @@
         <v>4725</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>5554</v>
+        <v>5555</v>
       </c>
       <c r="C251" s="4"/>
       <c r="D251" s="4" t="s">
@@ -61585,13 +61588,13 @@
         <v>69</v>
       </c>
       <c r="G251" s="5" t="s">
-        <v>5662</v>
+        <v>5663</v>
       </c>
       <c r="H251" s="5"/>
       <c r="I251" s="5"/>
       <c r="J251" s="5"/>
       <c r="K251" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L251" s="6"/>
@@ -61606,7 +61609,7 @@
         <v>4780</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>5518</v>
+        <v>5519</v>
       </c>
       <c r="C252" s="4"/>
       <c r="D252" s="4" t="s">
@@ -61617,13 +61620,13 @@
       </c>
       <c r="F252" s="4"/>
       <c r="G252" s="5" t="s">
-        <v>5663</v>
+        <v>5664</v>
       </c>
       <c r="H252" s="5"/>
       <c r="I252" s="5"/>
       <c r="J252" s="5"/>
       <c r="K252" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L252" s="6"/>
@@ -61638,7 +61641,7 @@
         <v>4825</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>5664</v>
+        <v>5665</v>
       </c>
       <c r="C253" s="4"/>
       <c r="D253" s="4" t="s">
@@ -61649,13 +61652,13 @@
       </c>
       <c r="F253" s="4"/>
       <c r="G253" s="5" t="s">
-        <v>5665</v>
+        <v>5666</v>
       </c>
       <c r="H253" s="5"/>
       <c r="I253" s="5"/>
       <c r="J253" s="5"/>
       <c r="K253" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L253" s="6"/>
@@ -61670,7 +61673,7 @@
         <v>4856</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>5666</v>
+        <v>5667</v>
       </c>
       <c r="C254" s="4"/>
       <c r="D254" s="4" t="s">
@@ -61683,13 +61686,13 @@
         <v>69</v>
       </c>
       <c r="G254" s="5" t="s">
-        <v>5667</v>
+        <v>5668</v>
       </c>
       <c r="H254" s="5"/>
       <c r="I254" s="5"/>
       <c r="J254" s="5"/>
       <c r="K254" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L254" s="6"/>
@@ -61704,7 +61707,7 @@
         <v>4856</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>5668</v>
+        <v>5669</v>
       </c>
       <c r="C255" s="4"/>
       <c r="D255" s="4" t="s">
@@ -61717,13 +61720,13 @@
         <v>69</v>
       </c>
       <c r="G255" s="5" t="s">
-        <v>5669</v>
+        <v>5670</v>
       </c>
       <c r="H255" s="5"/>
       <c r="I255" s="5"/>
       <c r="J255" s="5"/>
       <c r="K255" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L255" s="6"/>
@@ -61738,7 +61741,7 @@
         <v>4856</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>5670</v>
+        <v>5671</v>
       </c>
       <c r="C256" s="4"/>
       <c r="D256" s="4" t="s">
@@ -61751,13 +61754,13 @@
         <v>69</v>
       </c>
       <c r="G256" s="5" t="s">
-        <v>5671</v>
+        <v>5672</v>
       </c>
       <c r="H256" s="5"/>
       <c r="I256" s="5"/>
       <c r="J256" s="5"/>
       <c r="K256" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L256" s="6"/>
@@ -61787,7 +61790,7 @@
         <v>55</v>
       </c>
       <c r="G257" s="5" t="s">
-        <v>5672</v>
+        <v>5673</v>
       </c>
       <c r="H257" s="5"/>
       <c r="I257" s="5"/>
@@ -61805,7 +61808,7 @@
         <v>5022</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>5673</v>
+        <v>5674</v>
       </c>
       <c r="C258" s="4"/>
       <c r="D258" s="4" t="s">
@@ -61816,7 +61819,7 @@
       </c>
       <c r="F258" s="4"/>
       <c r="G258" s="5" t="s">
-        <v>5674</v>
+        <v>5675</v>
       </c>
       <c r="H258" s="5"/>
       <c r="I258" s="5"/>
@@ -61852,7 +61855,7 @@
         <v>31</v>
       </c>
       <c r="G259" s="5" t="s">
-        <v>5675</v>
+        <v>5676</v>
       </c>
       <c r="H259" s="5"/>
       <c r="I259" s="5"/>
@@ -61870,7 +61873,7 @@
         <v>5093</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>5676</v>
+        <v>5677</v>
       </c>
       <c r="C260" s="4"/>
       <c r="D260" s="4" t="s">
@@ -61883,7 +61886,7 @@
         <v>76</v>
       </c>
       <c r="G260" s="5" t="s">
-        <v>5677</v>
+        <v>5678</v>
       </c>
       <c r="H260" s="5"/>
       <c r="I260" s="5"/>
@@ -61904,7 +61907,7 @@
         <v>5093</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>5678</v>
+        <v>5679</v>
       </c>
       <c r="C261" s="4"/>
       <c r="D261" s="4" t="s">
@@ -61917,7 +61920,7 @@
         <v>76</v>
       </c>
       <c r="G261" s="5" t="s">
-        <v>5679</v>
+        <v>5680</v>
       </c>
       <c r="H261" s="5"/>
       <c r="I261" s="5"/>
@@ -61953,7 +61956,7 @@
         <v>76</v>
       </c>
       <c r="G262" s="5" t="s">
-        <v>5680</v>
+        <v>5681</v>
       </c>
       <c r="H262" s="5"/>
       <c r="I262" s="5"/>
@@ -61971,7 +61974,7 @@
         <v>5114</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>5681</v>
+        <v>5682</v>
       </c>
       <c r="C263" s="4"/>
       <c r="D263" s="4" t="s">
@@ -61982,7 +61985,7 @@
       </c>
       <c r="F263" s="4"/>
       <c r="G263" s="5" t="s">
-        <v>5682</v>
+        <v>5683</v>
       </c>
       <c r="H263" s="5"/>
       <c r="I263" s="5"/>
@@ -62018,7 +62021,7 @@
         <v>535</v>
       </c>
       <c r="G264" s="5" t="s">
-        <v>5683</v>
+        <v>5684</v>
       </c>
       <c r="H264" s="5"/>
       <c r="I264" s="5"/>
@@ -62036,7 +62039,7 @@
         <v>5201</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>5684</v>
+        <v>5685</v>
       </c>
       <c r="C265" s="4"/>
       <c r="D265" s="4" t="s">
@@ -62047,13 +62050,13 @@
       </c>
       <c r="F265" s="4"/>
       <c r="G265" s="5" t="s">
-        <v>5685</v>
+        <v>5686</v>
       </c>
       <c r="H265" s="5"/>
       <c r="I265" s="5"/>
       <c r="J265" s="5"/>
       <c r="K265" s="4">
-        <f>SUM(L265:Q265)</f>
+        <f t="shared" ref="K265:K270" si="9">SUM(L265:Q265)</f>
         <v>0</v>
       </c>
       <c r="L265" s="6"/>
@@ -62068,7 +62071,7 @@
         <v>5292</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>5686</v>
+        <v>5687</v>
       </c>
       <c r="C266" s="4"/>
       <c r="D266" s="4" t="s">
@@ -62081,13 +62084,13 @@
         <v>76</v>
       </c>
       <c r="G266" s="5" t="s">
-        <v>5687</v>
+        <v>5688</v>
       </c>
       <c r="H266" s="5"/>
       <c r="I266" s="5"/>
       <c r="J266" s="5"/>
       <c r="K266" s="4">
-        <f>SUM(L266:Q266)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L266" s="6"/>
@@ -62102,7 +62105,7 @@
         <v>5292</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>5688</v>
+        <v>5689</v>
       </c>
       <c r="C267" s="4"/>
       <c r="D267" s="4" t="s">
@@ -62115,13 +62118,13 @@
         <v>55</v>
       </c>
       <c r="G267" s="5" t="s">
-        <v>5689</v>
+        <v>5690</v>
       </c>
       <c r="H267" s="5"/>
       <c r="I267" s="5"/>
       <c r="J267" s="5"/>
       <c r="K267" s="4">
-        <f>SUM(L267:Q267)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L267" s="6"/>
@@ -62136,7 +62139,7 @@
         <v>5292</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>5690</v>
+        <v>5691</v>
       </c>
       <c r="C268" s="4"/>
       <c r="D268" s="4" t="s">
@@ -62149,13 +62152,13 @@
         <v>463</v>
       </c>
       <c r="G268" s="5" t="s">
-        <v>5691</v>
+        <v>5692</v>
       </c>
       <c r="H268" s="5"/>
       <c r="I268" s="5"/>
       <c r="J268" s="5"/>
       <c r="K268" s="4">
-        <f>SUM(L268:Q268)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L268" s="6"/>
@@ -62170,7 +62173,7 @@
         <v>5328</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>5692</v>
+        <v>5693</v>
       </c>
       <c r="C269" s="4"/>
       <c r="D269" s="4" t="s">
@@ -62181,13 +62184,13 @@
       </c>
       <c r="F269" s="4"/>
       <c r="G269" s="5" t="s">
-        <v>5693</v>
+        <v>5694</v>
       </c>
       <c r="H269" s="5"/>
       <c r="I269" s="5"/>
       <c r="J269" s="5"/>
       <c r="K269" s="4">
-        <f>SUM(L269:Q269)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L269" s="6"/>
@@ -62202,7 +62205,7 @@
         <v>5328</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>5694</v>
+        <v>5695</v>
       </c>
       <c r="C270" s="4"/>
       <c r="D270" s="4" t="s">
@@ -62213,13 +62216,13 @@
       </c>
       <c r="F270" s="4"/>
       <c r="G270" s="5" t="s">
-        <v>5695</v>
+        <v>5696</v>
       </c>
       <c r="H270" s="5"/>
       <c r="I270" s="5"/>
       <c r="J270" s="5"/>
       <c r="K270" s="4">
-        <f>SUM(L270:Q270)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L270" s="6"/>
@@ -62916,13 +62919,13 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>5696</v>
+        <v>5697</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>5697</v>
+        <v>5698</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>5698</v>
+        <v>5699</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -62930,13 +62933,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>5699</v>
+        <v>5700</v>
       </c>
       <c r="C2" t="s">
-        <v>5700</v>
+        <v>5701</v>
       </c>
       <c r="D2" t="s">
-        <v>5700</v>
+        <v>5701</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -62944,13 +62947,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>5702</v>
+      </c>
+      <c r="C3" t="s">
         <v>5701</v>
       </c>
-      <c r="C3" t="s">
-        <v>5700</v>
-      </c>
       <c r="D3" t="s">
-        <v>5700</v>
+        <v>5701</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -62958,13 +62961,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>5702</v>
+        <v>5703</v>
       </c>
       <c r="C4" t="s">
-        <v>5700</v>
+        <v>5701</v>
       </c>
       <c r="D4" t="s">
-        <v>5700</v>
+        <v>5701</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -62972,13 +62975,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>5703</v>
+        <v>5704</v>
       </c>
       <c r="C5" t="s">
-        <v>5700</v>
+        <v>5701</v>
       </c>
       <c r="D5" t="s">
-        <v>5700</v>
+        <v>5701</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -62986,13 +62989,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>5704</v>
+        <v>5705</v>
       </c>
       <c r="C6" t="s">
-        <v>5700</v>
+        <v>5701</v>
       </c>
       <c r="D6" t="s">
-        <v>5700</v>
+        <v>5701</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -63000,13 +63003,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>5705</v>
+        <v>5706</v>
       </c>
       <c r="C7" t="s">
-        <v>5700</v>
+        <v>5701</v>
       </c>
       <c r="D7" t="s">
-        <v>5700</v>
+        <v>5701</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -63017,10 +63020,10 @@
         <v>5357</v>
       </c>
       <c r="C8" t="s">
-        <v>5700</v>
+        <v>5701</v>
       </c>
       <c r="D8" t="s">
-        <v>5700</v>
+        <v>5701</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -63031,10 +63034,10 @@
         <v>5374</v>
       </c>
       <c r="C9" t="s">
-        <v>5700</v>
+        <v>5701</v>
       </c>
       <c r="D9" t="s">
-        <v>5700</v>
+        <v>5701</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -63042,13 +63045,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>5706</v>
+        <v>5707</v>
       </c>
       <c r="C10" t="s">
-        <v>5700</v>
+        <v>5701</v>
       </c>
       <c r="D10" t="s">
-        <v>5700</v>
+        <v>5701</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -63056,13 +63059,13 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>5707</v>
+        <v>5708</v>
       </c>
       <c r="C11" t="s">
-        <v>5700</v>
+        <v>5701</v>
       </c>
       <c r="D11" t="s">
-        <v>5700</v>
+        <v>5701</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -63073,10 +63076,10 @@
         <v>5379</v>
       </c>
       <c r="C12" t="s">
-        <v>5700</v>
+        <v>5701</v>
       </c>
       <c r="D12" t="s">
-        <v>5700</v>
+        <v>5701</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -63087,10 +63090,10 @@
         <v>5410</v>
       </c>
       <c r="C13" t="s">
-        <v>5700</v>
+        <v>5701</v>
       </c>
       <c r="D13" t="s">
-        <v>5700</v>
+        <v>5701</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -63098,13 +63101,13 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>5708</v>
+        <v>5709</v>
       </c>
       <c r="C14" t="s">
-        <v>5700</v>
+        <v>5701</v>
       </c>
       <c r="D14" t="s">
-        <v>5700</v>
+        <v>5701</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -63112,13 +63115,13 @@
         <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>5709</v>
+        <v>5710</v>
       </c>
       <c r="C15" t="s">
-        <v>5700</v>
+        <v>5701</v>
       </c>
       <c r="D15" t="s">
-        <v>5700</v>
+        <v>5701</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -63126,10 +63129,10 @@
         <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C16" t="s">
-        <v>5711</v>
+        <v>5712</v>
       </c>
       <c r="D16" t="s">
         <v>865</v>
@@ -63140,10 +63143,10 @@
         <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C17" t="s">
-        <v>5712</v>
+        <v>5713</v>
       </c>
       <c r="D17" t="s">
         <v>872</v>
@@ -63154,10 +63157,10 @@
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C18" t="s">
-        <v>5713</v>
+        <v>5714</v>
       </c>
       <c r="D18" t="s">
         <v>877</v>
@@ -63168,10 +63171,10 @@
         <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C19" t="s">
-        <v>5714</v>
+        <v>5715</v>
       </c>
       <c r="D19" t="s">
         <v>2633</v>
@@ -63182,10 +63185,10 @@
         <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C20" t="s">
-        <v>5715</v>
+        <v>5716</v>
       </c>
       <c r="D20" t="s">
         <v>2640</v>
@@ -63196,10 +63199,10 @@
         <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C21" t="s">
-        <v>5716</v>
+        <v>5717</v>
       </c>
       <c r="D21" t="s">
         <v>2645</v>
@@ -63210,10 +63213,10 @@
         <v>9</v>
       </c>
       <c r="B22" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C22" t="s">
-        <v>5717</v>
+        <v>5718</v>
       </c>
       <c r="D22" t="s">
         <v>898</v>
@@ -63224,10 +63227,10 @@
         <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C23" t="s">
-        <v>5718</v>
+        <v>5719</v>
       </c>
       <c r="D23" t="s">
         <v>905</v>
@@ -63238,10 +63241,10 @@
         <v>9</v>
       </c>
       <c r="B24" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C24" t="s">
-        <v>5719</v>
+        <v>5720</v>
       </c>
       <c r="D24" t="s">
         <v>910</v>
@@ -63252,10 +63255,10 @@
         <v>9</v>
       </c>
       <c r="B25" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C25" t="s">
-        <v>5720</v>
+        <v>5721</v>
       </c>
       <c r="D25" t="s">
         <v>3472</v>
@@ -63266,10 +63269,10 @@
         <v>9</v>
       </c>
       <c r="B26" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C26" t="s">
-        <v>5721</v>
+        <v>5722</v>
       </c>
       <c r="D26" t="s">
         <v>3479</v>
@@ -63280,10 +63283,10 @@
         <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C27" t="s">
-        <v>5722</v>
+        <v>5723</v>
       </c>
       <c r="D27" t="s">
         <v>3485</v>
@@ -63294,10 +63297,10 @@
         <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C28" t="s">
-        <v>5723</v>
+        <v>5724</v>
       </c>
       <c r="D28" t="s">
         <v>3458</v>
@@ -63308,10 +63311,10 @@
         <v>9</v>
       </c>
       <c r="B29" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C29" t="s">
-        <v>5724</v>
+        <v>5725</v>
       </c>
       <c r="D29" t="s">
         <v>3467</v>
@@ -63322,10 +63325,10 @@
         <v>9</v>
       </c>
       <c r="B30" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C30" t="s">
-        <v>5725</v>
+        <v>5726</v>
       </c>
       <c r="D30" t="s">
         <v>3492</v>
@@ -63336,10 +63339,10 @@
         <v>9</v>
       </c>
       <c r="B31" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C31" t="s">
-        <v>5726</v>
+        <v>5727</v>
       </c>
       <c r="D31" t="s">
         <v>3499</v>
@@ -63350,10 +63353,10 @@
         <v>9</v>
       </c>
       <c r="B32" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C32" t="s">
-        <v>5727</v>
+        <v>5728</v>
       </c>
       <c r="D32" t="s">
         <v>3504</v>
@@ -63364,10 +63367,10 @@
         <v>9</v>
       </c>
       <c r="B33" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C33" t="s">
-        <v>5728</v>
+        <v>5729</v>
       </c>
       <c r="D33" t="s">
         <v>108</v>
@@ -63378,10 +63381,10 @@
         <v>9</v>
       </c>
       <c r="B34" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C34" t="s">
-        <v>5729</v>
+        <v>5730</v>
       </c>
       <c r="D34" t="s">
         <v>116</v>
@@ -63392,10 +63395,10 @@
         <v>9</v>
       </c>
       <c r="B35" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C35" t="s">
-        <v>5730</v>
+        <v>5731</v>
       </c>
       <c r="D35" t="s">
         <v>123</v>
@@ -63406,10 +63409,10 @@
         <v>9</v>
       </c>
       <c r="B36" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C36" t="s">
-        <v>5731</v>
+        <v>5732</v>
       </c>
       <c r="D36" t="s">
         <v>130</v>
@@ -63420,10 +63423,10 @@
         <v>9</v>
       </c>
       <c r="B37" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C37" t="s">
-        <v>5732</v>
+        <v>5733</v>
       </c>
       <c r="D37" t="s">
         <v>140</v>
@@ -63434,10 +63437,10 @@
         <v>9</v>
       </c>
       <c r="B38" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C38" t="s">
-        <v>5733</v>
+        <v>5734</v>
       </c>
       <c r="D38" t="s">
         <v>146</v>
@@ -63448,10 +63451,10 @@
         <v>9</v>
       </c>
       <c r="B39" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C39" t="s">
-        <v>5734</v>
+        <v>5735</v>
       </c>
       <c r="D39" t="s">
         <v>1006</v>
@@ -63462,10 +63465,10 @@
         <v>9</v>
       </c>
       <c r="B40" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C40" t="s">
-        <v>5735</v>
+        <v>5736</v>
       </c>
       <c r="D40" t="s">
         <v>1011</v>
@@ -63476,10 +63479,10 @@
         <v>9</v>
       </c>
       <c r="B41" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C41" t="s">
-        <v>5736</v>
+        <v>5737</v>
       </c>
       <c r="D41" t="s">
         <v>1016</v>
@@ -63490,10 +63493,10 @@
         <v>9</v>
       </c>
       <c r="B42" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C42" t="s">
-        <v>5737</v>
+        <v>5738</v>
       </c>
       <c r="D42" t="s">
         <v>2667</v>
@@ -63504,10 +63507,10 @@
         <v>9</v>
       </c>
       <c r="B43" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C43" t="s">
-        <v>5738</v>
+        <v>5739</v>
       </c>
       <c r="D43" t="s">
         <v>2672</v>
@@ -63518,10 +63521,10 @@
         <v>9</v>
       </c>
       <c r="B44" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C44" t="s">
-        <v>5739</v>
+        <v>5740</v>
       </c>
       <c r="D44" t="s">
         <v>2155</v>
@@ -63532,10 +63535,10 @@
         <v>9</v>
       </c>
       <c r="B45" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C45" t="s">
-        <v>5740</v>
+        <v>5741</v>
       </c>
       <c r="D45" t="s">
         <v>1694</v>
@@ -63546,10 +63549,10 @@
         <v>9</v>
       </c>
       <c r="B46" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C46" t="s">
-        <v>5741</v>
+        <v>5742</v>
       </c>
       <c r="D46" t="s">
         <v>2161</v>
@@ -63560,10 +63563,10 @@
         <v>9</v>
       </c>
       <c r="B47" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C47" t="s">
-        <v>5742</v>
+        <v>5743</v>
       </c>
       <c r="D47" t="s">
         <v>743</v>
@@ -63574,10 +63577,10 @@
         <v>9</v>
       </c>
       <c r="B48" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C48" t="s">
-        <v>5743</v>
+        <v>5744</v>
       </c>
       <c r="D48" t="s">
         <v>748</v>
@@ -63588,10 +63591,10 @@
         <v>9</v>
       </c>
       <c r="B49" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C49" t="s">
-        <v>5744</v>
+        <v>5745</v>
       </c>
       <c r="D49" t="s">
         <v>3622</v>
@@ -63602,10 +63605,10 @@
         <v>9</v>
       </c>
       <c r="B50" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C50" t="s">
-        <v>5745</v>
+        <v>5746</v>
       </c>
       <c r="D50" t="s">
         <v>3627</v>
@@ -63616,10 +63619,10 @@
         <v>9</v>
       </c>
       <c r="B51" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C51" t="s">
-        <v>5746</v>
+        <v>5747</v>
       </c>
       <c r="D51" t="s">
         <v>698</v>
@@ -63630,10 +63633,10 @@
         <v>9</v>
       </c>
       <c r="B52" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C52" t="s">
-        <v>5747</v>
+        <v>5748</v>
       </c>
       <c r="D52" t="s">
         <v>703</v>
@@ -63644,10 +63647,10 @@
         <v>9</v>
       </c>
       <c r="B53" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C53" t="s">
-        <v>5748</v>
+        <v>5749</v>
       </c>
       <c r="D53" t="s">
         <v>3519</v>
@@ -63658,10 +63661,10 @@
         <v>9</v>
       </c>
       <c r="B54" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C54" t="s">
-        <v>5749</v>
+        <v>5750</v>
       </c>
       <c r="D54" t="s">
         <v>3524</v>
@@ -63672,10 +63675,10 @@
         <v>9</v>
       </c>
       <c r="B55" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C55" t="s">
-        <v>5750</v>
+        <v>5751</v>
       </c>
       <c r="D55" t="s">
         <v>3529</v>
@@ -63686,10 +63689,10 @@
         <v>9</v>
       </c>
       <c r="B56" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C56" t="s">
-        <v>5751</v>
+        <v>5752</v>
       </c>
       <c r="D56" t="s">
         <v>3534</v>
@@ -63700,10 +63703,10 @@
         <v>9</v>
       </c>
       <c r="B57" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C57" t="s">
-        <v>5752</v>
+        <v>5753</v>
       </c>
       <c r="D57" t="s">
         <v>3539</v>
@@ -63714,10 +63717,10 @@
         <v>9</v>
       </c>
       <c r="B58" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C58" t="s">
-        <v>5753</v>
+        <v>5754</v>
       </c>
       <c r="D58" t="s">
         <v>3564</v>
@@ -63728,10 +63731,10 @@
         <v>9</v>
       </c>
       <c r="B59" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C59" t="s">
-        <v>5754</v>
+        <v>5755</v>
       </c>
       <c r="D59" t="s">
         <v>3569</v>
@@ -63742,10 +63745,10 @@
         <v>9</v>
       </c>
       <c r="B60" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C60" t="s">
-        <v>5755</v>
+        <v>5756</v>
       </c>
       <c r="D60" t="s">
         <v>3509</v>
@@ -63756,10 +63759,10 @@
         <v>9</v>
       </c>
       <c r="B61" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C61" t="s">
-        <v>5756</v>
+        <v>5757</v>
       </c>
       <c r="D61" t="s">
         <v>3514</v>
@@ -63770,10 +63773,10 @@
         <v>9</v>
       </c>
       <c r="B62" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C62" t="s">
-        <v>5757</v>
+        <v>5758</v>
       </c>
       <c r="D62" t="s">
         <v>3544</v>
@@ -63784,10 +63787,10 @@
         <v>9</v>
       </c>
       <c r="B63" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C63" t="s">
-        <v>5758</v>
+        <v>5759</v>
       </c>
       <c r="D63" t="s">
         <v>3553</v>
@@ -63798,10 +63801,10 @@
         <v>9</v>
       </c>
       <c r="B64" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C64" t="s">
-        <v>5759</v>
+        <v>5760</v>
       </c>
       <c r="D64" t="s">
         <v>2990</v>
@@ -63812,10 +63815,10 @@
         <v>9</v>
       </c>
       <c r="B65" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C65" t="s">
-        <v>5760</v>
+        <v>5761</v>
       </c>
       <c r="D65" t="s">
         <v>2995</v>
@@ -63826,10 +63829,10 @@
         <v>9</v>
       </c>
       <c r="B66" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C66" t="s">
-        <v>5761</v>
+        <v>5762</v>
       </c>
       <c r="D66" t="s">
         <v>3697</v>
@@ -63840,10 +63843,10 @@
         <v>9</v>
       </c>
       <c r="B67" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C67" t="s">
-        <v>5762</v>
+        <v>5763</v>
       </c>
       <c r="D67" t="s">
         <v>195</v>
@@ -63854,10 +63857,10 @@
         <v>9</v>
       </c>
       <c r="B68" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C68" t="s">
-        <v>5763</v>
+        <v>5764</v>
       </c>
       <c r="D68" t="s">
         <v>185</v>
@@ -63868,10 +63871,10 @@
         <v>9</v>
       </c>
       <c r="B69" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C69" t="s">
-        <v>5764</v>
+        <v>5765</v>
       </c>
       <c r="D69" t="s">
         <v>196</v>
@@ -63882,10 +63885,10 @@
         <v>9</v>
       </c>
       <c r="B70" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C70" t="s">
-        <v>5765</v>
+        <v>5766</v>
       </c>
       <c r="D70" t="s">
         <v>253</v>
@@ -63896,10 +63899,10 @@
         <v>9</v>
       </c>
       <c r="B71" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C71" t="s">
-        <v>5766</v>
+        <v>5767</v>
       </c>
       <c r="D71" t="s">
         <v>244</v>
@@ -63910,10 +63913,10 @@
         <v>9</v>
       </c>
       <c r="B72" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C72" t="s">
-        <v>5767</v>
+        <v>5768</v>
       </c>
       <c r="D72" t="s">
         <v>254</v>
@@ -63924,10 +63927,10 @@
         <v>9</v>
       </c>
       <c r="B73" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C73" t="s">
-        <v>5768</v>
+        <v>5769</v>
       </c>
       <c r="D73" t="s">
         <v>945</v>
@@ -63938,10 +63941,10 @@
         <v>9</v>
       </c>
       <c r="B74" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C74" t="s">
-        <v>5769</v>
+        <v>5770</v>
       </c>
       <c r="D74" t="s">
         <v>950</v>
@@ -63952,10 +63955,10 @@
         <v>9</v>
       </c>
       <c r="B75" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C75" t="s">
-        <v>5770</v>
+        <v>5771</v>
       </c>
       <c r="D75" t="s">
         <v>171</v>
@@ -63966,10 +63969,10 @@
         <v>9</v>
       </c>
       <c r="B76" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C76" t="s">
-        <v>5771</v>
+        <v>5772</v>
       </c>
       <c r="D76" t="s">
         <v>179</v>
@@ -63980,10 +63983,10 @@
         <v>9</v>
       </c>
       <c r="B77" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C77" t="s">
-        <v>5772</v>
+        <v>5773</v>
       </c>
       <c r="D77" t="s">
         <v>392</v>
@@ -63994,10 +63997,10 @@
         <v>9</v>
       </c>
       <c r="B78" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C78" t="s">
-        <v>5773</v>
+        <v>5774</v>
       </c>
       <c r="D78" t="s">
         <v>401</v>
@@ -64008,10 +64011,10 @@
         <v>9</v>
       </c>
       <c r="B79" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C79" t="s">
-        <v>5774</v>
+        <v>5775</v>
       </c>
       <c r="D79" t="s">
         <v>406</v>
@@ -64022,10 +64025,10 @@
         <v>9</v>
       </c>
       <c r="B80" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C80" t="s">
-        <v>5775</v>
+        <v>5776</v>
       </c>
       <c r="D80" t="s">
         <v>557</v>
@@ -64036,10 +64039,10 @@
         <v>9</v>
       </c>
       <c r="B81" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C81" t="s">
-        <v>5776</v>
+        <v>5777</v>
       </c>
       <c r="D81" t="s">
         <v>563</v>
@@ -64050,10 +64053,10 @@
         <v>9</v>
       </c>
       <c r="B82" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C82" t="s">
-        <v>5777</v>
+        <v>5778</v>
       </c>
       <c r="D82" t="s">
         <v>568</v>
@@ -64064,10 +64067,10 @@
         <v>9</v>
       </c>
       <c r="B83" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C83" t="s">
-        <v>5778</v>
+        <v>5779</v>
       </c>
       <c r="D83" t="s">
         <v>2863</v>
@@ -64078,10 +64081,10 @@
         <v>9</v>
       </c>
       <c r="B84" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C84" t="s">
-        <v>5779</v>
+        <v>5780</v>
       </c>
       <c r="D84" t="s">
         <v>2868</v>
@@ -64092,10 +64095,10 @@
         <v>9</v>
       </c>
       <c r="B85" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C85" t="s">
-        <v>5780</v>
+        <v>5781</v>
       </c>
       <c r="D85" t="s">
         <v>2873</v>
@@ -64106,10 +64109,10 @@
         <v>9</v>
       </c>
       <c r="B86" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C86" t="s">
-        <v>5781</v>
+        <v>5782</v>
       </c>
       <c r="D86" t="s">
         <v>3574</v>
@@ -64120,10 +64123,10 @@
         <v>9</v>
       </c>
       <c r="B87" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C87" t="s">
-        <v>5782</v>
+        <v>5783</v>
       </c>
       <c r="D87" t="s">
         <v>3579</v>
@@ -64134,10 +64137,10 @@
         <v>9</v>
       </c>
       <c r="B88" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C88" t="s">
-        <v>5783</v>
+        <v>5784</v>
       </c>
       <c r="D88" t="s">
         <v>3584</v>
@@ -64148,10 +64151,10 @@
         <v>9</v>
       </c>
       <c r="B89" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C89" t="s">
-        <v>5784</v>
+        <v>5785</v>
       </c>
       <c r="D89" t="s">
         <v>430</v>
@@ -64162,10 +64165,10 @@
         <v>9</v>
       </c>
       <c r="B90" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C90" t="s">
-        <v>5785</v>
+        <v>5786</v>
       </c>
       <c r="D90" t="s">
         <v>437</v>
@@ -64176,10 +64179,10 @@
         <v>9</v>
       </c>
       <c r="B91" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C91" t="s">
-        <v>5786</v>
+        <v>5787</v>
       </c>
       <c r="D91" t="s">
         <v>443</v>
@@ -64190,10 +64193,10 @@
         <v>9</v>
       </c>
       <c r="B92" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C92" t="s">
-        <v>5787</v>
+        <v>5788</v>
       </c>
       <c r="D92" t="s">
         <v>2702</v>
@@ -64204,10 +64207,10 @@
         <v>9</v>
       </c>
       <c r="B93" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C93" t="s">
-        <v>5788</v>
+        <v>5789</v>
       </c>
       <c r="D93" t="s">
         <v>2707</v>
@@ -64218,10 +64221,10 @@
         <v>9</v>
       </c>
       <c r="B94" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C94" t="s">
-        <v>5789</v>
+        <v>5790</v>
       </c>
       <c r="D94" t="s">
         <v>2712</v>
@@ -64232,10 +64235,10 @@
         <v>9</v>
       </c>
       <c r="B95" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C95" t="s">
-        <v>5790</v>
+        <v>5791</v>
       </c>
       <c r="D95" t="s">
         <v>2717</v>
@@ -64246,10 +64249,10 @@
         <v>9</v>
       </c>
       <c r="B96" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C96" t="s">
-        <v>5791</v>
+        <v>5792</v>
       </c>
       <c r="D96" t="s">
         <v>2722</v>
@@ -64260,10 +64263,10 @@
         <v>9</v>
       </c>
       <c r="B97" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C97" t="s">
-        <v>5792</v>
+        <v>5793</v>
       </c>
       <c r="D97" t="s">
         <v>2727</v>
@@ -64274,10 +64277,10 @@
         <v>9</v>
       </c>
       <c r="B98" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C98" t="s">
-        <v>5793</v>
+        <v>5794</v>
       </c>
       <c r="D98" t="s">
         <v>1654</v>
@@ -64288,10 +64291,10 @@
         <v>9</v>
       </c>
       <c r="B99" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C99" t="s">
-        <v>5794</v>
+        <v>5795</v>
       </c>
       <c r="D99" t="s">
         <v>1659</v>
@@ -64302,10 +64305,10 @@
         <v>9</v>
       </c>
       <c r="B100" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C100" t="s">
-        <v>5795</v>
+        <v>5796</v>
       </c>
       <c r="D100" t="s">
         <v>1664</v>
@@ -64316,10 +64319,10 @@
         <v>9</v>
       </c>
       <c r="B101" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C101" t="s">
-        <v>5796</v>
+        <v>5797</v>
       </c>
       <c r="D101" t="s">
         <v>1669</v>
@@ -64330,10 +64333,10 @@
         <v>9</v>
       </c>
       <c r="B102" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C102" t="s">
-        <v>5797</v>
+        <v>5798</v>
       </c>
       <c r="D102" t="s">
         <v>1517</v>
@@ -64344,10 +64347,10 @@
         <v>9</v>
       </c>
       <c r="B103" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C103" t="s">
-        <v>5798</v>
+        <v>5799</v>
       </c>
       <c r="D103" t="s">
         <v>1522</v>
@@ -64358,10 +64361,10 @@
         <v>9</v>
       </c>
       <c r="B104" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C104" t="s">
-        <v>5799</v>
+        <v>5800</v>
       </c>
       <c r="D104" t="s">
         <v>1527</v>
@@ -64372,10 +64375,10 @@
         <v>9</v>
       </c>
       <c r="B105" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C105" t="s">
-        <v>5800</v>
+        <v>5801</v>
       </c>
       <c r="D105" t="s">
         <v>2514</v>
@@ -64386,10 +64389,10 @@
         <v>9</v>
       </c>
       <c r="B106" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C106" t="s">
-        <v>5801</v>
+        <v>5802</v>
       </c>
       <c r="D106" t="s">
         <v>1255</v>
@@ -64400,10 +64403,10 @@
         <v>9</v>
       </c>
       <c r="B107" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C107" t="s">
-        <v>5802</v>
+        <v>5803</v>
       </c>
       <c r="D107" t="s">
         <v>1260</v>
@@ -64414,10 +64417,10 @@
         <v>9</v>
       </c>
       <c r="B108" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C108" t="s">
-        <v>5803</v>
+        <v>5804</v>
       </c>
       <c r="D108" t="s">
         <v>1784</v>
@@ -64428,10 +64431,10 @@
         <v>9</v>
       </c>
       <c r="B109" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C109" t="s">
-        <v>5804</v>
+        <v>5805</v>
       </c>
       <c r="D109" t="s">
         <v>1789</v>
@@ -64442,10 +64445,10 @@
         <v>9</v>
       </c>
       <c r="B110" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C110" t="s">
-        <v>5805</v>
+        <v>5806</v>
       </c>
       <c r="D110" t="s">
         <v>2803</v>
@@ -64456,10 +64459,10 @@
         <v>9</v>
       </c>
       <c r="B111" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C111" t="s">
-        <v>5806</v>
+        <v>5807</v>
       </c>
       <c r="D111" t="s">
         <v>3590</v>
@@ -64470,10 +64473,10 @@
         <v>9</v>
       </c>
       <c r="B112" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C112" t="s">
-        <v>5807</v>
+        <v>5808</v>
       </c>
       <c r="D112" t="s">
         <v>3595</v>
@@ -64484,10 +64487,10 @@
         <v>9</v>
       </c>
       <c r="B113" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C113" t="s">
-        <v>5808</v>
+        <v>5809</v>
       </c>
       <c r="D113" t="s">
         <v>3601</v>
@@ -64498,10 +64501,10 @@
         <v>9</v>
       </c>
       <c r="B114" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C114" t="s">
-        <v>5809</v>
+        <v>5810</v>
       </c>
       <c r="D114" t="s">
         <v>3606</v>
@@ -64512,10 +64515,10 @@
         <v>9</v>
       </c>
       <c r="B115" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C115" t="s">
-        <v>5810</v>
+        <v>5811</v>
       </c>
       <c r="D115" t="s">
         <v>763</v>
@@ -64526,10 +64529,10 @@
         <v>9</v>
       </c>
       <c r="B116" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C116" t="s">
-        <v>5811</v>
+        <v>5812</v>
       </c>
       <c r="D116" t="s">
         <v>771</v>
@@ -64540,10 +64543,10 @@
         <v>9</v>
       </c>
       <c r="B117" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C117" t="s">
-        <v>5812</v>
+        <v>5813</v>
       </c>
       <c r="D117" t="s">
         <v>776</v>
@@ -64554,10 +64557,10 @@
         <v>9</v>
       </c>
       <c r="B118" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C118" t="s">
-        <v>5813</v>
+        <v>5814</v>
       </c>
       <c r="D118" t="s">
         <v>781</v>
@@ -64568,10 +64571,10 @@
         <v>9</v>
       </c>
       <c r="B119" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C119" t="s">
-        <v>5814</v>
+        <v>5815</v>
       </c>
       <c r="D119" t="s">
         <v>1092</v>
@@ -64582,10 +64585,10 @@
         <v>9</v>
       </c>
       <c r="B120" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C120" t="s">
-        <v>5815</v>
+        <v>5816</v>
       </c>
       <c r="D120" t="s">
         <v>1097</v>
@@ -64596,10 +64599,10 @@
         <v>9</v>
       </c>
       <c r="B121" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C121" t="s">
-        <v>5816</v>
+        <v>5817</v>
       </c>
       <c r="D121" t="s">
         <v>2488</v>
@@ -64610,10 +64613,10 @@
         <v>9</v>
       </c>
       <c r="B122" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C122" t="s">
-        <v>5817</v>
+        <v>5818</v>
       </c>
       <c r="D122" t="s">
         <v>2493</v>
@@ -64624,10 +64627,10 @@
         <v>9</v>
       </c>
       <c r="B123" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C123" t="s">
-        <v>5818</v>
+        <v>5819</v>
       </c>
       <c r="D123" t="s">
         <v>3686</v>
@@ -64638,10 +64641,10 @@
         <v>9</v>
       </c>
       <c r="B124" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C124" t="s">
-        <v>5819</v>
+        <v>5820</v>
       </c>
       <c r="D124" t="s">
         <v>2264</v>
@@ -64652,10 +64655,10 @@
         <v>9</v>
       </c>
       <c r="B125" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C125" t="s">
-        <v>5820</v>
+        <v>5821</v>
       </c>
       <c r="D125" t="s">
         <v>2269</v>
@@ -64666,10 +64669,10 @@
         <v>9</v>
       </c>
       <c r="B126" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C126" t="s">
-        <v>5821</v>
+        <v>5822</v>
       </c>
       <c r="D126" t="s">
         <v>1885</v>
@@ -64680,10 +64683,10 @@
         <v>9</v>
       </c>
       <c r="B127" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C127" t="s">
-        <v>5822</v>
+        <v>5823</v>
       </c>
       <c r="D127" t="s">
         <v>1890</v>
@@ -64694,10 +64697,10 @@
         <v>9</v>
       </c>
       <c r="B128" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C128" t="s">
-        <v>5823</v>
+        <v>5824</v>
       </c>
       <c r="D128" t="s">
         <v>3060</v>
@@ -64708,10 +64711,10 @@
         <v>9</v>
       </c>
       <c r="B129" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C129" t="s">
-        <v>5824</v>
+        <v>5825</v>
       </c>
       <c r="D129" t="s">
         <v>3065</v>
@@ -64722,10 +64725,10 @@
         <v>9</v>
       </c>
       <c r="B130" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C130" t="s">
-        <v>5825</v>
+        <v>5826</v>
       </c>
       <c r="D130" t="s">
         <v>3070</v>
@@ -64736,10 +64739,10 @@
         <v>9</v>
       </c>
       <c r="B131" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C131" t="s">
-        <v>5826</v>
+        <v>5827</v>
       </c>
       <c r="D131" t="s">
         <v>1729</v>
@@ -64750,10 +64753,10 @@
         <v>9</v>
       </c>
       <c r="B132" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C132" t="s">
-        <v>5827</v>
+        <v>5828</v>
       </c>
       <c r="D132" t="s">
         <v>1734</v>
@@ -64764,10 +64767,10 @@
         <v>9</v>
       </c>
       <c r="B133" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C133" t="s">
-        <v>5828</v>
+        <v>5829</v>
       </c>
       <c r="D133" t="s">
         <v>2379</v>
@@ -64778,10 +64781,10 @@
         <v>9</v>
       </c>
       <c r="B134" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C134" t="s">
-        <v>5829</v>
+        <v>5830</v>
       </c>
       <c r="D134" t="s">
         <v>2384</v>
@@ -64792,10 +64795,10 @@
         <v>9</v>
       </c>
       <c r="B135" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C135" t="s">
-        <v>5830</v>
+        <v>5831</v>
       </c>
       <c r="D135" t="s">
         <v>2793</v>
@@ -64806,10 +64809,10 @@
         <v>9</v>
       </c>
       <c r="B136" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C136" t="s">
-        <v>5831</v>
+        <v>5832</v>
       </c>
       <c r="D136" t="s">
         <v>2798</v>
@@ -64820,10 +64823,10 @@
         <v>9</v>
       </c>
       <c r="B137" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C137" t="s">
-        <v>5832</v>
+        <v>5833</v>
       </c>
       <c r="D137" t="s">
         <v>2904</v>
@@ -64834,10 +64837,10 @@
         <v>9</v>
       </c>
       <c r="B138" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C138" t="s">
-        <v>5833</v>
+        <v>5834</v>
       </c>
       <c r="D138" t="s">
         <v>2909</v>
@@ -64848,10 +64851,10 @@
         <v>9</v>
       </c>
       <c r="B139" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C139" t="s">
-        <v>5834</v>
+        <v>5835</v>
       </c>
       <c r="D139" t="s">
         <v>2914</v>
@@ -64862,10 +64865,10 @@
         <v>9</v>
       </c>
       <c r="B140" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C140" t="s">
-        <v>5835</v>
+        <v>5836</v>
       </c>
       <c r="D140" t="s">
         <v>412</v>
@@ -64876,10 +64879,10 @@
         <v>9</v>
       </c>
       <c r="B141" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C141" t="s">
-        <v>5836</v>
+        <v>5837</v>
       </c>
       <c r="D141" t="s">
         <v>421</v>
@@ -64890,10 +64893,10 @@
         <v>9</v>
       </c>
       <c r="B142" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C142" t="s">
-        <v>5837</v>
+        <v>5838</v>
       </c>
       <c r="D142" t="s">
         <v>426</v>
@@ -64904,10 +64907,10 @@
         <v>9</v>
       </c>
       <c r="B143" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C143" t="s">
-        <v>5838</v>
+        <v>5839</v>
       </c>
       <c r="D143" t="s">
         <v>2348</v>
@@ -64918,10 +64921,10 @@
         <v>9</v>
       </c>
       <c r="B144" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C144" t="s">
-        <v>5839</v>
+        <v>5840</v>
       </c>
       <c r="D144" t="s">
         <v>2353</v>
@@ -64932,10 +64935,10 @@
         <v>9</v>
       </c>
       <c r="B145" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C145" t="s">
-        <v>5840</v>
+        <v>5841</v>
       </c>
       <c r="D145" t="s">
         <v>2358</v>
@@ -64946,10 +64949,10 @@
         <v>9</v>
       </c>
       <c r="B146" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C146" t="s">
-        <v>5841</v>
+        <v>5842</v>
       </c>
       <c r="D146" t="s">
         <v>3702</v>
@@ -64960,10 +64963,10 @@
         <v>9</v>
       </c>
       <c r="B147" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C147" t="s">
-        <v>5842</v>
+        <v>5843</v>
       </c>
       <c r="D147" t="s">
         <v>1629</v>
@@ -64974,10 +64977,10 @@
         <v>9</v>
       </c>
       <c r="B148" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C148" t="s">
-        <v>5843</v>
+        <v>5844</v>
       </c>
       <c r="D148" t="s">
         <v>1634</v>
@@ -64988,10 +64991,10 @@
         <v>9</v>
       </c>
       <c r="B149" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C149" t="s">
-        <v>5844</v>
+        <v>5845</v>
       </c>
       <c r="D149" t="s">
         <v>1915</v>
@@ -65002,10 +65005,10 @@
         <v>9</v>
       </c>
       <c r="B150" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C150" t="s">
-        <v>5845</v>
+        <v>5846</v>
       </c>
       <c r="D150" t="s">
         <v>2369</v>
@@ -65016,10 +65019,10 @@
         <v>9</v>
       </c>
       <c r="B151" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C151" t="s">
-        <v>5846</v>
+        <v>5847</v>
       </c>
       <c r="D151" t="s">
         <v>2374</v>
@@ -65030,10 +65033,10 @@
         <v>9</v>
       </c>
       <c r="B152" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C152" t="s">
-        <v>5847</v>
+        <v>5848</v>
       </c>
       <c r="D152" t="s">
         <v>485</v>
@@ -65044,10 +65047,10 @@
         <v>9</v>
       </c>
       <c r="B153" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C153" t="s">
-        <v>5848</v>
+        <v>5849</v>
       </c>
       <c r="D153" t="s">
         <v>494</v>
@@ -65058,10 +65061,10 @@
         <v>9</v>
       </c>
       <c r="B154" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C154" t="s">
-        <v>5849</v>
+        <v>5850</v>
       </c>
       <c r="D154" t="s">
         <v>1108</v>
@@ -65072,10 +65075,10 @@
         <v>9</v>
       </c>
       <c r="B155" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C155" t="s">
-        <v>5850</v>
+        <v>5851</v>
       </c>
       <c r="D155" t="s">
         <v>1709</v>
@@ -65086,10 +65089,10 @@
         <v>9</v>
       </c>
       <c r="B156" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C156" t="s">
-        <v>5851</v>
+        <v>5852</v>
       </c>
       <c r="D156" t="s">
         <v>1714</v>
@@ -65100,10 +65103,10 @@
         <v>9</v>
       </c>
       <c r="B157" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C157" t="s">
-        <v>5852</v>
+        <v>5853</v>
       </c>
       <c r="D157" t="s">
         <v>3162</v>
@@ -65114,10 +65117,10 @@
         <v>9</v>
       </c>
       <c r="B158" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C158" t="s">
-        <v>5853</v>
+        <v>5854</v>
       </c>
       <c r="D158" t="s">
         <v>3167</v>
@@ -65128,10 +65131,10 @@
         <v>9</v>
       </c>
       <c r="B159" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C159" t="s">
-        <v>5854</v>
+        <v>5855</v>
       </c>
       <c r="D159" t="s">
         <v>3172</v>
@@ -65142,10 +65145,10 @@
         <v>9</v>
       </c>
       <c r="B160" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C160" t="s">
-        <v>5855</v>
+        <v>5856</v>
       </c>
       <c r="D160" t="s">
         <v>837</v>
@@ -65156,10 +65159,10 @@
         <v>9</v>
       </c>
       <c r="B161" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C161" t="s">
-        <v>5856</v>
+        <v>5857</v>
       </c>
       <c r="D161" t="s">
         <v>843</v>
@@ -65170,10 +65173,10 @@
         <v>9</v>
       </c>
       <c r="B162" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C162" t="s">
-        <v>5857</v>
+        <v>5858</v>
       </c>
       <c r="D162" t="s">
         <v>848</v>
@@ -65184,10 +65187,10 @@
         <v>9</v>
       </c>
       <c r="B163" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C163" t="s">
-        <v>5858</v>
+        <v>5859</v>
       </c>
       <c r="D163" t="s">
         <v>25</v>
@@ -65198,10 +65201,10 @@
         <v>9</v>
       </c>
       <c r="B164" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C164" t="s">
-        <v>5859</v>
+        <v>5860</v>
       </c>
       <c r="D164" t="s">
         <v>38</v>
@@ -65212,10 +65215,10 @@
         <v>9</v>
       </c>
       <c r="B165" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C165" t="s">
-        <v>5860</v>
+        <v>5861</v>
       </c>
       <c r="D165" t="s">
         <v>44</v>
@@ -65226,10 +65229,10 @@
         <v>9</v>
       </c>
       <c r="B166" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C166" t="s">
-        <v>5861</v>
+        <v>5862</v>
       </c>
       <c r="D166" t="s">
         <v>50</v>
@@ -65240,10 +65243,10 @@
         <v>9</v>
       </c>
       <c r="B167" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C167" t="s">
-        <v>5862</v>
+        <v>5863</v>
       </c>
       <c r="D167" t="s">
         <v>59</v>
@@ -65254,10 +65257,10 @@
         <v>9</v>
       </c>
       <c r="B168" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C168" t="s">
-        <v>5863</v>
+        <v>5864</v>
       </c>
       <c r="D168" t="s">
         <v>65</v>
@@ -65268,10 +65271,10 @@
         <v>9</v>
       </c>
       <c r="B169" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C169" t="s">
-        <v>5864</v>
+        <v>5865</v>
       </c>
       <c r="D169" t="s">
         <v>71</v>
@@ -65282,10 +65285,10 @@
         <v>9</v>
       </c>
       <c r="B170" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C170" t="s">
-        <v>5865</v>
+        <v>5866</v>
       </c>
       <c r="D170" t="s">
         <v>80</v>
@@ -65296,10 +65299,10 @@
         <v>9</v>
       </c>
       <c r="B171" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C171" t="s">
-        <v>5866</v>
+        <v>5867</v>
       </c>
       <c r="D171" t="s">
         <v>86</v>
@@ -65310,10 +65313,10 @@
         <v>9</v>
       </c>
       <c r="B172" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C172" t="s">
-        <v>5867</v>
+        <v>5868</v>
       </c>
       <c r="D172" t="s">
         <v>3242</v>
@@ -65324,10 +65327,10 @@
         <v>9</v>
       </c>
       <c r="B173" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C173" t="s">
-        <v>5868</v>
+        <v>5869</v>
       </c>
       <c r="D173" t="s">
         <v>3559</v>
@@ -65338,10 +65341,10 @@
         <v>9</v>
       </c>
       <c r="B174" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C174" t="s">
-        <v>5869</v>
+        <v>5870</v>
       </c>
       <c r="D174" t="s">
         <v>3612</v>
@@ -65352,10 +65355,10 @@
         <v>9</v>
       </c>
       <c r="B175" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C175" t="s">
-        <v>5870</v>
+        <v>5871</v>
       </c>
       <c r="D175" t="s">
         <v>3617</v>
@@ -65366,10 +65369,10 @@
         <v>9</v>
       </c>
       <c r="B176" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C176" t="s">
-        <v>5871</v>
+        <v>5872</v>
       </c>
       <c r="D176" t="s">
         <v>3632</v>
@@ -65380,10 +65383,10 @@
         <v>9</v>
       </c>
       <c r="B177" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C177" t="s">
-        <v>5872</v>
+        <v>5873</v>
       </c>
       <c r="D177" t="s">
         <v>3637</v>
@@ -65394,10 +65397,10 @@
         <v>9</v>
       </c>
       <c r="B178" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C178" t="s">
-        <v>5873</v>
+        <v>5874</v>
       </c>
       <c r="D178" t="s">
         <v>3642</v>
@@ -65408,10 +65411,10 @@
         <v>9</v>
       </c>
       <c r="B179" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C179" t="s">
-        <v>5874</v>
+        <v>5875</v>
       </c>
       <c r="D179" t="s">
         <v>3647</v>
@@ -65422,10 +65425,10 @@
         <v>9</v>
       </c>
       <c r="B180" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C180" t="s">
-        <v>5875</v>
+        <v>5876</v>
       </c>
       <c r="D180" t="s">
         <v>3707</v>
@@ -65436,10 +65439,10 @@
         <v>9</v>
       </c>
       <c r="B181" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C181" t="s">
-        <v>5876</v>
+        <v>5877</v>
       </c>
       <c r="D181" t="s">
         <v>3712</v>
@@ -65450,10 +65453,10 @@
         <v>9</v>
       </c>
       <c r="B182" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C182" t="s">
-        <v>5877</v>
+        <v>5878</v>
       </c>
       <c r="D182" t="s">
         <v>3717</v>
@@ -65464,10 +65467,10 @@
         <v>9</v>
       </c>
       <c r="B183" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C183" t="s">
-        <v>5878</v>
+        <v>5879</v>
       </c>
       <c r="D183" t="s">
         <v>1240</v>
@@ -65478,10 +65481,10 @@
         <v>9</v>
       </c>
       <c r="B184" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C184" t="s">
-        <v>5879</v>
+        <v>5880</v>
       </c>
       <c r="D184" t="s">
         <v>1926</v>
@@ -65492,10 +65495,10 @@
         <v>9</v>
       </c>
       <c r="B185" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C185" t="s">
-        <v>5880</v>
+        <v>5881</v>
       </c>
       <c r="D185" t="s">
         <v>1931</v>
@@ -65506,10 +65509,10 @@
         <v>9</v>
       </c>
       <c r="B186" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C186" t="s">
-        <v>5881</v>
+        <v>5882</v>
       </c>
       <c r="D186" t="s">
         <v>2530</v>
@@ -65520,10 +65523,10 @@
         <v>9</v>
       </c>
       <c r="B187" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C187" t="s">
-        <v>5882</v>
+        <v>5883</v>
       </c>
       <c r="D187" t="s">
         <v>2430</v>
@@ -65534,10 +65537,10 @@
         <v>9</v>
       </c>
       <c r="B188" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C188" t="s">
-        <v>5883</v>
+        <v>5884</v>
       </c>
       <c r="D188" t="s">
         <v>2435</v>
@@ -65548,10 +65551,10 @@
         <v>9</v>
       </c>
       <c r="B189" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C189" t="s">
-        <v>5884</v>
+        <v>5885</v>
       </c>
       <c r="D189" t="s">
         <v>3748</v>
@@ -65562,10 +65565,10 @@
         <v>9</v>
       </c>
       <c r="B190" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C190" t="s">
-        <v>5885</v>
+        <v>5886</v>
       </c>
       <c r="D190" t="s">
         <v>3753</v>
@@ -65576,10 +65579,10 @@
         <v>9</v>
       </c>
       <c r="B191" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C191" t="s">
-        <v>5886</v>
+        <v>5887</v>
       </c>
       <c r="D191" t="s">
         <v>713</v>
@@ -65590,10 +65593,10 @@
         <v>9</v>
       </c>
       <c r="B192" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C192" t="s">
-        <v>5887</v>
+        <v>5888</v>
       </c>
       <c r="D192" t="s">
         <v>1175</v>
@@ -65604,10 +65607,10 @@
         <v>9</v>
       </c>
       <c r="B193" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C193" t="s">
-        <v>5888</v>
+        <v>5889</v>
       </c>
       <c r="D193" t="s">
         <v>733</v>
@@ -65618,10 +65621,10 @@
         <v>9</v>
       </c>
       <c r="B194" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C194" t="s">
-        <v>5889</v>
+        <v>5890</v>
       </c>
       <c r="D194" t="s">
         <v>1185</v>
@@ -65632,10 +65635,10 @@
         <v>9</v>
       </c>
       <c r="B195" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C195" t="s">
-        <v>5890</v>
+        <v>5891</v>
       </c>
       <c r="D195" t="s">
         <v>3086</v>
@@ -65646,10 +65649,10 @@
         <v>9</v>
       </c>
       <c r="B196" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C196" t="s">
-        <v>5891</v>
+        <v>5892</v>
       </c>
       <c r="D196" t="s">
         <v>3692</v>
@@ -65660,10 +65663,10 @@
         <v>9</v>
       </c>
       <c r="B197" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C197" t="s">
-        <v>5892</v>
+        <v>5893</v>
       </c>
       <c r="D197" t="s">
         <v>3728</v>
@@ -65674,10 +65677,10 @@
         <v>9</v>
       </c>
       <c r="B198" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C198" t="s">
-        <v>5893</v>
+        <v>5894</v>
       </c>
       <c r="D198" t="s">
         <v>3733</v>
@@ -65688,10 +65691,10 @@
         <v>9</v>
       </c>
       <c r="B199" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C199" t="s">
-        <v>5894</v>
+        <v>5895</v>
       </c>
       <c r="D199" t="s">
         <v>2945</v>
@@ -65702,10 +65705,10 @@
         <v>9</v>
       </c>
       <c r="B200" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C200" t="s">
-        <v>5895</v>
+        <v>5896</v>
       </c>
       <c r="D200" t="s">
         <v>2950</v>
@@ -65716,10 +65719,10 @@
         <v>9</v>
       </c>
       <c r="B201" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C201" t="s">
-        <v>5896</v>
+        <v>5897</v>
       </c>
       <c r="D201" t="s">
         <v>3758</v>
@@ -65730,10 +65733,10 @@
         <v>9</v>
       </c>
       <c r="B202" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C202" t="s">
-        <v>5897</v>
+        <v>5898</v>
       </c>
       <c r="D202" t="s">
         <v>3763</v>
@@ -65744,10 +65747,10 @@
         <v>9</v>
       </c>
       <c r="B203" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C203" t="s">
-        <v>5898</v>
+        <v>5899</v>
       </c>
       <c r="D203" t="s">
         <v>3723</v>
@@ -65758,10 +65761,10 @@
         <v>9</v>
       </c>
       <c r="B204" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C204" t="s">
-        <v>5899</v>
+        <v>5900</v>
       </c>
       <c r="D204" t="s">
         <v>3187</v>
@@ -65772,10 +65775,10 @@
         <v>9</v>
       </c>
       <c r="B205" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C205" t="s">
-        <v>5900</v>
+        <v>5901</v>
       </c>
       <c r="D205" t="s">
         <v>3192</v>
@@ -65786,10 +65789,10 @@
         <v>9</v>
       </c>
       <c r="B206" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C206" t="s">
-        <v>5901</v>
+        <v>5902</v>
       </c>
       <c r="D206" t="s">
         <v>3197</v>
@@ -65800,10 +65803,10 @@
         <v>9</v>
       </c>
       <c r="B207" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C207" t="s">
-        <v>5902</v>
+        <v>5903</v>
       </c>
       <c r="D207" t="s">
         <v>811</v>
@@ -65814,10 +65817,10 @@
         <v>9</v>
       </c>
       <c r="B208" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C208" t="s">
-        <v>5903</v>
+        <v>5904</v>
       </c>
       <c r="D208" t="s">
         <v>3663</v>
@@ -65828,10 +65831,10 @@
         <v>9</v>
       </c>
       <c r="B209" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C209" t="s">
-        <v>5904</v>
+        <v>5905</v>
       </c>
       <c r="D209" t="s">
         <v>3669</v>
@@ -65842,10 +65845,10 @@
         <v>9</v>
       </c>
       <c r="B210" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C210" t="s">
-        <v>5905</v>
+        <v>5906</v>
       </c>
       <c r="D210" t="s">
         <v>3675</v>
@@ -65856,10 +65859,10 @@
         <v>9</v>
       </c>
       <c r="B211" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C211" t="s">
-        <v>5906</v>
+        <v>5907</v>
       </c>
       <c r="D211" t="s">
         <v>3680</v>
@@ -65870,10 +65873,10 @@
         <v>9</v>
       </c>
       <c r="B212" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C212" t="s">
-        <v>5907</v>
+        <v>5908</v>
       </c>
       <c r="D212" t="s">
         <v>573</v>
@@ -65884,10 +65887,10 @@
         <v>9</v>
       </c>
       <c r="B213" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C213" t="s">
-        <v>5908</v>
+        <v>5909</v>
       </c>
       <c r="D213" t="s">
         <v>1154</v>
@@ -65898,10 +65901,10 @@
         <v>9</v>
       </c>
       <c r="B214" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C214" t="s">
-        <v>5909</v>
+        <v>5910</v>
       </c>
       <c r="D214" t="s">
         <v>1639</v>
@@ -65912,10 +65915,10 @@
         <v>9</v>
       </c>
       <c r="B215" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C215" t="s">
-        <v>5910</v>
+        <v>5911</v>
       </c>
       <c r="D215" t="s">
         <v>1644</v>
@@ -65926,10 +65929,10 @@
         <v>9</v>
       </c>
       <c r="B216" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C216" t="s">
-        <v>5911</v>
+        <v>5912</v>
       </c>
       <c r="D216" t="s">
         <v>1649</v>
@@ -65940,10 +65943,10 @@
         <v>9</v>
       </c>
       <c r="B217" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C217" t="s">
-        <v>5912</v>
+        <v>5913</v>
       </c>
       <c r="D217" t="s">
         <v>3652</v>
@@ -65954,10 +65957,10 @@
         <v>9</v>
       </c>
       <c r="B218" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C218" t="s">
-        <v>5913</v>
+        <v>5914</v>
       </c>
       <c r="D218" t="s">
         <v>3657</v>
@@ -65968,10 +65971,10 @@
         <v>9</v>
       </c>
       <c r="B219" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C219" t="s">
-        <v>5914</v>
+        <v>5915</v>
       </c>
       <c r="D219" t="s">
         <v>3738</v>
@@ -65982,10 +65985,10 @@
         <v>9</v>
       </c>
       <c r="B220" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C220" t="s">
-        <v>5915</v>
+        <v>5916</v>
       </c>
       <c r="D220" t="s">
         <v>3743</v>
@@ -65996,10 +65999,10 @@
         <v>9</v>
       </c>
       <c r="B221" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C221" t="s">
-        <v>5916</v>
+        <v>5917</v>
       </c>
       <c r="D221" t="s">
         <v>1347</v>
@@ -66010,10 +66013,10 @@
         <v>9</v>
       </c>
       <c r="B222" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C222" t="s">
-        <v>5917</v>
+        <v>5918</v>
       </c>
       <c r="D222" t="s">
         <v>1352</v>
@@ -66024,10 +66027,10 @@
         <v>9</v>
       </c>
       <c r="B223" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C223" t="s">
-        <v>5918</v>
+        <v>5919</v>
       </c>
       <c r="D223" t="s">
         <v>1357</v>
@@ -66038,10 +66041,10 @@
         <v>9</v>
       </c>
       <c r="B224" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C224" t="s">
-        <v>5919</v>
+        <v>5920</v>
       </c>
       <c r="D224" t="s">
         <v>3440</v>
@@ -66052,10 +66055,10 @@
         <v>9</v>
       </c>
       <c r="B225" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C225" t="s">
-        <v>5920</v>
+        <v>5921</v>
       </c>
       <c r="D225" t="s">
         <v>3447</v>
@@ -66066,10 +66069,10 @@
         <v>9</v>
       </c>
       <c r="B226" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C226" t="s">
-        <v>5921</v>
+        <v>5922</v>
       </c>
       <c r="D226" t="s">
         <v>3452</v>
@@ -66080,10 +66083,10 @@
         <v>9</v>
       </c>
       <c r="B227" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C227" t="s">
-        <v>5922</v>
+        <v>5923</v>
       </c>
       <c r="D227" t="s">
         <v>4546</v>
@@ -66094,10 +66097,10 @@
         <v>9</v>
       </c>
       <c r="B228" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C228" t="s">
-        <v>5923</v>
+        <v>5924</v>
       </c>
       <c r="D228" t="s">
         <v>3405</v>
@@ -66108,10 +66111,10 @@
         <v>9</v>
       </c>
       <c r="B229" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C229" t="s">
-        <v>5924</v>
+        <v>5925</v>
       </c>
       <c r="D229" t="s">
         <v>3412</v>
@@ -66122,10 +66125,10 @@
         <v>9</v>
       </c>
       <c r="B230" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C230" t="s">
-        <v>5925</v>
+        <v>5926</v>
       </c>
       <c r="D230" t="s">
         <v>3418</v>
@@ -66136,10 +66139,10 @@
         <v>9</v>
       </c>
       <c r="B231" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C231" t="s">
-        <v>5926</v>
+        <v>5927</v>
       </c>
       <c r="D231" t="s">
         <v>1250</v>
@@ -66150,10 +66153,10 @@
         <v>9</v>
       </c>
       <c r="B232" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C232" t="s">
-        <v>5927</v>
+        <v>5928</v>
       </c>
       <c r="D232" t="s">
         <v>3423</v>
@@ -66164,10 +66167,10 @@
         <v>9</v>
       </c>
       <c r="B233" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C233" t="s">
-        <v>5928</v>
+        <v>5929</v>
       </c>
       <c r="D233" t="s">
         <v>3430</v>
@@ -66178,10 +66181,10 @@
         <v>9</v>
       </c>
       <c r="B234" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C234" t="s">
-        <v>5929</v>
+        <v>5930</v>
       </c>
       <c r="D234" t="s">
         <v>3435</v>
@@ -66192,10 +66195,10 @@
         <v>9</v>
       </c>
       <c r="B235" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C235" t="s">
-        <v>5930</v>
+        <v>5931</v>
       </c>
       <c r="D235" t="s">
         <v>1979</v>
@@ -66206,10 +66209,10 @@
         <v>9</v>
       </c>
       <c r="B236" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C236" t="s">
-        <v>5931</v>
+        <v>5932</v>
       </c>
       <c r="D236" t="s">
         <v>1984</v>
@@ -66220,10 +66223,10 @@
         <v>9</v>
       </c>
       <c r="B237" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C237" t="s">
-        <v>5932</v>
+        <v>5933</v>
       </c>
       <c r="D237" t="s">
         <v>1989</v>
@@ -66234,10 +66237,10 @@
         <v>9</v>
       </c>
       <c r="B238" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C238" t="s">
-        <v>5933</v>
+        <v>5934</v>
       </c>
       <c r="D238" t="s">
         <v>673</v>
@@ -66248,10 +66251,10 @@
         <v>9</v>
       </c>
       <c r="B239" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C239" t="s">
-        <v>5934</v>
+        <v>5935</v>
       </c>
       <c r="D239" t="s">
         <v>4094</v>
@@ -66262,10 +66265,10 @@
         <v>9</v>
       </c>
       <c r="B240" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C240" t="s">
-        <v>5935</v>
+        <v>5936</v>
       </c>
       <c r="D240" t="s">
         <v>1994</v>
@@ -66276,10 +66279,10 @@
         <v>9</v>
       </c>
       <c r="B241" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C241" t="s">
-        <v>5936</v>
+        <v>5937</v>
       </c>
       <c r="D241" t="s">
         <v>1999</v>
@@ -66290,10 +66293,10 @@
         <v>9</v>
       </c>
       <c r="B242" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C242" t="s">
-        <v>5937</v>
+        <v>5938</v>
       </c>
       <c r="D242" t="s">
         <v>2004</v>
@@ -66304,10 +66307,10 @@
         <v>9</v>
       </c>
       <c r="B243" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C243" t="s">
-        <v>5938</v>
+        <v>5939</v>
       </c>
       <c r="D243" t="s">
         <v>3768</v>
@@ -66318,10 +66321,10 @@
         <v>9</v>
       </c>
       <c r="B244" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C244" t="s">
-        <v>5939</v>
+        <v>5940</v>
       </c>
       <c r="D244" t="s">
         <v>3773</v>
@@ -66332,10 +66335,10 @@
         <v>9</v>
       </c>
       <c r="B245" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C245" t="s">
-        <v>5940</v>
+        <v>5941</v>
       </c>
       <c r="D245" t="s">
         <v>3778</v>
@@ -66346,10 +66349,10 @@
         <v>9</v>
       </c>
       <c r="B246" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C246" t="s">
-        <v>5941</v>
+        <v>5942</v>
       </c>
       <c r="D246" t="s">
         <v>3784</v>
@@ -66360,10 +66363,10 @@
         <v>9</v>
       </c>
       <c r="B247" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="C247" t="s">
-        <v>5942</v>
+        <v>5943</v>
       </c>
       <c r="D247" t="s">
         <v>854</v>
@@ -66383,600 +66386,600 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>5943</v>
+        <v>5944</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>5944</v>
+        <v>5945</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>5945</v>
+        <v>5946</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>5946</v>
+        <v>5947</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>5947</v>
+        <v>5948</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5948</v>
+        <v>5949</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5949</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>5950</v>
+        <v>5951</v>
       </c>
       <c r="B2" t="s">
-        <v>5951</v>
+        <v>5952</v>
       </c>
       <c r="C2" t="s">
-        <v>5952</v>
+        <v>5953</v>
       </c>
       <c r="D2" t="s">
-        <v>5953</v>
+        <v>5954</v>
       </c>
       <c r="E2" t="s">
-        <v>5953</v>
+        <v>5954</v>
       </c>
       <c r="F2" t="s">
-        <v>5953</v>
+        <v>5954</v>
       </c>
       <c r="G2" t="s">
-        <v>5953</v>
+        <v>5954</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>5954</v>
+        <v>5955</v>
       </c>
       <c r="B3" t="s">
-        <v>5955</v>
+        <v>5956</v>
       </c>
       <c r="C3" t="s">
-        <v>5956</v>
+        <v>5957</v>
       </c>
       <c r="D3" t="s">
-        <v>5957</v>
+        <v>5958</v>
       </c>
       <c r="E3" t="s">
-        <v>5958</v>
+        <v>5959</v>
       </c>
       <c r="F3" t="s">
-        <v>5959</v>
+        <v>5960</v>
       </c>
       <c r="G3" t="s">
-        <v>5960</v>
+        <v>5961</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>5961</v>
+        <v>5962</v>
       </c>
       <c r="B4" t="s">
-        <v>5962</v>
+        <v>5963</v>
       </c>
       <c r="C4" t="s">
-        <v>5963</v>
+        <v>5964</v>
       </c>
       <c r="D4" t="s">
-        <v>5957</v>
+        <v>5958</v>
       </c>
       <c r="E4" t="s">
-        <v>5964</v>
+        <v>5965</v>
       </c>
       <c r="F4" t="s">
-        <v>5959</v>
+        <v>5960</v>
       </c>
       <c r="G4" t="s">
-        <v>5965</v>
+        <v>5966</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>5966</v>
+        <v>5967</v>
       </c>
       <c r="B5" t="s">
-        <v>5967</v>
+        <v>5968</v>
       </c>
       <c r="C5" t="s">
-        <v>5968</v>
+        <v>5969</v>
       </c>
       <c r="D5" t="s">
-        <v>5957</v>
+        <v>5958</v>
       </c>
       <c r="E5" t="s">
-        <v>5969</v>
+        <v>5970</v>
       </c>
       <c r="F5" t="s">
-        <v>5959</v>
+        <v>5960</v>
       </c>
       <c r="G5" t="s">
-        <v>5970</v>
+        <v>5971</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>5971</v>
+        <v>5972</v>
       </c>
       <c r="B6" t="s">
-        <v>5972</v>
+        <v>5973</v>
       </c>
       <c r="C6" t="s">
-        <v>5973</v>
+        <v>5974</v>
       </c>
       <c r="D6" t="s">
-        <v>5957</v>
+        <v>5958</v>
       </c>
       <c r="E6" t="s">
-        <v>5974</v>
+        <v>5975</v>
       </c>
       <c r="F6" t="s">
-        <v>5959</v>
+        <v>5960</v>
       </c>
       <c r="G6" t="s">
-        <v>5975</v>
+        <v>5976</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>5976</v>
+        <v>5977</v>
       </c>
       <c r="B7" t="s">
-        <v>5977</v>
+        <v>5978</v>
       </c>
       <c r="C7" t="s">
-        <v>5978</v>
+        <v>5979</v>
       </c>
       <c r="D7" t="s">
+        <v>5959</v>
+      </c>
+      <c r="E7" t="s">
         <v>5958</v>
       </c>
-      <c r="E7" t="s">
-        <v>5957</v>
-      </c>
       <c r="F7" t="s">
+        <v>5961</v>
+      </c>
+      <c r="G7" t="s">
         <v>5960</v>
-      </c>
-      <c r="G7" t="s">
-        <v>5959</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>5979</v>
+        <v>5980</v>
       </c>
       <c r="B8" t="s">
-        <v>5980</v>
+        <v>5981</v>
       </c>
       <c r="C8" t="s">
-        <v>5981</v>
+        <v>5982</v>
       </c>
       <c r="D8" t="s">
-        <v>5953</v>
+        <v>5954</v>
       </c>
       <c r="E8" t="s">
-        <v>5953</v>
+        <v>5954</v>
       </c>
       <c r="F8" t="s">
-        <v>5953</v>
+        <v>5954</v>
       </c>
       <c r="G8" t="s">
-        <v>5953</v>
+        <v>5954</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>5982</v>
+        <v>5983</v>
       </c>
       <c r="B9" t="s">
-        <v>5983</v>
+        <v>5984</v>
       </c>
       <c r="C9" t="s">
-        <v>5984</v>
+        <v>5985</v>
       </c>
       <c r="D9" t="s">
-        <v>5958</v>
+        <v>5959</v>
       </c>
       <c r="E9" t="s">
-        <v>5964</v>
+        <v>5965</v>
       </c>
       <c r="F9" t="s">
-        <v>5960</v>
+        <v>5961</v>
       </c>
       <c r="G9" t="s">
-        <v>5965</v>
+        <v>5966</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>5985</v>
+        <v>5986</v>
       </c>
       <c r="B10" t="s">
-        <v>5986</v>
+        <v>5987</v>
       </c>
       <c r="C10" t="s">
-        <v>5987</v>
+        <v>5988</v>
       </c>
       <c r="D10" t="s">
-        <v>5958</v>
+        <v>5959</v>
       </c>
       <c r="E10" t="s">
-        <v>5969</v>
+        <v>5970</v>
       </c>
       <c r="F10" t="s">
-        <v>5960</v>
+        <v>5961</v>
       </c>
       <c r="G10" t="s">
-        <v>5970</v>
+        <v>5971</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>5988</v>
+        <v>5989</v>
       </c>
       <c r="B11" t="s">
-        <v>5989</v>
+        <v>5990</v>
       </c>
       <c r="C11" t="s">
-        <v>5990</v>
+        <v>5991</v>
       </c>
       <c r="D11" t="s">
-        <v>5958</v>
+        <v>5959</v>
       </c>
       <c r="E11" t="s">
-        <v>5974</v>
+        <v>5975</v>
       </c>
       <c r="F11" t="s">
-        <v>5960</v>
+        <v>5961</v>
       </c>
       <c r="G11" t="s">
-        <v>5975</v>
+        <v>5976</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>5991</v>
+        <v>5992</v>
       </c>
       <c r="B12" t="s">
-        <v>5992</v>
+        <v>5993</v>
       </c>
       <c r="C12" t="s">
-        <v>5993</v>
+        <v>5994</v>
       </c>
       <c r="D12" t="s">
-        <v>5964</v>
+        <v>5965</v>
       </c>
       <c r="E12" t="s">
-        <v>5957</v>
+        <v>5958</v>
       </c>
       <c r="F12" t="s">
-        <v>5965</v>
+        <v>5966</v>
       </c>
       <c r="G12" t="s">
-        <v>5959</v>
+        <v>5960</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>5994</v>
+        <v>5995</v>
       </c>
       <c r="B13" t="s">
-        <v>5995</v>
+        <v>5996</v>
       </c>
       <c r="C13" t="s">
-        <v>5996</v>
+        <v>5997</v>
       </c>
       <c r="D13" t="s">
-        <v>5964</v>
+        <v>5965</v>
       </c>
       <c r="E13" t="s">
-        <v>5958</v>
+        <v>5959</v>
       </c>
       <c r="F13" t="s">
-        <v>5965</v>
+        <v>5966</v>
       </c>
       <c r="G13" t="s">
-        <v>5960</v>
+        <v>5961</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>5997</v>
+        <v>5998</v>
       </c>
       <c r="B14" t="s">
-        <v>5998</v>
+        <v>5999</v>
       </c>
       <c r="C14" t="s">
-        <v>5999</v>
+        <v>6000</v>
       </c>
       <c r="D14" t="s">
-        <v>5953</v>
+        <v>5954</v>
       </c>
       <c r="E14" t="s">
-        <v>5953</v>
+        <v>5954</v>
       </c>
       <c r="F14" t="s">
-        <v>5953</v>
+        <v>5954</v>
       </c>
       <c r="G14" t="s">
-        <v>5953</v>
+        <v>5954</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>6000</v>
+        <v>6001</v>
       </c>
       <c r="B15" t="s">
-        <v>6001</v>
+        <v>6002</v>
       </c>
       <c r="C15" t="s">
-        <v>6002</v>
+        <v>6003</v>
       </c>
       <c r="D15" t="s">
-        <v>5964</v>
+        <v>5965</v>
       </c>
       <c r="E15" t="s">
-        <v>5969</v>
+        <v>5970</v>
       </c>
       <c r="F15" t="s">
-        <v>5965</v>
+        <v>5966</v>
       </c>
       <c r="G15" t="s">
-        <v>5970</v>
+        <v>5971</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>6003</v>
+        <v>6004</v>
       </c>
       <c r="B16" t="s">
-        <v>6004</v>
+        <v>6005</v>
       </c>
       <c r="C16" t="s">
-        <v>6005</v>
+        <v>6006</v>
       </c>
       <c r="D16" t="s">
-        <v>5964</v>
+        <v>5965</v>
       </c>
       <c r="E16" t="s">
-        <v>5974</v>
+        <v>5975</v>
       </c>
       <c r="F16" t="s">
-        <v>5965</v>
+        <v>5966</v>
       </c>
       <c r="G16" t="s">
-        <v>5975</v>
+        <v>5976</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>6006</v>
+        <v>6007</v>
       </c>
       <c r="B17" t="s">
-        <v>6007</v>
+        <v>6008</v>
       </c>
       <c r="C17" t="s">
-        <v>6008</v>
+        <v>6009</v>
       </c>
       <c r="D17" t="s">
-        <v>5969</v>
+        <v>5970</v>
       </c>
       <c r="E17" t="s">
-        <v>5957</v>
+        <v>5958</v>
       </c>
       <c r="F17" t="s">
-        <v>5970</v>
+        <v>5971</v>
       </c>
       <c r="G17" t="s">
-        <v>5959</v>
+        <v>5960</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>6009</v>
+        <v>6010</v>
       </c>
       <c r="B18" t="s">
-        <v>6010</v>
+        <v>6011</v>
       </c>
       <c r="C18" t="s">
-        <v>6011</v>
+        <v>6012</v>
       </c>
       <c r="D18" t="s">
-        <v>5969</v>
+        <v>5970</v>
       </c>
       <c r="E18" t="s">
-        <v>5958</v>
+        <v>5959</v>
       </c>
       <c r="F18" t="s">
-        <v>5970</v>
+        <v>5971</v>
       </c>
       <c r="G18" t="s">
-        <v>5960</v>
+        <v>5961</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>6012</v>
+        <v>6013</v>
       </c>
       <c r="B19" t="s">
-        <v>6013</v>
+        <v>6014</v>
       </c>
       <c r="C19" t="s">
-        <v>6014</v>
+        <v>6015</v>
       </c>
       <c r="D19" t="s">
-        <v>5969</v>
+        <v>5970</v>
       </c>
       <c r="E19" t="s">
-        <v>5964</v>
+        <v>5965</v>
       </c>
       <c r="F19" t="s">
-        <v>5970</v>
+        <v>5971</v>
       </c>
       <c r="G19" t="s">
-        <v>5965</v>
+        <v>5966</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>6015</v>
+        <v>6016</v>
       </c>
       <c r="B20" t="s">
-        <v>6016</v>
+        <v>6017</v>
       </c>
       <c r="C20" t="s">
-        <v>6017</v>
+        <v>6018</v>
       </c>
       <c r="D20" t="s">
-        <v>5953</v>
+        <v>5954</v>
       </c>
       <c r="E20" t="s">
-        <v>5953</v>
+        <v>5954</v>
       </c>
       <c r="F20" t="s">
-        <v>5953</v>
+        <v>5954</v>
       </c>
       <c r="G20" t="s">
-        <v>5953</v>
+        <v>5954</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>6018</v>
+        <v>6019</v>
       </c>
       <c r="B21" t="s">
-        <v>6019</v>
+        <v>6020</v>
       </c>
       <c r="C21" t="s">
-        <v>6020</v>
+        <v>6021</v>
       </c>
       <c r="D21" t="s">
-        <v>5969</v>
+        <v>5970</v>
       </c>
       <c r="E21" t="s">
-        <v>5974</v>
+        <v>5975</v>
       </c>
       <c r="F21" t="s">
-        <v>5970</v>
+        <v>5971</v>
       </c>
       <c r="G21" t="s">
-        <v>5975</v>
+        <v>5976</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>6021</v>
+        <v>6022</v>
       </c>
       <c r="B22" t="s">
-        <v>6022</v>
+        <v>6023</v>
       </c>
       <c r="C22" t="s">
-        <v>6023</v>
+        <v>6024</v>
       </c>
       <c r="D22" t="s">
-        <v>5974</v>
+        <v>5975</v>
       </c>
       <c r="E22" t="s">
-        <v>5957</v>
+        <v>5958</v>
       </c>
       <c r="F22" t="s">
-        <v>5975</v>
+        <v>5976</v>
       </c>
       <c r="G22" t="s">
-        <v>5959</v>
+        <v>5960</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>6024</v>
+        <v>6025</v>
       </c>
       <c r="B23" t="s">
-        <v>6025</v>
+        <v>6026</v>
       </c>
       <c r="C23" t="s">
-        <v>6026</v>
+        <v>6027</v>
       </c>
       <c r="D23" t="s">
-        <v>5974</v>
+        <v>5975</v>
       </c>
       <c r="E23" t="s">
-        <v>5958</v>
+        <v>5959</v>
       </c>
       <c r="F23" t="s">
-        <v>5975</v>
+        <v>5976</v>
       </c>
       <c r="G23" t="s">
-        <v>5960</v>
+        <v>5961</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>6027</v>
+        <v>6028</v>
       </c>
       <c r="B24" t="s">
-        <v>6028</v>
+        <v>6029</v>
       </c>
       <c r="C24" t="s">
-        <v>6029</v>
+        <v>6030</v>
       </c>
       <c r="D24" t="s">
-        <v>5974</v>
+        <v>5975</v>
       </c>
       <c r="E24" t="s">
-        <v>5964</v>
+        <v>5965</v>
       </c>
       <c r="F24" t="s">
-        <v>5975</v>
+        <v>5976</v>
       </c>
       <c r="G24" t="s">
-        <v>5965</v>
+        <v>5966</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>6030</v>
+        <v>6031</v>
       </c>
       <c r="B25" t="s">
-        <v>6031</v>
+        <v>6032</v>
       </c>
       <c r="C25" t="s">
-        <v>6032</v>
+        <v>6033</v>
       </c>
       <c r="D25" t="s">
-        <v>5974</v>
+        <v>5975</v>
       </c>
       <c r="E25" t="s">
-        <v>5969</v>
+        <v>5970</v>
       </c>
       <c r="F25" t="s">
-        <v>5975</v>
+        <v>5976</v>
       </c>
       <c r="G25" t="s">
-        <v>5970</v>
+        <v>5971</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>6033</v>
+        <v>6034</v>
       </c>
       <c r="B26" t="s">
-        <v>6034</v>
+        <v>6035</v>
       </c>
       <c r="C26" t="s">
-        <v>6035</v>
+        <v>6036</v>
       </c>
       <c r="D26" t="s">
-        <v>5953</v>
+        <v>5954</v>
       </c>
       <c r="E26" t="s">
-        <v>5953</v>
+        <v>5954</v>
       </c>
       <c r="F26" t="s">
-        <v>5953</v>
+        <v>5954</v>
       </c>
       <c r="G26" t="s">
-        <v>5953</v>
+        <v>5954</v>
       </c>
     </row>
   </sheetData>
@@ -66997,66 +67000,66 @@
   <sheetData>
     <row r="1" spans="1:19">
       <c r="A1" t="s">
-        <v>6036</v>
+        <v>6037</v>
       </c>
       <c r="B1" t="s">
-        <v>6037</v>
+        <v>6038</v>
       </c>
       <c r="C1" t="s">
-        <v>6038</v>
+        <v>6039</v>
       </c>
       <c r="D1" t="s">
-        <v>6039</v>
+        <v>6040</v>
       </c>
       <c r="E1" t="s">
-        <v>6040</v>
+        <v>6041</v>
       </c>
       <c r="F1" t="s">
-        <v>6041</v>
+        <v>6042</v>
       </c>
       <c r="G1" t="s">
-        <v>6042</v>
+        <v>6043</v>
       </c>
       <c r="H1" t="s">
-        <v>6043</v>
+        <v>6044</v>
       </c>
       <c r="I1" t="s">
-        <v>6044</v>
+        <v>6045</v>
       </c>
       <c r="J1" t="s">
-        <v>6045</v>
+        <v>6046</v>
       </c>
       <c r="K1" t="s">
-        <v>6046</v>
+        <v>6047</v>
       </c>
       <c r="L1" t="s">
-        <v>6047</v>
+        <v>6048</v>
       </c>
       <c r="M1" t="s">
-        <v>6048</v>
+        <v>6049</v>
       </c>
       <c r="N1" t="s">
-        <v>6049</v>
+        <v>6050</v>
       </c>
       <c r="O1" t="s">
-        <v>6050</v>
+        <v>6051</v>
       </c>
       <c r="P1" t="s">
-        <v>6051</v>
+        <v>6052</v>
       </c>
       <c r="Q1" t="s">
-        <v>6052</v>
+        <v>6053</v>
       </c>
       <c r="R1" t="s">
-        <v>6053</v>
+        <v>6054</v>
       </c>
       <c r="S1" t="s">
-        <v>6054</v>
+        <v>6055</v>
       </c>
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>6037</v>
+        <v>6038</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -67115,7 +67118,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>6038</v>
+        <v>6039</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -67174,7 +67177,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>6039</v>
+        <v>6040</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -67233,7 +67236,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>6040</v>
+        <v>6041</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -67292,7 +67295,7 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>6041</v>
+        <v>6042</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -67351,7 +67354,7 @@
     </row>
     <row r="7" spans="1:19">
       <c r="A7" t="s">
-        <v>6042</v>
+        <v>6043</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -67410,7 +67413,7 @@
     </row>
     <row r="8" spans="1:19">
       <c r="A8" t="s">
-        <v>6043</v>
+        <v>6044</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -67469,7 +67472,7 @@
     </row>
     <row r="9" spans="1:19">
       <c r="A9" t="s">
-        <v>6044</v>
+        <v>6045</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -67528,7 +67531,7 @@
     </row>
     <row r="10" spans="1:19">
       <c r="A10" t="s">
-        <v>6045</v>
+        <v>6046</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -67587,7 +67590,7 @@
     </row>
     <row r="11" spans="1:19">
       <c r="A11" t="s">
-        <v>6046</v>
+        <v>6047</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -67646,7 +67649,7 @@
     </row>
     <row r="12" spans="1:19">
       <c r="A12" t="s">
-        <v>6047</v>
+        <v>6048</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -67705,7 +67708,7 @@
     </row>
     <row r="13" spans="1:19">
       <c r="A13" t="s">
-        <v>6048</v>
+        <v>6049</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -67764,7 +67767,7 @@
     </row>
     <row r="14" spans="1:19">
       <c r="A14" t="s">
-        <v>6049</v>
+        <v>6050</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -67823,7 +67826,7 @@
     </row>
     <row r="15" spans="1:19">
       <c r="A15" t="s">
-        <v>6050</v>
+        <v>6051</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -67882,7 +67885,7 @@
     </row>
     <row r="16" spans="1:19">
       <c r="A16" t="s">
-        <v>6051</v>
+        <v>6052</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -67941,7 +67944,7 @@
     </row>
     <row r="17" spans="1:19">
       <c r="A17" t="s">
-        <v>6052</v>
+        <v>6053</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -68000,7 +68003,7 @@
     </row>
     <row r="18" spans="1:19">
       <c r="A18" t="s">
-        <v>6053</v>
+        <v>6054</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -68059,7 +68062,7 @@
     </row>
     <row r="19" spans="1:19">
       <c r="A19" t="s">
-        <v>6054</v>
+        <v>6055</v>
       </c>
       <c r="B19">
         <v>1</v>

--- a/public/docs/datas/pokes.xlsx
+++ b/public/docs/datas/pokes.xlsx
@@ -16420,6 +16420,9 @@
     <t>0359-mega.png</t>
   </si>
   <si>
+    <t>超进化Z</t>
+  </si>
+  <si>
     <t>0359-mega-z.png</t>
   </si>
   <si>
@@ -16511,9 +16514,6 @@
   </si>
   <si>
     <t>0445-mega.png</t>
-  </si>
-  <si>
-    <t>超进化Z</t>
   </si>
   <si>
     <t>0445-mega-z.png</t>
@@ -53304,7 +53304,7 @@
         <v>196</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>5340</v>
+        <v>5346</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>5340</v>
@@ -53350,7 +53350,7 @@
         <v>196</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>5340</v>
+        <v>5348</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>5340</v>
@@ -55165,7 +55165,7 @@
         <v>854</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>5340</v>
+        <v>5346</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>5340</v>
@@ -55201,7 +55201,7 @@
         <v>854</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>5340</v>
+        <v>5348</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>5340</v>
@@ -56389,7 +56389,7 @@
         <v>1915</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>5340</v>
+        <v>5461</v>
       </c>
       <c r="C102" s="4" t="s">
         <v>5340</v>
@@ -56404,7 +56404,7 @@
         <v>561</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>5461</v>
+        <v>5462</v>
       </c>
       <c r="H102" s="5"/>
       <c r="I102" s="5"/>
@@ -56450,7 +56450,7 @@
       </c>
       <c r="F103" s="4"/>
       <c r="G103" s="5" t="s">
-        <v>5462</v>
+        <v>5463</v>
       </c>
       <c r="H103" s="5"/>
       <c r="I103" s="5"/>
@@ -56486,7 +56486,7 @@
         <v>69</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>5463</v>
+        <v>5464</v>
       </c>
       <c r="H104" s="5"/>
       <c r="I104" s="5"/>
@@ -56522,7 +56522,7 @@
         <v>397</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>5464</v>
+        <v>5465</v>
       </c>
       <c r="H105" s="5"/>
       <c r="I105" s="5"/>
@@ -56558,7 +56558,7 @@
         <v>397</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>5465</v>
+        <v>5466</v>
       </c>
       <c r="H106" s="5"/>
       <c r="I106" s="5"/>
@@ -56594,7 +56594,7 @@
         <v>397</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>5466</v>
+        <v>5467</v>
       </c>
       <c r="H107" s="5"/>
       <c r="I107" s="5"/>
@@ -56615,18 +56615,18 @@
         <v>2034</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>5467</v>
+        <v>5468</v>
       </c>
       <c r="C108" s="4"/>
       <c r="D108" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E108" s="4" t="s">
         <v>76</v>
       </c>
       <c r="F108" s="4"/>
       <c r="G108" s="5" t="s">
-        <v>5469</v>
+        <v>5470</v>
       </c>
       <c r="H108" s="5"/>
       <c r="I108" s="5"/>
@@ -56647,11 +56647,11 @@
         <v>2039</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>5467</v>
+        <v>5468</v>
       </c>
       <c r="C109" s="4"/>
       <c r="D109" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E109" s="4" t="s">
         <v>207</v>
@@ -56660,7 +56660,7 @@
         <v>55</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>5470</v>
+        <v>5471</v>
       </c>
       <c r="H109" s="5"/>
       <c r="I109" s="5"/>
@@ -56696,7 +56696,7 @@
         <v>69</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>5471</v>
+        <v>5472</v>
       </c>
       <c r="H110" s="5"/>
       <c r="I110" s="5"/>
@@ -56717,18 +56717,18 @@
         <v>2054</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>5472</v>
+        <v>5473</v>
       </c>
       <c r="C111" s="4"/>
       <c r="D111" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E111" s="4" t="s">
         <v>397</v>
       </c>
       <c r="F111" s="4"/>
       <c r="G111" s="5" t="s">
-        <v>5473</v>
+        <v>5474</v>
       </c>
       <c r="H111" s="5"/>
       <c r="I111" s="5"/>
@@ -56749,18 +56749,18 @@
         <v>2054</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>5474</v>
+        <v>5475</v>
       </c>
       <c r="C112" s="4"/>
       <c r="D112" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E112" s="4" t="s">
         <v>397</v>
       </c>
       <c r="F112" s="4"/>
       <c r="G112" s="5" t="s">
-        <v>5475</v>
+        <v>5476</v>
       </c>
       <c r="H112" s="5"/>
       <c r="I112" s="5"/>
@@ -56781,18 +56781,18 @@
         <v>2054</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>5476</v>
+        <v>5477</v>
       </c>
       <c r="C113" s="4"/>
       <c r="D113" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E113" s="4" t="s">
         <v>397</v>
       </c>
       <c r="F113" s="4"/>
       <c r="G113" s="5" t="s">
-        <v>5477</v>
+        <v>5478</v>
       </c>
       <c r="H113" s="5"/>
       <c r="I113" s="5"/>
@@ -56828,7 +56828,7 @@
         <v>69</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>5478</v>
+        <v>5479</v>
       </c>
       <c r="H114" s="5"/>
       <c r="I114" s="5"/>
@@ -56846,24 +56846,24 @@
         <v>2186</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>5479</v>
+        <v>5480</v>
       </c>
       <c r="C115" s="4"/>
       <c r="D115" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E115" s="4" t="s">
         <v>96</v>
       </c>
       <c r="F115" s="4"/>
       <c r="G115" s="5" t="s">
-        <v>5480</v>
+        <v>5481</v>
       </c>
       <c r="H115" s="5"/>
       <c r="I115" s="5"/>
       <c r="J115" s="5"/>
       <c r="K115" s="4">
-        <f>SUM(L115:Q115)</f>
+        <f t="shared" ref="K115:K124" si="3">SUM(L115:Q115)</f>
         <v>0</v>
       </c>
       <c r="L115" s="6"/>
@@ -56878,24 +56878,24 @@
         <v>2186</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>5481</v>
+        <v>5482</v>
       </c>
       <c r="C116" s="4"/>
       <c r="D116" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E116" s="4" t="s">
         <v>96</v>
       </c>
       <c r="F116" s="4"/>
       <c r="G116" s="5" t="s">
-        <v>5482</v>
+        <v>5483</v>
       </c>
       <c r="H116" s="5"/>
       <c r="I116" s="5"/>
       <c r="J116" s="5"/>
       <c r="K116" s="4">
-        <f>SUM(L116:Q116)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L116" s="6"/>
@@ -56910,11 +56910,11 @@
         <v>2192</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>5479</v>
+        <v>5480</v>
       </c>
       <c r="C117" s="4"/>
       <c r="D117" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E117" s="4" t="s">
         <v>96</v>
@@ -56923,13 +56923,13 @@
         <v>207</v>
       </c>
       <c r="G117" s="5" t="s">
-        <v>5483</v>
+        <v>5484</v>
       </c>
       <c r="H117" s="5"/>
       <c r="I117" s="5"/>
       <c r="J117" s="5"/>
       <c r="K117" s="4">
-        <f>SUM(L117:Q117)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L117" s="6"/>
@@ -56944,11 +56944,11 @@
         <v>2192</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>5481</v>
+        <v>5482</v>
       </c>
       <c r="C118" s="4"/>
       <c r="D118" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E118" s="4" t="s">
         <v>96</v>
@@ -56957,13 +56957,13 @@
         <v>504</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>5484</v>
+        <v>5485</v>
       </c>
       <c r="H118" s="5"/>
       <c r="I118" s="5"/>
       <c r="J118" s="5"/>
       <c r="K118" s="4">
-        <f>SUM(L118:Q118)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L118" s="6"/>
@@ -56978,24 +56978,24 @@
         <v>2232</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>5485</v>
+        <v>5486</v>
       </c>
       <c r="C119" s="4"/>
       <c r="D119" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E119" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F119" s="4"/>
       <c r="G119" s="5" t="s">
-        <v>5486</v>
+        <v>5487</v>
       </c>
       <c r="H119" s="5"/>
       <c r="I119" s="5"/>
       <c r="J119" s="5"/>
       <c r="K119" s="4">
-        <f>SUM(L119:Q119)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L119" s="6"/>
@@ -57010,24 +57010,24 @@
         <v>2238</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>5487</v>
+        <v>5488</v>
       </c>
       <c r="C120" s="4"/>
       <c r="D120" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E120" s="4" t="s">
         <v>76</v>
       </c>
       <c r="F120" s="4"/>
       <c r="G120" s="5" t="s">
-        <v>5488</v>
+        <v>5489</v>
       </c>
       <c r="H120" s="5"/>
       <c r="I120" s="5"/>
       <c r="J120" s="5"/>
       <c r="K120" s="4">
-        <f>SUM(L120:Q120)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L120" s="6"/>
@@ -57042,11 +57042,11 @@
         <v>2244</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>5487</v>
+        <v>5488</v>
       </c>
       <c r="C121" s="4"/>
       <c r="D121" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E121" s="4" t="s">
         <v>76</v>
@@ -57055,13 +57055,13 @@
         <v>207</v>
       </c>
       <c r="G121" s="5" t="s">
-        <v>5489</v>
+        <v>5490</v>
       </c>
       <c r="H121" s="5"/>
       <c r="I121" s="5"/>
       <c r="J121" s="5"/>
       <c r="K121" s="4">
-        <f>SUM(L121:Q121)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L121" s="6"/>
@@ -57091,13 +57091,13 @@
         <v>360</v>
       </c>
       <c r="G122" s="5" t="s">
-        <v>5490</v>
+        <v>5491</v>
       </c>
       <c r="H122" s="5"/>
       <c r="I122" s="5"/>
       <c r="J122" s="5"/>
       <c r="K122" s="4">
-        <f>SUM(L122:Q122)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L122" s="6"/>
@@ -57127,13 +57127,13 @@
         <v>207</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>5491</v>
+        <v>5492</v>
       </c>
       <c r="H123" s="5"/>
       <c r="I123" s="5"/>
       <c r="J123" s="5"/>
       <c r="K123" s="4">
-        <f>SUM(L123:Q123)</f>
+        <f t="shared" si="3"/>
         <v>700</v>
       </c>
       <c r="L123" s="6">
@@ -57160,7 +57160,7 @@
         <v>2358</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>5492</v>
+        <v>5461</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>5340</v>
@@ -57179,7 +57179,7 @@
       <c r="I124" s="5"/>
       <c r="J124" s="5"/>
       <c r="K124" s="4">
-        <f>SUM(L124:Q124)</f>
+        <f t="shared" si="3"/>
         <v>700</v>
       </c>
       <c r="L124" s="6">
@@ -57227,7 +57227,7 @@
       <c r="I125" s="5"/>
       <c r="J125" s="5"/>
       <c r="K125" s="4">
-        <f t="shared" ref="K125:K136" si="3">SUM(L125:Q125)</f>
+        <f t="shared" ref="K125:K136" si="4">SUM(L125:Q125)</f>
         <v>625</v>
       </c>
       <c r="L125" s="6">
@@ -57254,7 +57254,7 @@
         <v>2374</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>5492</v>
+        <v>5461</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>5340</v>
@@ -57275,7 +57275,7 @@
       <c r="I126" s="5"/>
       <c r="J126" s="5"/>
       <c r="K126" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>625</v>
       </c>
       <c r="L126" s="6">
@@ -57323,7 +57323,7 @@
       <c r="I127" s="5"/>
       <c r="J127" s="5"/>
       <c r="K127" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L127" s="6"/>
@@ -57359,7 +57359,7 @@
       <c r="I128" s="5"/>
       <c r="J128" s="5"/>
       <c r="K128" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L128" s="6"/>
@@ -57395,7 +57395,7 @@
       <c r="I129" s="5"/>
       <c r="J129" s="5"/>
       <c r="K129" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L129" s="6"/>
@@ -57414,7 +57414,7 @@
       </c>
       <c r="C130" s="4"/>
       <c r="D130" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E130" s="4" t="s">
         <v>190</v>
@@ -57429,7 +57429,7 @@
       <c r="I130" s="5"/>
       <c r="J130" s="5"/>
       <c r="K130" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L130" s="6"/>
@@ -57448,7 +57448,7 @@
       </c>
       <c r="C131" s="4"/>
       <c r="D131" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E131" s="4" t="s">
         <v>190</v>
@@ -57463,7 +57463,7 @@
       <c r="I131" s="5"/>
       <c r="J131" s="5"/>
       <c r="K131" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L131" s="6"/>
@@ -57482,7 +57482,7 @@
       </c>
       <c r="C132" s="4"/>
       <c r="D132" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E132" s="4" t="s">
         <v>190</v>
@@ -57497,7 +57497,7 @@
       <c r="I132" s="5"/>
       <c r="J132" s="5"/>
       <c r="K132" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L132" s="6"/>
@@ -57516,7 +57516,7 @@
       </c>
       <c r="C133" s="4"/>
       <c r="D133" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E133" s="4" t="s">
         <v>190</v>
@@ -57531,7 +57531,7 @@
       <c r="I133" s="5"/>
       <c r="J133" s="5"/>
       <c r="K133" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L133" s="6"/>
@@ -57550,7 +57550,7 @@
       </c>
       <c r="C134" s="4"/>
       <c r="D134" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E134" s="4" t="s">
         <v>190</v>
@@ -57565,7 +57565,7 @@
       <c r="I134" s="5"/>
       <c r="J134" s="5"/>
       <c r="K134" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L134" s="6"/>
@@ -57584,7 +57584,7 @@
       </c>
       <c r="C135" s="4"/>
       <c r="D135" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E135" s="4" t="s">
         <v>504</v>
@@ -57599,7 +57599,7 @@
       <c r="I135" s="5"/>
       <c r="J135" s="5"/>
       <c r="K135" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L135" s="6"/>
@@ -57618,7 +57618,7 @@
       </c>
       <c r="C136" s="4"/>
       <c r="D136" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E136" s="4" t="s">
         <v>76</v>
@@ -57633,7 +57633,7 @@
       <c r="I136" s="5"/>
       <c r="J136" s="5"/>
       <c r="K136" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L136" s="6"/>
@@ -57685,7 +57685,7 @@
       </c>
       <c r="C138" s="4"/>
       <c r="D138" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E138" s="4" t="s">
         <v>561</v>
@@ -57753,7 +57753,7 @@
       </c>
       <c r="C140" s="4"/>
       <c r="D140" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E140" s="4" t="s">
         <v>30</v>
@@ -57859,7 +57859,7 @@
       </c>
       <c r="C143" s="4"/>
       <c r="D143" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E143" s="4" t="s">
         <v>135</v>
@@ -57874,7 +57874,7 @@
       <c r="I143" s="5"/>
       <c r="J143" s="5"/>
       <c r="K143" s="4">
-        <f t="shared" ref="K143:K169" si="4">SUM(L143:Q143)</f>
+        <f t="shared" ref="K143:K169" si="5">SUM(L143:Q143)</f>
         <v>0</v>
       </c>
       <c r="L143" s="6"/>
@@ -57910,7 +57910,7 @@
       <c r="I144" s="5"/>
       <c r="J144" s="5"/>
       <c r="K144" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L144" s="6"/>
@@ -57946,7 +57946,7 @@
       <c r="I145" s="5"/>
       <c r="J145" s="5"/>
       <c r="K145" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L145" s="6"/>
@@ -57982,7 +57982,7 @@
       <c r="I146" s="5"/>
       <c r="J146" s="5"/>
       <c r="K146" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L146" s="6"/>
@@ -58018,7 +58018,7 @@
       <c r="I147" s="5"/>
       <c r="J147" s="5"/>
       <c r="K147" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L147" s="6"/>
@@ -58037,7 +58037,7 @@
       </c>
       <c r="C148" s="4"/>
       <c r="D148" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E148" s="4" t="s">
         <v>76</v>
@@ -58050,7 +58050,7 @@
       <c r="I148" s="5"/>
       <c r="J148" s="5"/>
       <c r="K148" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L148" s="6"/>
@@ -58069,7 +58069,7 @@
       </c>
       <c r="C149" s="4"/>
       <c r="D149" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E149" s="4" t="s">
         <v>76</v>
@@ -58082,7 +58082,7 @@
       <c r="I149" s="5"/>
       <c r="J149" s="5"/>
       <c r="K149" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L149" s="6"/>
@@ -58116,7 +58116,7 @@
       <c r="I150" s="5"/>
       <c r="J150" s="5"/>
       <c r="K150" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L150" s="6"/>
@@ -58135,7 +58135,7 @@
       </c>
       <c r="C151" s="4"/>
       <c r="D151" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E151" s="4" t="s">
         <v>55</v>
@@ -58150,7 +58150,7 @@
       <c r="I151" s="5"/>
       <c r="J151" s="5"/>
       <c r="K151" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L151" s="6"/>
@@ -58184,7 +58184,7 @@
       <c r="I152" s="5"/>
       <c r="J152" s="5"/>
       <c r="K152" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L152" s="6"/>
@@ -58203,7 +58203,7 @@
       </c>
       <c r="C153" s="4"/>
       <c r="D153" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E153" s="4" t="s">
         <v>535</v>
@@ -58218,7 +58218,7 @@
       <c r="I153" s="5"/>
       <c r="J153" s="5"/>
       <c r="K153" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L153" s="6"/>
@@ -58254,7 +58254,7 @@
       <c r="I154" s="5"/>
       <c r="J154" s="5"/>
       <c r="K154" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L154" s="6"/>
@@ -58290,7 +58290,7 @@
       <c r="I155" s="5"/>
       <c r="J155" s="5"/>
       <c r="K155" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L155" s="6"/>
@@ -58324,7 +58324,7 @@
       <c r="I156" s="5"/>
       <c r="J156" s="5"/>
       <c r="K156" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L156" s="6"/>
@@ -58360,7 +58360,7 @@
       <c r="I157" s="5"/>
       <c r="J157" s="5"/>
       <c r="K157" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L157" s="6"/>
@@ -58396,7 +58396,7 @@
       <c r="I158" s="5"/>
       <c r="J158" s="5"/>
       <c r="K158" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L158" s="6"/>
@@ -58415,7 +58415,7 @@
       </c>
       <c r="C159" s="4"/>
       <c r="D159" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E159" s="4" t="s">
         <v>135</v>
@@ -58430,7 +58430,7 @@
       <c r="I159" s="5"/>
       <c r="J159" s="5"/>
       <c r="K159" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L159" s="6"/>
@@ -58449,7 +58449,7 @@
       </c>
       <c r="C160" s="4"/>
       <c r="D160" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E160" s="4" t="s">
         <v>135</v>
@@ -58464,7 +58464,7 @@
       <c r="I160" s="5"/>
       <c r="J160" s="5"/>
       <c r="K160" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L160" s="6"/>
@@ -58483,7 +58483,7 @@
       </c>
       <c r="C161" s="4"/>
       <c r="D161" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E161" s="4" t="s">
         <v>135</v>
@@ -58498,7 +58498,7 @@
       <c r="I161" s="5"/>
       <c r="J161" s="5"/>
       <c r="K161" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L161" s="6"/>
@@ -58517,7 +58517,7 @@
       </c>
       <c r="C162" s="4"/>
       <c r="D162" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E162" s="4" t="s">
         <v>135</v>
@@ -58532,7 +58532,7 @@
       <c r="I162" s="5"/>
       <c r="J162" s="5"/>
       <c r="K162" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L162" s="6"/>
@@ -58551,7 +58551,7 @@
       </c>
       <c r="C163" s="4"/>
       <c r="D163" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E163" s="4" t="s">
         <v>135</v>
@@ -58566,7 +58566,7 @@
       <c r="I163" s="5"/>
       <c r="J163" s="5"/>
       <c r="K163" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L163" s="6"/>
@@ -58585,7 +58585,7 @@
       </c>
       <c r="C164" s="4"/>
       <c r="D164" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E164" s="4" t="s">
         <v>135</v>
@@ -58600,7 +58600,7 @@
       <c r="I164" s="5"/>
       <c r="J164" s="5"/>
       <c r="K164" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L164" s="6"/>
@@ -58619,7 +58619,7 @@
       </c>
       <c r="C165" s="4"/>
       <c r="D165" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E165" s="4" t="s">
         <v>76</v>
@@ -58634,7 +58634,7 @@
       <c r="I165" s="5"/>
       <c r="J165" s="5"/>
       <c r="K165" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L165" s="6"/>
@@ -58653,7 +58653,7 @@
       </c>
       <c r="C166" s="4"/>
       <c r="D166" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E166" s="4" t="s">
         <v>76</v>
@@ -58668,7 +58668,7 @@
       <c r="I166" s="5"/>
       <c r="J166" s="5"/>
       <c r="K166" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L166" s="6"/>
@@ -58702,7 +58702,7 @@
       <c r="I167" s="5"/>
       <c r="J167" s="5"/>
       <c r="K167" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L167" s="6"/>
@@ -58738,7 +58738,7 @@
       <c r="I168" s="5"/>
       <c r="J168" s="5"/>
       <c r="K168" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L168" s="6"/>
@@ -58774,7 +58774,7 @@
       <c r="I169" s="5"/>
       <c r="J169" s="5"/>
       <c r="K169" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L169" s="6"/>
@@ -58843,7 +58843,7 @@
       <c r="I171" s="5"/>
       <c r="J171" s="5"/>
       <c r="K171" s="4">
-        <f t="shared" ref="K171:K182" si="5">SUM(L171:Q171)</f>
+        <f t="shared" ref="K171:K182" si="6">SUM(L171:Q171)</f>
         <v>0</v>
       </c>
       <c r="L171" s="6"/>
@@ -58862,7 +58862,7 @@
       </c>
       <c r="C172" s="4"/>
       <c r="D172" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E172" s="4" t="s">
         <v>69</v>
@@ -58875,7 +58875,7 @@
       <c r="I172" s="5"/>
       <c r="J172" s="5"/>
       <c r="K172" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L172" s="6"/>
@@ -58894,7 +58894,7 @@
       </c>
       <c r="C173" s="4"/>
       <c r="D173" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E173" s="4" t="s">
         <v>190</v>
@@ -58909,7 +58909,7 @@
       <c r="I173" s="5"/>
       <c r="J173" s="5"/>
       <c r="K173" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L173" s="6"/>
@@ -58928,7 +58928,7 @@
       </c>
       <c r="C174" s="4"/>
       <c r="D174" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E174" s="4" t="s">
         <v>207</v>
@@ -58943,7 +58943,7 @@
       <c r="I174" s="5"/>
       <c r="J174" s="5"/>
       <c r="K174" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L174" s="6"/>
@@ -58962,7 +58962,7 @@
       </c>
       <c r="C175" s="4"/>
       <c r="D175" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E175" s="4" t="s">
         <v>841</v>
@@ -58977,7 +58977,7 @@
       <c r="I175" s="5"/>
       <c r="J175" s="5"/>
       <c r="K175" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L175" s="6"/>
@@ -58996,7 +58996,7 @@
       </c>
       <c r="C176" s="4"/>
       <c r="D176" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E176" s="4" t="s">
         <v>841</v>
@@ -59011,7 +59011,7 @@
       <c r="I176" s="5"/>
       <c r="J176" s="5"/>
       <c r="K176" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L176" s="6"/>
@@ -59030,7 +59030,7 @@
       </c>
       <c r="C177" s="4"/>
       <c r="D177" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E177" s="4" t="s">
         <v>76</v>
@@ -59045,7 +59045,7 @@
       <c r="I177" s="5"/>
       <c r="J177" s="5"/>
       <c r="K177" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L177" s="6"/>
@@ -59064,7 +59064,7 @@
       </c>
       <c r="C178" s="4"/>
       <c r="D178" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E178" s="4" t="s">
         <v>135</v>
@@ -59079,7 +59079,7 @@
       <c r="I178" s="5"/>
       <c r="J178" s="5"/>
       <c r="K178" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L178" s="6"/>
@@ -59115,7 +59115,7 @@
       <c r="I179" s="5"/>
       <c r="J179" s="5"/>
       <c r="K179" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L179" s="6"/>
@@ -59151,7 +59151,7 @@
       <c r="I180" s="5"/>
       <c r="J180" s="5"/>
       <c r="K180" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L180" s="6"/>
@@ -59187,7 +59187,7 @@
       <c r="I181" s="5"/>
       <c r="J181" s="5"/>
       <c r="K181" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L181" s="6"/>
@@ -59206,7 +59206,7 @@
       </c>
       <c r="C182" s="4"/>
       <c r="D182" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E182" s="4" t="s">
         <v>76</v>
@@ -59221,7 +59221,7 @@
       <c r="I182" s="5"/>
       <c r="J182" s="5"/>
       <c r="K182" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L182" s="6"/>
@@ -59240,7 +59240,7 @@
       </c>
       <c r="C183" s="4"/>
       <c r="D183" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E183" s="4" t="s">
         <v>55</v>
@@ -59255,7 +59255,7 @@
       <c r="I183" s="5"/>
       <c r="J183" s="5"/>
       <c r="K183" s="4">
-        <f t="shared" ref="K183:K221" si="6">SUM(L183:Q183)</f>
+        <f t="shared" ref="K183:K221" si="7">SUM(L183:Q183)</f>
         <v>0</v>
       </c>
       <c r="L183" s="6"/>
@@ -59291,7 +59291,7 @@
       <c r="I184" s="5"/>
       <c r="J184" s="5"/>
       <c r="K184" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L184" s="6"/>
@@ -59325,7 +59325,7 @@
       <c r="I185" s="5"/>
       <c r="J185" s="5"/>
       <c r="K185" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L185" s="6"/>
@@ -59344,7 +59344,7 @@
       </c>
       <c r="C186" s="4"/>
       <c r="D186" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E186" s="4" t="s">
         <v>397</v>
@@ -59357,7 +59357,7 @@
       <c r="I186" s="5"/>
       <c r="J186" s="5"/>
       <c r="K186" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L186" s="6"/>
@@ -59391,7 +59391,7 @@
       <c r="I187" s="5"/>
       <c r="J187" s="5"/>
       <c r="K187" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L187" s="6"/>
@@ -59410,7 +59410,7 @@
       </c>
       <c r="C188" s="4"/>
       <c r="D188" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E188" s="4" t="s">
         <v>504</v>
@@ -59425,7 +59425,7 @@
       <c r="I188" s="5"/>
       <c r="J188" s="5"/>
       <c r="K188" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L188" s="6"/>
@@ -59461,7 +59461,7 @@
       <c r="I189" s="5"/>
       <c r="J189" s="5"/>
       <c r="K189" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L189" s="6"/>
@@ -59497,7 +59497,7 @@
       <c r="I190" s="5"/>
       <c r="J190" s="5"/>
       <c r="K190" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L190" s="6"/>
@@ -59533,7 +59533,7 @@
       <c r="I191" s="5"/>
       <c r="J191" s="5"/>
       <c r="K191" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L191" s="6"/>
@@ -59569,7 +59569,7 @@
       <c r="I192" s="5"/>
       <c r="J192" s="5"/>
       <c r="K192" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L192" s="6"/>
@@ -59605,7 +59605,7 @@
       <c r="I193" s="5"/>
       <c r="J193" s="5"/>
       <c r="K193" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L193" s="6"/>
@@ -59641,7 +59641,7 @@
       <c r="I194" s="5"/>
       <c r="J194" s="5"/>
       <c r="K194" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L194" s="6"/>
@@ -59677,7 +59677,7 @@
       <c r="I195" s="5"/>
       <c r="J195" s="5"/>
       <c r="K195" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L195" s="6"/>
@@ -59696,7 +59696,7 @@
       </c>
       <c r="C196" s="4"/>
       <c r="D196" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E196" s="4" t="s">
         <v>841</v>
@@ -59711,7 +59711,7 @@
       <c r="I196" s="5"/>
       <c r="J196" s="5"/>
       <c r="K196" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L196" s="6"/>
@@ -59730,7 +59730,7 @@
       </c>
       <c r="C197" s="4"/>
       <c r="D197" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E197" s="4" t="s">
         <v>841</v>
@@ -59745,7 +59745,7 @@
       <c r="I197" s="5"/>
       <c r="J197" s="5"/>
       <c r="K197" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L197" s="6"/>
@@ -59781,7 +59781,7 @@
       <c r="I198" s="5"/>
       <c r="J198" s="5"/>
       <c r="K198" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L198" s="6"/>
@@ -59798,7 +59798,7 @@
       <c r="B199" s="4"/>
       <c r="C199" s="4"/>
       <c r="D199" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E199" s="4"/>
       <c r="F199" s="4"/>
@@ -59809,7 +59809,7 @@
       <c r="I199" s="5"/>
       <c r="J199" s="5"/>
       <c r="K199" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L199" s="6"/>
@@ -59845,7 +59845,7 @@
       <c r="I200" s="5"/>
       <c r="J200" s="5"/>
       <c r="K200" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L200" s="6"/>
@@ -59864,7 +59864,7 @@
       </c>
       <c r="C201" s="4"/>
       <c r="D201" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E201" s="4" t="s">
         <v>397</v>
@@ -59879,7 +59879,7 @@
       <c r="I201" s="5"/>
       <c r="J201" s="5"/>
       <c r="K201" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L201" s="6"/>
@@ -59915,7 +59915,7 @@
       <c r="I202" s="5"/>
       <c r="J202" s="5"/>
       <c r="K202" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L202" s="6"/>
@@ -59951,7 +59951,7 @@
       <c r="I203" s="5"/>
       <c r="J203" s="5"/>
       <c r="K203" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L203" s="6"/>
@@ -59983,7 +59983,7 @@
       <c r="I204" s="5"/>
       <c r="J204" s="5"/>
       <c r="K204" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L204" s="6"/>
@@ -60015,7 +60015,7 @@
       <c r="I205" s="5"/>
       <c r="J205" s="5"/>
       <c r="K205" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L205" s="6"/>
@@ -60047,7 +60047,7 @@
       <c r="I206" s="5"/>
       <c r="J206" s="5"/>
       <c r="K206" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L206" s="6"/>
@@ -60077,7 +60077,7 @@
       <c r="I207" s="5"/>
       <c r="J207" s="5"/>
       <c r="K207" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L207" s="6"/>
@@ -60107,7 +60107,7 @@
       <c r="I208" s="5"/>
       <c r="J208" s="5"/>
       <c r="K208" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L208" s="6"/>
@@ -60137,7 +60137,7 @@
       <c r="I209" s="5"/>
       <c r="J209" s="5"/>
       <c r="K209" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L209" s="6"/>
@@ -60173,7 +60173,7 @@
       <c r="I210" s="5"/>
       <c r="J210" s="5"/>
       <c r="K210" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L210" s="6"/>
@@ -60192,7 +60192,7 @@
       </c>
       <c r="C211" s="4"/>
       <c r="D211" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E211" s="4" t="s">
         <v>463</v>
@@ -60207,7 +60207,7 @@
       <c r="I211" s="5"/>
       <c r="J211" s="5"/>
       <c r="K211" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L211" s="6"/>
@@ -60243,7 +60243,7 @@
       <c r="I212" s="5"/>
       <c r="J212" s="5"/>
       <c r="K212" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L212" s="6"/>
@@ -60262,7 +60262,7 @@
       </c>
       <c r="C213" s="4"/>
       <c r="D213" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E213" s="4" t="s">
         <v>397</v>
@@ -60277,7 +60277,7 @@
       <c r="I213" s="5"/>
       <c r="J213" s="5"/>
       <c r="K213" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L213" s="6"/>
@@ -60296,7 +60296,7 @@
       </c>
       <c r="C214" s="4"/>
       <c r="D214" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E214" s="4" t="s">
         <v>397</v>
@@ -60311,7 +60311,7 @@
       <c r="I214" s="5"/>
       <c r="J214" s="5"/>
       <c r="K214" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L214" s="6"/>
@@ -60330,7 +60330,7 @@
       </c>
       <c r="C215" s="4"/>
       <c r="D215" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E215" s="4" t="s">
         <v>397</v>
@@ -60345,7 +60345,7 @@
       <c r="I215" s="5"/>
       <c r="J215" s="5"/>
       <c r="K215" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L215" s="6"/>
@@ -60381,7 +60381,7 @@
       <c r="I216" s="5"/>
       <c r="J216" s="5"/>
       <c r="K216" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L216" s="6"/>
@@ -60415,7 +60415,7 @@
       <c r="I217" s="5"/>
       <c r="J217" s="5"/>
       <c r="K217" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L217" s="6"/>
@@ -60449,7 +60449,7 @@
       <c r="I218" s="5"/>
       <c r="J218" s="5"/>
       <c r="K218" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L218" s="6"/>
@@ -60483,7 +60483,7 @@
       <c r="I219" s="5"/>
       <c r="J219" s="5"/>
       <c r="K219" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L219" s="6"/>
@@ -60517,7 +60517,7 @@
       <c r="I220" s="5"/>
       <c r="J220" s="5"/>
       <c r="K220" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L220" s="6"/>
@@ -60551,7 +60551,7 @@
       <c r="I221" s="5"/>
       <c r="J221" s="5"/>
       <c r="K221" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L221" s="6"/>
@@ -60587,7 +60587,7 @@
       <c r="I222" s="5"/>
       <c r="J222" s="5"/>
       <c r="K222" s="4">
-        <f t="shared" ref="K218:K234" si="7">SUM(L222:Q222)</f>
+        <f t="shared" ref="K218:K234" si="8">SUM(L222:Q222)</f>
         <v>0</v>
       </c>
       <c r="L222" s="6"/>
@@ -60623,7 +60623,7 @@
       <c r="I223" s="5"/>
       <c r="J223" s="5"/>
       <c r="K223" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L223" s="6"/>
@@ -60659,7 +60659,7 @@
       <c r="I224" s="5"/>
       <c r="J224" s="5"/>
       <c r="K224" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L224" s="6"/>
@@ -60695,7 +60695,7 @@
       <c r="I225" s="5"/>
       <c r="J225" s="5"/>
       <c r="K225" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L225" s="6"/>
@@ -60731,7 +60731,7 @@
       <c r="I226" s="5"/>
       <c r="J226" s="5"/>
       <c r="K226" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L226" s="6"/>
@@ -60767,7 +60767,7 @@
       <c r="I227" s="5"/>
       <c r="J227" s="5"/>
       <c r="K227" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L227" s="6"/>
@@ -60801,7 +60801,7 @@
       <c r="I228" s="5"/>
       <c r="J228" s="5"/>
       <c r="K228" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L228" s="6"/>
@@ -60820,7 +60820,7 @@
       </c>
       <c r="C229" s="4"/>
       <c r="D229" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E229" s="4" t="s">
         <v>190</v>
@@ -60835,7 +60835,7 @@
       <c r="I229" s="5"/>
       <c r="J229" s="5"/>
       <c r="K229" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L229" s="6"/>
@@ -60871,7 +60871,7 @@
       <c r="I230" s="5"/>
       <c r="J230" s="5"/>
       <c r="K230" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L230" s="6"/>
@@ -60907,7 +60907,7 @@
       <c r="I231" s="5"/>
       <c r="J231" s="5"/>
       <c r="K231" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L231" s="6"/>
@@ -60943,7 +60943,7 @@
       <c r="I232" s="5"/>
       <c r="J232" s="5"/>
       <c r="K232" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L232" s="6"/>
@@ -60979,7 +60979,7 @@
       <c r="I233" s="5"/>
       <c r="J233" s="5"/>
       <c r="K233" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L233" s="6"/>
@@ -61013,7 +61013,7 @@
       <c r="I234" s="5"/>
       <c r="J234" s="5"/>
       <c r="K234" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L234" s="6"/>
@@ -61063,7 +61063,7 @@
       </c>
       <c r="C236" s="4"/>
       <c r="D236" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E236" s="4" t="s">
         <v>535</v>
@@ -61076,7 +61076,7 @@
       <c r="I236" s="5"/>
       <c r="J236" s="5"/>
       <c r="K236" s="4">
-        <f t="shared" ref="K236:K266" si="8">SUM(L236:Q236)</f>
+        <f t="shared" ref="K236:K266" si="9">SUM(L236:Q236)</f>
         <v>0</v>
       </c>
       <c r="L236" s="6"/>
@@ -61095,7 +61095,7 @@
       </c>
       <c r="C237" s="4"/>
       <c r="D237" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E237" s="4" t="s">
         <v>397</v>
@@ -61110,7 +61110,7 @@
       <c r="I237" s="5"/>
       <c r="J237" s="5"/>
       <c r="K237" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L237" s="6"/>
@@ -61129,7 +61129,7 @@
       </c>
       <c r="C238" s="4"/>
       <c r="D238" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E238" s="4" t="s">
         <v>190</v>
@@ -61144,7 +61144,7 @@
       <c r="I238" s="5"/>
       <c r="J238" s="5"/>
       <c r="K238" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L238" s="6"/>
@@ -61178,7 +61178,7 @@
       <c r="I239" s="5"/>
       <c r="J239" s="5"/>
       <c r="K239" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L239" s="6"/>
@@ -61214,7 +61214,7 @@
       <c r="I240" s="5"/>
       <c r="J240" s="5"/>
       <c r="K240" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L240" s="6"/>
@@ -61233,7 +61233,7 @@
       </c>
       <c r="C241" s="4"/>
       <c r="D241" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E241" s="4" t="s">
         <v>248</v>
@@ -61248,7 +61248,7 @@
       <c r="I241" s="5"/>
       <c r="J241" s="5"/>
       <c r="K241" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L241" s="6"/>
@@ -61267,7 +61267,7 @@
       </c>
       <c r="C242" s="4"/>
       <c r="D242" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E242" s="4" t="s">
         <v>360</v>
@@ -61282,7 +61282,7 @@
       <c r="I242" s="5"/>
       <c r="J242" s="5"/>
       <c r="K242" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L242" s="6"/>
@@ -61318,7 +61318,7 @@
       <c r="I243" s="5"/>
       <c r="J243" s="5"/>
       <c r="K243" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L243" s="6"/>
@@ -61337,7 +61337,7 @@
       </c>
       <c r="C244" s="4"/>
       <c r="D244" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E244" s="4" t="s">
         <v>360</v>
@@ -61352,7 +61352,7 @@
       <c r="I244" s="5"/>
       <c r="J244" s="5"/>
       <c r="K244" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L244" s="6"/>
@@ -61388,7 +61388,7 @@
       <c r="I245" s="5"/>
       <c r="J245" s="5"/>
       <c r="K245" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L245" s="6"/>
@@ -61424,7 +61424,7 @@
       <c r="I246" s="5"/>
       <c r="J246" s="5"/>
       <c r="K246" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L246" s="6"/>
@@ -61443,7 +61443,7 @@
       </c>
       <c r="C247" s="4"/>
       <c r="D247" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E247" s="4" t="s">
         <v>397</v>
@@ -61458,7 +61458,7 @@
       <c r="I247" s="5"/>
       <c r="J247" s="5"/>
       <c r="K247" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L247" s="6"/>
@@ -61477,7 +61477,7 @@
       </c>
       <c r="C248" s="4"/>
       <c r="D248" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E248" s="4" t="s">
         <v>397</v>
@@ -61492,7 +61492,7 @@
       <c r="I248" s="5"/>
       <c r="J248" s="5"/>
       <c r="K248" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L248" s="6"/>
@@ -61511,7 +61511,7 @@
       </c>
       <c r="C249" s="4"/>
       <c r="D249" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E249" s="4" t="s">
         <v>207</v>
@@ -61526,7 +61526,7 @@
       <c r="I249" s="5"/>
       <c r="J249" s="5"/>
       <c r="K249" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L249" s="6"/>
@@ -61545,7 +61545,7 @@
       </c>
       <c r="C250" s="4"/>
       <c r="D250" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E250" s="4" t="s">
         <v>76</v>
@@ -61560,7 +61560,7 @@
       <c r="I250" s="5"/>
       <c r="J250" s="5"/>
       <c r="K250" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L250" s="6"/>
@@ -61579,7 +61579,7 @@
       </c>
       <c r="C251" s="4"/>
       <c r="D251" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E251" s="4" t="s">
         <v>248</v>
@@ -61594,7 +61594,7 @@
       <c r="I251" s="5"/>
       <c r="J251" s="5"/>
       <c r="K251" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L251" s="6"/>
@@ -61613,7 +61613,7 @@
       </c>
       <c r="C252" s="4"/>
       <c r="D252" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E252" s="4" t="s">
         <v>135</v>
@@ -61626,7 +61626,7 @@
       <c r="I252" s="5"/>
       <c r="J252" s="5"/>
       <c r="K252" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L252" s="6"/>
@@ -61645,7 +61645,7 @@
       </c>
       <c r="C253" s="4"/>
       <c r="D253" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E253" s="4" t="s">
         <v>135</v>
@@ -61658,7 +61658,7 @@
       <c r="I253" s="5"/>
       <c r="J253" s="5"/>
       <c r="K253" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L253" s="6"/>
@@ -61677,7 +61677,7 @@
       </c>
       <c r="C254" s="4"/>
       <c r="D254" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E254" s="4" t="s">
         <v>135</v>
@@ -61692,7 +61692,7 @@
       <c r="I254" s="5"/>
       <c r="J254" s="5"/>
       <c r="K254" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L254" s="6"/>
@@ -61711,7 +61711,7 @@
       </c>
       <c r="C255" s="4"/>
       <c r="D255" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E255" s="4" t="s">
         <v>135</v>
@@ -61726,7 +61726,7 @@
       <c r="I255" s="5"/>
       <c r="J255" s="5"/>
       <c r="K255" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L255" s="6"/>
@@ -61745,7 +61745,7 @@
       </c>
       <c r="C256" s="4"/>
       <c r="D256" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E256" s="4" t="s">
         <v>135</v>
@@ -61760,7 +61760,7 @@
       <c r="I256" s="5"/>
       <c r="J256" s="5"/>
       <c r="K256" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L256" s="6"/>
@@ -61812,7 +61812,7 @@
       </c>
       <c r="C258" s="4"/>
       <c r="D258" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E258" s="4" t="s">
         <v>76</v>
@@ -61877,7 +61877,7 @@
       </c>
       <c r="C260" s="4"/>
       <c r="D260" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E260" s="4" t="s">
         <v>841</v>
@@ -61911,7 +61911,7 @@
       </c>
       <c r="C261" s="4"/>
       <c r="D261" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E261" s="4" t="s">
         <v>841</v>
@@ -61978,7 +61978,7 @@
       </c>
       <c r="C263" s="4"/>
       <c r="D263" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E263" s="4" t="s">
         <v>135</v>
@@ -62043,7 +62043,7 @@
       </c>
       <c r="C265" s="4"/>
       <c r="D265" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E265" s="4" t="s">
         <v>561</v>
@@ -62056,7 +62056,7 @@
       <c r="I265" s="5"/>
       <c r="J265" s="5"/>
       <c r="K265" s="4">
-        <f t="shared" ref="K265:K270" si="9">SUM(L265:Q265)</f>
+        <f t="shared" ref="K265:K270" si="10">SUM(L265:Q265)</f>
         <v>0</v>
       </c>
       <c r="L265" s="6"/>
@@ -62075,7 +62075,7 @@
       </c>
       <c r="C266" s="4"/>
       <c r="D266" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E266" s="4" t="s">
         <v>30</v>
@@ -62090,7 +62090,7 @@
       <c r="I266" s="5"/>
       <c r="J266" s="5"/>
       <c r="K266" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L266" s="6"/>
@@ -62109,7 +62109,7 @@
       </c>
       <c r="C267" s="4"/>
       <c r="D267" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E267" s="4" t="s">
         <v>30</v>
@@ -62124,7 +62124,7 @@
       <c r="I267" s="5"/>
       <c r="J267" s="5"/>
       <c r="K267" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L267" s="6"/>
@@ -62143,7 +62143,7 @@
       </c>
       <c r="C268" s="4"/>
       <c r="D268" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E268" s="4" t="s">
         <v>30</v>
@@ -62158,7 +62158,7 @@
       <c r="I268" s="5"/>
       <c r="J268" s="5"/>
       <c r="K268" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L268" s="6"/>
@@ -62177,7 +62177,7 @@
       </c>
       <c r="C269" s="4"/>
       <c r="D269" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E269" s="4" t="s">
         <v>135</v>
@@ -62190,7 +62190,7 @@
       <c r="I269" s="5"/>
       <c r="J269" s="5"/>
       <c r="K269" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L269" s="6"/>
@@ -62209,7 +62209,7 @@
       </c>
       <c r="C270" s="4"/>
       <c r="D270" s="4" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="E270" s="4" t="s">
         <v>135</v>
@@ -62222,7 +62222,7 @@
       <c r="I270" s="5"/>
       <c r="J270" s="5"/>
       <c r="K270" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L270" s="6"/>
